--- a/data_exploration/Encoding/categorical_value_mapping.xlsx
+++ b/data_exploration/Encoding/categorical_value_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\Documents\GitHub Repository\Patient_Feedback\data_exploration\Encoding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2C1DA8C-EBB3-48E0-A46E-912A01B2C4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25551D3-C813-4ECA-8A9A-5BD977350CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="320">
   <si>
     <t>Column</t>
   </si>
@@ -974,13 +974,37 @@
   </si>
   <si>
     <t>Ordinary Complaint</t>
+  </si>
+  <si>
+    <t>New_Encoding</t>
+  </si>
+  <si>
+    <t>Cardinality</t>
+  </si>
+  <si>
+    <t>Fixing Report</t>
+  </si>
+  <si>
+    <t>sub_category</t>
+  </si>
+  <si>
+    <t>Before</t>
+  </si>
+  <si>
+    <t>After</t>
+  </si>
+  <si>
+    <t>harm level</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -993,16 +1017,40 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1025,14 +1073,112 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1336,14 +1482,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D338"/>
+  <dimension ref="A1:H354"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="78.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="7"/>
+    <col min="7" max="7" width="13.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1353,8 +1504,16 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D1" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1364,11 +1523,12 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G2" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="H2" s="21"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1378,8 +1538,14 @@
       <c r="C3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G3" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1389,8 +1555,12 @@
       <c r="C4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G4" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="H4" s="22"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1400,8 +1570,14 @@
       <c r="C5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G5" s="23">
+        <v>7</v>
+      </c>
+      <c r="H5" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1411,8 +1587,14 @@
       <c r="C6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G6" s="23">
+        <v>17</v>
+      </c>
+      <c r="H6" s="23">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1422,8 +1604,14 @@
       <c r="C7">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G7" s="23">
+        <v>20</v>
+      </c>
+      <c r="H7" s="23">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1433,8 +1621,14 @@
       <c r="C8">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G8" s="23">
+        <v>25</v>
+      </c>
+      <c r="H8" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1444,8 +1638,12 @@
       <c r="C9">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G9" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="H9" s="22"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1455,8 +1653,14 @@
       <c r="C10">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G10" s="23">
+        <v>4</v>
+      </c>
+      <c r="H10" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1466,8 +1670,14 @@
       <c r="C11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G11" s="23">
+        <v>5</v>
+      </c>
+      <c r="H11" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1477,8 +1687,12 @@
       <c r="C12">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G12" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="H12" s="22"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1488,8 +1702,14 @@
       <c r="C13">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G13" s="23">
+        <v>3</v>
+      </c>
+      <c r="H13" s="23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1499,8 +1719,14 @@
       <c r="C14">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G14" s="23">
+        <v>5</v>
+      </c>
+      <c r="H14" s="23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1510,8 +1736,14 @@
       <c r="C15">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G15" s="23">
+        <v>7</v>
+      </c>
+      <c r="H15" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1521,8 +1753,12 @@
       <c r="C16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G16" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="H16" s="13"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1532,8 +1768,14 @@
       <c r="C17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G17" s="23">
+        <v>2</v>
+      </c>
+      <c r="H17" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1543,8 +1785,12 @@
       <c r="C18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G18" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="H18" s="13"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1554,8 +1800,14 @@
       <c r="C19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G19" s="23">
+        <v>7</v>
+      </c>
+      <c r="H19" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1566,7 +1818,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1577,7 +1829,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1588,7 +1840,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1599,7 +1851,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -1610,7 +1862,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -1621,7 +1873,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -1632,7 +1884,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1643,7 +1895,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -1654,7 +1906,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -1665,7 +1917,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>3</v>
       </c>
@@ -1676,7 +1928,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -1687,7 +1939,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -1698,7 +1950,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>3</v>
       </c>
@@ -1709,7 +1961,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>3</v>
       </c>
@@ -1720,7 +1972,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -1731,7 +1983,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>3</v>
       </c>
@@ -1742,7 +1994,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>3</v>
       </c>
@@ -1753,7 +2005,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -1764,7 +2016,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -1775,7 +2027,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>3</v>
       </c>
@@ -1786,7 +2038,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -1797,7 +2049,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -1807,11 +2059,8 @@
       <c r="C42">
         <v>1</v>
       </c>
-      <c r="D42">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -1822,7 +2071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -1833,7 +2082,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -1844,7 +2093,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -1855,7 +2104,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>44</v>
       </c>
@@ -1866,7 +2115,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>44</v>
       </c>
@@ -2581,7 +2830,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>80</v>
       </c>
@@ -2592,7 +2841,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>80</v>
       </c>
@@ -2603,7 +2852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>80</v>
       </c>
@@ -2614,7 +2863,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>80</v>
       </c>
@@ -2625,7 +2874,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>80</v>
       </c>
@@ -2636,7 +2885,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>89</v>
       </c>
@@ -2646,2437 +2895,3199 @@
       <c r="C118">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
+      <c r="E118" s="4"/>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C119">
+      <c r="C119" s="5">
         <v>1</v>
       </c>
-      <c r="D119">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
+      <c r="D119" s="5"/>
+      <c r="E119" s="15">
+        <v>3</v>
+      </c>
+      <c r="F119" s="12"/>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C120">
+      <c r="C120" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+      <c r="D120" s="2"/>
+      <c r="E120" s="15"/>
+      <c r="F120" s="12"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="C121">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
+      <c r="C121" s="9">
+        <v>3</v>
+      </c>
+      <c r="D121" s="9"/>
+      <c r="E121" s="15"/>
+      <c r="F121" s="12"/>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C122">
+      <c r="C122" s="5">
         <v>1</v>
       </c>
-      <c r="D122">
+      <c r="D122" s="5"/>
+      <c r="E122" s="17">
         <v>7</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+      <c r="F122" s="12"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C123">
+      <c r="C123" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+      <c r="D123" s="2"/>
+      <c r="E123" s="17"/>
+      <c r="F123" s="12"/>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C124">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+      <c r="C124" s="2">
+        <v>3</v>
+      </c>
+      <c r="D124" s="2"/>
+      <c r="E124" s="17"/>
+      <c r="F124" s="12"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C125">
+      <c r="C125" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
+      <c r="D125" s="2"/>
+      <c r="E125" s="17"/>
+      <c r="F125" s="12"/>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C126">
+      <c r="C126" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
+      <c r="D126" s="2"/>
+      <c r="E126" s="17"/>
+      <c r="F126" s="12"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C127">
+      <c r="C127" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
+      <c r="D127" s="2"/>
+      <c r="E127" s="17"/>
+      <c r="F127" s="12"/>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="C128">
+      <c r="C128" s="9">
         <v>7</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+      <c r="D128" s="9"/>
+      <c r="E128" s="17"/>
+      <c r="F128" s="12"/>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C129">
+      <c r="C129" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+      <c r="D129" s="6">
+        <v>1</v>
+      </c>
+      <c r="E129" s="17">
+        <v>27</v>
+      </c>
+      <c r="F129" s="12"/>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C130">
+      <c r="C130" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+      <c r="D130" s="2">
+        <v>2</v>
+      </c>
+      <c r="E130" s="17"/>
+      <c r="F130" s="12"/>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C131">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+      <c r="C131" s="2">
+        <v>3</v>
+      </c>
+      <c r="D131" s="2">
+        <v>3</v>
+      </c>
+      <c r="E131" s="17"/>
+      <c r="F131" s="12"/>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C132">
+      <c r="C132" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
+      <c r="D132" s="18">
+        <v>4</v>
+      </c>
+      <c r="E132" s="17"/>
+      <c r="F132" s="12"/>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C133">
+      <c r="C133" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
+      <c r="D133" s="18">
+        <v>5</v>
+      </c>
+      <c r="E133" s="17"/>
+      <c r="F133" s="12"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C134">
+      <c r="C134" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
+      <c r="D134" s="3">
+        <v>6</v>
+      </c>
+      <c r="E134" s="17"/>
+      <c r="F134" s="12"/>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C135">
+      <c r="C135" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
+      <c r="D135" s="3">
+        <v>6</v>
+      </c>
+      <c r="E135" s="17"/>
+      <c r="F135" s="12"/>
+      <c r="G135" s="2">
+        <v>7</v>
+      </c>
+      <c r="H135" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C136">
+      <c r="C136" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
+      <c r="D136" s="18">
+        <v>8</v>
+      </c>
+      <c r="E136" s="17"/>
+      <c r="F136" s="12"/>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="C137">
+      <c r="C137" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
+      <c r="D137" s="18">
+        <v>9</v>
+      </c>
+      <c r="E137" s="17"/>
+      <c r="F137" s="12"/>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C138">
+      <c r="C138" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
+      <c r="D138" s="18">
+        <v>10</v>
+      </c>
+      <c r="E138" s="17"/>
+      <c r="F138" s="12"/>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C139">
+      <c r="C139" s="2">
         <v>11</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
+      <c r="D139" s="18">
+        <v>11</v>
+      </c>
+      <c r="E139" s="17"/>
+      <c r="F139" s="12"/>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C140">
+      <c r="C140" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
+      <c r="D140" s="18">
+        <v>12</v>
+      </c>
+      <c r="E140" s="17"/>
+      <c r="F140" s="12"/>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C141">
+      <c r="C141" s="2">
         <v>13</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
+      <c r="D141" s="18">
+        <v>13</v>
+      </c>
+      <c r="E141" s="17"/>
+      <c r="F141" s="12"/>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C142">
+      <c r="C142" s="2">
         <v>14</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
+      <c r="D142" s="18">
+        <v>14</v>
+      </c>
+      <c r="E142" s="17"/>
+      <c r="F142" s="12"/>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="C143">
+      <c r="C143" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
+      <c r="D143" s="18">
+        <v>15</v>
+      </c>
+      <c r="E143" s="17"/>
+      <c r="F143" s="12"/>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C144">
+      <c r="C144" s="2">
         <v>16</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
+      <c r="D144" s="3">
+        <v>16</v>
+      </c>
+      <c r="E144" s="17"/>
+      <c r="F144" s="12"/>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C145">
+      <c r="C145" s="2">
         <v>17</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
+      <c r="D145" s="3">
+        <v>16</v>
+      </c>
+      <c r="E145" s="17"/>
+      <c r="F145" s="12"/>
+      <c r="G145" s="2">
+        <v>17</v>
+      </c>
+      <c r="H145" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C146">
+      <c r="C146" s="2">
         <v>18</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
+      <c r="D146" s="18">
+        <v>18</v>
+      </c>
+      <c r="E146" s="17"/>
+      <c r="F146" s="12"/>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C147">
+      <c r="C147" s="2">
         <v>19</v>
       </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
+      <c r="D147" s="3">
+        <v>19</v>
+      </c>
+      <c r="E147" s="17"/>
+      <c r="F147" s="12"/>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C148">
+      <c r="C148" s="2">
         <v>20</v>
       </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
+      <c r="D148" s="3">
+        <v>19</v>
+      </c>
+      <c r="E148" s="17"/>
+      <c r="F148" s="12"/>
+      <c r="G148" s="2">
+        <v>20</v>
+      </c>
+      <c r="H148" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C149">
+      <c r="C149" s="2">
         <v>21</v>
       </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
+      <c r="D149" s="19">
+        <v>21</v>
+      </c>
+      <c r="E149" s="17"/>
+      <c r="F149" s="12"/>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C150">
+      <c r="C150" s="2">
         <v>22</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
+      <c r="D150" s="19">
+        <v>22</v>
+      </c>
+      <c r="E150" s="17"/>
+      <c r="F150" s="12"/>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C151">
+      <c r="C151" s="2">
         <v>23</v>
       </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
+      <c r="D151" s="19">
+        <v>23</v>
+      </c>
+      <c r="E151" s="17"/>
+      <c r="F151" s="12"/>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C152">
+      <c r="C152" s="2">
         <v>24</v>
       </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
+      <c r="D152" s="19">
+        <v>24</v>
+      </c>
+      <c r="E152" s="17"/>
+      <c r="F152" s="12"/>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B153" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C153">
+      <c r="C153" s="2">
         <v>25</v>
       </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
+      <c r="D153" s="3">
+        <v>1</v>
+      </c>
+      <c r="E153" s="17"/>
+      <c r="F153" s="12"/>
+      <c r="G153" s="2">
+        <v>25</v>
+      </c>
+      <c r="H153" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B154" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="C154">
+      <c r="C154" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
+      <c r="D154" s="19">
+        <v>26</v>
+      </c>
+      <c r="E154" s="17"/>
+      <c r="F154" s="12"/>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B155" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C155">
+      <c r="C155" s="2">
         <v>27</v>
       </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
+      <c r="D155" s="19">
+        <v>27</v>
+      </c>
+      <c r="E155" s="17"/>
+      <c r="F155" s="12"/>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B156" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C156">
+      <c r="C156" s="2">
         <v>28</v>
       </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
+      <c r="D156" s="19">
+        <v>28</v>
+      </c>
+      <c r="E156" s="17"/>
+      <c r="F156" s="12"/>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B157" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C157">
+      <c r="C157" s="2">
         <v>29</v>
       </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
+      <c r="D157" s="19">
+        <v>29</v>
+      </c>
+      <c r="E157" s="17"/>
+      <c r="F157" s="12"/>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B158" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C158">
+      <c r="C158" s="2">
         <v>30</v>
       </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
+      <c r="D158" s="19">
+        <v>30</v>
+      </c>
+      <c r="E158" s="17"/>
+      <c r="F158" s="12"/>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B159" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="C159">
+      <c r="C159" s="9">
         <v>31</v>
       </c>
-      <c r="D159">
+      <c r="D159" s="9">
+        <v>31</v>
+      </c>
+      <c r="E159" s="17"/>
+      <c r="F159" s="12"/>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C160" s="5">
+        <v>1</v>
+      </c>
+      <c r="D160" s="5"/>
+      <c r="E160" s="17">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C161" s="2">
+        <v>2</v>
+      </c>
+      <c r="D161" s="2"/>
+      <c r="E161" s="17"/>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C162" s="2">
+        <v>3</v>
+      </c>
+      <c r="D162" s="2"/>
+      <c r="E162" s="17"/>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C163" s="2">
+        <v>4</v>
+      </c>
+      <c r="D163" s="2"/>
+      <c r="E163" s="17"/>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C164" s="2">
+        <v>5</v>
+      </c>
+      <c r="D164" s="2"/>
+      <c r="E164" s="17"/>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C165" s="2">
+        <v>6</v>
+      </c>
+      <c r="D165" s="2"/>
+      <c r="E165" s="17"/>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C166" s="2">
+        <v>7</v>
+      </c>
+      <c r="D166" s="2"/>
+      <c r="E166" s="17"/>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C167" s="2">
+        <v>8</v>
+      </c>
+      <c r="D167" s="2"/>
+      <c r="E167" s="17"/>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C168" s="2">
+        <v>9</v>
+      </c>
+      <c r="D168" s="2"/>
+      <c r="E168" s="17"/>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C169" s="2">
+        <v>10</v>
+      </c>
+      <c r="D169" s="2"/>
+      <c r="E169" s="17"/>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C170" s="2">
+        <v>11</v>
+      </c>
+      <c r="D170" s="2"/>
+      <c r="E170" s="17"/>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C171" s="2">
+        <v>12</v>
+      </c>
+      <c r="D171" s="2"/>
+      <c r="E171" s="17"/>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C172" s="2">
+        <v>13</v>
+      </c>
+      <c r="D172" s="2"/>
+      <c r="E172" s="17"/>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C173" s="2">
+        <v>14</v>
+      </c>
+      <c r="D173" s="2"/>
+      <c r="E173" s="17"/>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C174" s="2">
+        <v>15</v>
+      </c>
+      <c r="D174" s="2"/>
+      <c r="E174" s="17"/>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C175" s="2">
+        <v>16</v>
+      </c>
+      <c r="D175" s="2"/>
+      <c r="E175" s="17"/>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C176" s="2">
+        <v>17</v>
+      </c>
+      <c r="D176" s="2"/>
+      <c r="E176" s="17"/>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C177" s="2">
+        <v>18</v>
+      </c>
+      <c r="D177" s="2"/>
+      <c r="E177" s="17"/>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C178" s="2">
+        <v>19</v>
+      </c>
+      <c r="D178" s="2"/>
+      <c r="E178" s="17"/>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C179" s="2">
+        <v>20</v>
+      </c>
+      <c r="D179" s="2"/>
+      <c r="E179" s="17"/>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C180" s="2">
+        <v>21</v>
+      </c>
+      <c r="D180" s="2"/>
+      <c r="E180" s="17"/>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C181" s="2">
+        <v>22</v>
+      </c>
+      <c r="D181" s="2"/>
+      <c r="E181" s="17"/>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C182" s="2">
+        <v>23</v>
+      </c>
+      <c r="D182" s="2"/>
+      <c r="E182" s="17"/>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C183" s="2">
+        <v>24</v>
+      </c>
+      <c r="D183" s="2"/>
+      <c r="E183" s="17"/>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C184" s="2">
+        <v>25</v>
+      </c>
+      <c r="D184" s="2"/>
+      <c r="E184" s="17"/>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C185" s="2">
+        <v>26</v>
+      </c>
+      <c r="D185" s="2"/>
+      <c r="E185" s="17"/>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C186" s="2">
+        <v>27</v>
+      </c>
+      <c r="D186" s="2"/>
+      <c r="E186" s="17"/>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C187" s="2">
+        <v>28</v>
+      </c>
+      <c r="D187" s="2"/>
+      <c r="E187" s="17"/>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C188" s="2">
+        <v>29</v>
+      </c>
+      <c r="D188" s="2"/>
+      <c r="E188" s="17"/>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C189" s="2">
+        <v>30</v>
+      </c>
+      <c r="D189" s="2"/>
+      <c r="E189" s="17"/>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C190" s="2">
+        <v>31</v>
+      </c>
+      <c r="D190" s="2"/>
+      <c r="E190" s="17"/>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C191" s="2">
+        <v>32</v>
+      </c>
+      <c r="D191" s="2"/>
+      <c r="E191" s="17"/>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C192" s="2">
         <v>33</v>
       </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>135</v>
-      </c>
-      <c r="B160" t="s">
-        <v>136</v>
-      </c>
-      <c r="C160">
+      <c r="D192" s="2"/>
+      <c r="E192" s="17"/>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C193" s="2">
+        <v>34</v>
+      </c>
+      <c r="D193" s="2"/>
+      <c r="E193" s="17"/>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C194" s="2">
+        <v>35</v>
+      </c>
+      <c r="D194" s="2"/>
+      <c r="E194" s="17"/>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C195" s="2">
+        <v>36</v>
+      </c>
+      <c r="D195" s="2"/>
+      <c r="E195" s="17"/>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C196" s="2">
+        <v>37</v>
+      </c>
+      <c r="D196" s="2"/>
+      <c r="E196" s="17"/>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C197" s="2">
+        <v>38</v>
+      </c>
+      <c r="D197" s="2"/>
+      <c r="E197" s="17"/>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C198" s="2">
+        <v>39</v>
+      </c>
+      <c r="D198" s="2"/>
+      <c r="E198" s="17"/>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C199" s="2">
+        <v>40</v>
+      </c>
+      <c r="D199" s="2"/>
+      <c r="E199" s="17"/>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C200" s="2">
+        <v>41</v>
+      </c>
+      <c r="D200" s="2"/>
+      <c r="E200" s="17"/>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C201" s="2">
+        <v>42</v>
+      </c>
+      <c r="D201" s="2"/>
+      <c r="E201" s="17"/>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C202" s="2">
+        <v>43</v>
+      </c>
+      <c r="D202" s="2"/>
+      <c r="E202" s="17"/>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C203" s="2">
+        <v>44</v>
+      </c>
+      <c r="D203" s="2"/>
+      <c r="E203" s="17"/>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A204" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C204" s="2">
+        <v>45</v>
+      </c>
+      <c r="D204" s="2"/>
+      <c r="E204" s="17"/>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A205" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C205" s="2">
+        <v>46</v>
+      </c>
+      <c r="D205" s="2"/>
+      <c r="E205" s="17"/>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C206" s="2">
+        <v>47</v>
+      </c>
+      <c r="D206" s="2"/>
+      <c r="E206" s="17"/>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C207" s="2">
+        <v>48</v>
+      </c>
+      <c r="D207" s="2"/>
+      <c r="E207" s="17"/>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C208" s="2">
+        <v>49</v>
+      </c>
+      <c r="D208" s="2"/>
+      <c r="E208" s="17"/>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C209" s="2">
+        <v>50</v>
+      </c>
+      <c r="D209" s="2"/>
+      <c r="E209" s="17"/>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C210" s="2">
+        <v>51</v>
+      </c>
+      <c r="D210" s="2"/>
+      <c r="E210" s="17"/>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C211" s="2">
+        <v>52</v>
+      </c>
+      <c r="D211" s="2"/>
+      <c r="E211" s="17"/>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C212" s="2">
+        <v>53</v>
+      </c>
+      <c r="D212" s="2"/>
+      <c r="E212" s="17"/>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C213" s="2">
+        <v>54</v>
+      </c>
+      <c r="D213" s="2"/>
+      <c r="E213" s="17"/>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C214" s="2">
+        <v>55</v>
+      </c>
+      <c r="D214" s="2"/>
+      <c r="E214" s="17"/>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C215" s="2">
+        <v>56</v>
+      </c>
+      <c r="D215" s="2"/>
+      <c r="E215" s="17"/>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C216" s="2">
+        <v>57</v>
+      </c>
+      <c r="D216" s="2"/>
+      <c r="E216" s="17"/>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A217" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C217" s="2">
+        <v>58</v>
+      </c>
+      <c r="D217" s="2"/>
+      <c r="E217" s="17"/>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A218" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C218" s="2">
+        <v>59</v>
+      </c>
+      <c r="D218" s="2"/>
+      <c r="E218" s="17"/>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A219" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C219" s="2">
+        <v>60</v>
+      </c>
+      <c r="D219" s="2"/>
+      <c r="E219" s="17"/>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A220" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C220" s="2">
+        <v>61</v>
+      </c>
+      <c r="D220" s="2"/>
+      <c r="E220" s="17"/>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A221" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C221" s="2">
+        <v>62</v>
+      </c>
+      <c r="D221" s="2"/>
+      <c r="E221" s="17"/>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C222" s="2">
+        <v>63</v>
+      </c>
+      <c r="D222" s="2"/>
+      <c r="E222" s="17"/>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A223" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C223" s="2">
+        <v>64</v>
+      </c>
+      <c r="D223" s="2"/>
+      <c r="E223" s="17"/>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A224" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C224" s="2">
+        <v>65</v>
+      </c>
+      <c r="D224" s="2"/>
+      <c r="E224" s="17"/>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A225" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C225" s="2">
+        <v>66</v>
+      </c>
+      <c r="D225" s="2"/>
+      <c r="E225" s="17"/>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A226" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C226" s="2">
+        <v>67</v>
+      </c>
+      <c r="D226" s="2"/>
+      <c r="E226" s="17"/>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A227" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C227" s="2">
+        <v>68</v>
+      </c>
+      <c r="D227" s="2"/>
+      <c r="E227" s="17"/>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A228" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C228" s="2">
+        <v>69</v>
+      </c>
+      <c r="D228" s="2"/>
+      <c r="E228" s="17"/>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A229" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C229" s="2">
+        <v>70</v>
+      </c>
+      <c r="D229" s="2"/>
+      <c r="E229" s="17"/>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A230" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C230" s="2">
+        <v>71</v>
+      </c>
+      <c r="D230" s="2"/>
+      <c r="E230" s="17"/>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A231" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C231" s="2">
+        <v>72</v>
+      </c>
+      <c r="D231" s="2"/>
+      <c r="E231" s="17"/>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A232" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C232" s="2">
+        <v>73</v>
+      </c>
+      <c r="D232" s="2"/>
+      <c r="E232" s="17"/>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A233" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C233" s="2">
+        <v>74</v>
+      </c>
+      <c r="D233" s="2"/>
+      <c r="E233" s="17"/>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A234" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C234" s="2">
+        <v>75</v>
+      </c>
+      <c r="D234" s="2"/>
+      <c r="E234" s="17"/>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A235" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C235" s="2">
+        <v>76</v>
+      </c>
+      <c r="D235" s="2"/>
+      <c r="E235" s="17"/>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A236" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C236" s="2">
+        <v>77</v>
+      </c>
+      <c r="D236" s="2"/>
+      <c r="E236" s="17"/>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A237" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B237" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C237" s="9">
+        <v>78</v>
+      </c>
+      <c r="D237" s="9"/>
+      <c r="E237" s="17"/>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A238" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C238" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>135</v>
-      </c>
-      <c r="B161" t="s">
-        <v>137</v>
-      </c>
-      <c r="C161">
+      <c r="D238" s="5"/>
+      <c r="E238" s="17">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A239" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C239" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>135</v>
-      </c>
-      <c r="B162" t="s">
-        <v>138</v>
-      </c>
-      <c r="C162">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>135</v>
-      </c>
-      <c r="B163" t="s">
-        <v>139</v>
-      </c>
-      <c r="C163">
+      <c r="D239" s="2"/>
+      <c r="E239" s="17"/>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A240" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C240" s="2">
+        <v>3</v>
+      </c>
+      <c r="D240" s="2"/>
+      <c r="E240" s="17"/>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A241" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C241" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>135</v>
-      </c>
-      <c r="B164" t="s">
-        <v>140</v>
-      </c>
-      <c r="C164">
+      <c r="D241" s="2"/>
+      <c r="E241" s="17"/>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A242" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C242" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>135</v>
-      </c>
-      <c r="B165" t="s">
-        <v>141</v>
-      </c>
-      <c r="C165">
+      <c r="D242" s="2"/>
+      <c r="E242" s="17"/>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A243" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C243" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>135</v>
-      </c>
-      <c r="B166" t="s">
-        <v>142</v>
-      </c>
-      <c r="C166">
+      <c r="D243" s="2"/>
+      <c r="E243" s="17"/>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A244" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C244" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>135</v>
-      </c>
-      <c r="B167" t="s">
-        <v>143</v>
-      </c>
-      <c r="C167">
+      <c r="D244" s="2"/>
+      <c r="E244" s="17"/>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A245" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C245" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>135</v>
-      </c>
-      <c r="B168" t="s">
-        <v>144</v>
-      </c>
-      <c r="C168">
+      <c r="D245" s="2"/>
+      <c r="E245" s="17"/>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A246" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C246" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>135</v>
-      </c>
-      <c r="B169" t="s">
-        <v>145</v>
-      </c>
-      <c r="C169">
+      <c r="D246" s="2"/>
+      <c r="E246" s="17"/>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A247" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C247" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>135</v>
-      </c>
-      <c r="B170" t="s">
-        <v>146</v>
-      </c>
-      <c r="C170">
+      <c r="D247" s="2"/>
+      <c r="E247" s="17"/>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A248" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C248" s="2">
         <v>11</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>135</v>
-      </c>
-      <c r="B171" t="s">
-        <v>147</v>
-      </c>
-      <c r="C171">
+      <c r="D248" s="2"/>
+      <c r="E248" s="17"/>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A249" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C249" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>135</v>
-      </c>
-      <c r="B172" t="s">
-        <v>148</v>
-      </c>
-      <c r="C172">
+      <c r="D249" s="2"/>
+      <c r="E249" s="17"/>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A250" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C250" s="2">
         <v>13</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>135</v>
-      </c>
-      <c r="B173" t="s">
-        <v>149</v>
-      </c>
-      <c r="C173">
+      <c r="D250" s="2"/>
+      <c r="E250" s="17"/>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A251" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C251" s="2">
         <v>14</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>135</v>
-      </c>
-      <c r="B174" t="s">
-        <v>150</v>
-      </c>
-      <c r="C174">
+      <c r="D251" s="2"/>
+      <c r="E251" s="17"/>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A252" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C252" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>135</v>
-      </c>
-      <c r="B175" t="s">
-        <v>151</v>
-      </c>
-      <c r="C175">
+      <c r="D252" s="2"/>
+      <c r="E252" s="17"/>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A253" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C253" s="2">
         <v>16</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>135</v>
-      </c>
-      <c r="B176" t="s">
-        <v>152</v>
-      </c>
-      <c r="C176">
+      <c r="D253" s="2"/>
+      <c r="E253" s="17"/>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A254" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C254" s="2">
         <v>17</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>135</v>
-      </c>
-      <c r="B177" t="s">
-        <v>153</v>
-      </c>
-      <c r="C177">
+      <c r="D254" s="2"/>
+      <c r="E254" s="17"/>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A255" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C255" s="2">
         <v>18</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
-        <v>135</v>
-      </c>
-      <c r="B178" t="s">
-        <v>154</v>
-      </c>
-      <c r="C178">
+      <c r="D255" s="2"/>
+      <c r="E255" s="17"/>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A256" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C256" s="2">
         <v>19</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
-        <v>135</v>
-      </c>
-      <c r="B179" t="s">
-        <v>155</v>
-      </c>
-      <c r="C179">
+      <c r="D256" s="2"/>
+      <c r="E256" s="17"/>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A257" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C257" s="2">
         <v>20</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>135</v>
-      </c>
-      <c r="B180" t="s">
-        <v>156</v>
-      </c>
-      <c r="C180">
+      <c r="D257" s="2"/>
+      <c r="E257" s="17"/>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A258" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C258" s="2">
         <v>21</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>135</v>
-      </c>
-      <c r="B181" t="s">
-        <v>157</v>
-      </c>
-      <c r="C181">
+      <c r="D258" s="2"/>
+      <c r="E258" s="17"/>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A259" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C259" s="2">
         <v>22</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>135</v>
-      </c>
-      <c r="B182" t="s">
-        <v>158</v>
-      </c>
-      <c r="C182">
+      <c r="D259" s="2"/>
+      <c r="E259" s="17"/>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A260" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C260" s="2">
         <v>23</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>135</v>
-      </c>
-      <c r="B183" t="s">
-        <v>159</v>
-      </c>
-      <c r="C183">
+      <c r="D260" s="2"/>
+      <c r="E260" s="17"/>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A261" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C261" s="2">
         <v>24</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>135</v>
-      </c>
-      <c r="B184" t="s">
-        <v>160</v>
-      </c>
-      <c r="C184">
+      <c r="D261" s="2"/>
+      <c r="E261" s="17"/>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A262" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C262" s="2">
         <v>25</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>135</v>
-      </c>
-      <c r="B185" t="s">
-        <v>161</v>
-      </c>
-      <c r="C185">
+      <c r="D262" s="2"/>
+      <c r="E262" s="17"/>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A263" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C263" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>135</v>
-      </c>
-      <c r="B186" t="s">
-        <v>162</v>
-      </c>
-      <c r="C186">
+      <c r="D263" s="2"/>
+      <c r="E263" s="17"/>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A264" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C264" s="2">
         <v>27</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>135</v>
-      </c>
-      <c r="B187" t="s">
-        <v>163</v>
-      </c>
-      <c r="C187">
+      <c r="D264" s="2"/>
+      <c r="E264" s="17"/>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A265" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C265" s="2">
         <v>28</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>135</v>
-      </c>
-      <c r="B188" t="s">
-        <v>164</v>
-      </c>
-      <c r="C188">
+      <c r="D265" s="2"/>
+      <c r="E265" s="17"/>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A266" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C266" s="2">
         <v>29</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>135</v>
-      </c>
-      <c r="B189" t="s">
-        <v>165</v>
-      </c>
-      <c r="C189">
+      <c r="D266" s="2"/>
+      <c r="E266" s="17"/>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A267" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C267" s="2">
         <v>30</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>135</v>
-      </c>
-      <c r="B190" t="s">
-        <v>166</v>
-      </c>
-      <c r="C190">
+      <c r="D267" s="2"/>
+      <c r="E267" s="17"/>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A268" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C268" s="2">
         <v>31</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>135</v>
-      </c>
-      <c r="B191" t="s">
-        <v>167</v>
-      </c>
-      <c r="C191">
+      <c r="D268" s="2"/>
+      <c r="E268" s="17"/>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A269" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C269" s="2">
         <v>32</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
-        <v>135</v>
-      </c>
-      <c r="B192" t="s">
-        <v>168</v>
-      </c>
-      <c r="C192">
+      <c r="D269" s="2"/>
+      <c r="E269" s="17"/>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A270" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C270" s="2">
         <v>33</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>135</v>
-      </c>
-      <c r="B193" t="s">
-        <v>169</v>
-      </c>
-      <c r="C193">
+      <c r="D270" s="2"/>
+      <c r="E270" s="17"/>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A271" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C271" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>135</v>
-      </c>
-      <c r="B194" t="s">
-        <v>170</v>
-      </c>
-      <c r="C194">
+      <c r="D271" s="2"/>
+      <c r="E271" s="17"/>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A272" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C272" s="2">
         <v>35</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>135</v>
-      </c>
-      <c r="B195" t="s">
-        <v>171</v>
-      </c>
-      <c r="C195">
+      <c r="D272" s="2"/>
+      <c r="E272" s="17"/>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A273" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C273" s="2">
         <v>36</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>135</v>
-      </c>
-      <c r="B196" t="s">
-        <v>172</v>
-      </c>
-      <c r="C196">
+      <c r="D273" s="2"/>
+      <c r="E273" s="17"/>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A274" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C274" s="2">
         <v>37</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>135</v>
-      </c>
-      <c r="B197" t="s">
-        <v>173</v>
-      </c>
-      <c r="C197">
+      <c r="D274" s="2"/>
+      <c r="E274" s="17"/>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A275" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C275" s="2">
         <v>38</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>135</v>
-      </c>
-      <c r="B198" t="s">
-        <v>174</v>
-      </c>
-      <c r="C198">
+      <c r="D275" s="2"/>
+      <c r="E275" s="17"/>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A276" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C276" s="2">
         <v>39</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>135</v>
-      </c>
-      <c r="B199" t="s">
-        <v>175</v>
-      </c>
-      <c r="C199">
+      <c r="D276" s="2"/>
+      <c r="E276" s="17"/>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A277" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C277" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>135</v>
-      </c>
-      <c r="B200" t="s">
-        <v>176</v>
-      </c>
-      <c r="C200">
+      <c r="D277" s="2"/>
+      <c r="E277" s="17"/>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A278" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C278" s="2">
         <v>41</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>135</v>
-      </c>
-      <c r="B201" t="s">
-        <v>177</v>
-      </c>
-      <c r="C201">
+      <c r="D278" s="2"/>
+      <c r="E278" s="17"/>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A279" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C279" s="2">
         <v>42</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>135</v>
-      </c>
-      <c r="B202" t="s">
-        <v>178</v>
-      </c>
-      <c r="C202">
+      <c r="D279" s="2"/>
+      <c r="E279" s="17"/>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A280" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C280" s="2">
         <v>43</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>135</v>
-      </c>
-      <c r="B203" t="s">
-        <v>179</v>
-      </c>
-      <c r="C203">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>135</v>
-      </c>
-      <c r="B204" t="s">
+      <c r="D280" s="2"/>
+      <c r="E280" s="17"/>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A281" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C281" s="2">
+        <v>44</v>
+      </c>
+      <c r="D281" s="2"/>
+      <c r="E281" s="17"/>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A282" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C282" s="2">
+        <v>45</v>
+      </c>
+      <c r="D282" s="2"/>
+      <c r="E282" s="17"/>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A283" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C283" s="2">
+        <v>46</v>
+      </c>
+      <c r="D283" s="2"/>
+      <c r="E283" s="17"/>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A284" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C284" s="2">
+        <v>47</v>
+      </c>
+      <c r="D284" s="2"/>
+      <c r="E284" s="17"/>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A285" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C285" s="2">
+        <v>48</v>
+      </c>
+      <c r="D285" s="2"/>
+      <c r="E285" s="17"/>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A286" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C286" s="2">
+        <v>49</v>
+      </c>
+      <c r="D286" s="2"/>
+      <c r="E286" s="17"/>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A287" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C287" s="2">
+        <v>50</v>
+      </c>
+      <c r="D287" s="2"/>
+      <c r="E287" s="17"/>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A288" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C288" s="2">
+        <v>51</v>
+      </c>
+      <c r="D288" s="2"/>
+      <c r="E288" s="17"/>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A289" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C289" s="2">
+        <v>52</v>
+      </c>
+      <c r="D289" s="2"/>
+      <c r="E289" s="17"/>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A290" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C290" s="2">
+        <v>53</v>
+      </c>
+      <c r="D290" s="2"/>
+      <c r="E290" s="17"/>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A291" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C291" s="2">
+        <v>54</v>
+      </c>
+      <c r="D291" s="2"/>
+      <c r="E291" s="17"/>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A292" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C292" s="2">
+        <v>55</v>
+      </c>
+      <c r="D292" s="2"/>
+      <c r="E292" s="17"/>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A293" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C293" s="2">
+        <v>56</v>
+      </c>
+      <c r="D293" s="2"/>
+      <c r="E293" s="17"/>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A294" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C294" s="2">
+        <v>57</v>
+      </c>
+      <c r="D294" s="2"/>
+      <c r="E294" s="17"/>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A295" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C295" s="2">
+        <v>58</v>
+      </c>
+      <c r="D295" s="2"/>
+      <c r="E295" s="17"/>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A296" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C296" s="2">
+        <v>59</v>
+      </c>
+      <c r="D296" s="2"/>
+      <c r="E296" s="17"/>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A297" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C297" s="2">
+        <v>60</v>
+      </c>
+      <c r="D297" s="2"/>
+      <c r="E297" s="17"/>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A298" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C298" s="2">
+        <v>61</v>
+      </c>
+      <c r="D298" s="2"/>
+      <c r="E298" s="17"/>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A299" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C299" s="2">
+        <v>62</v>
+      </c>
+      <c r="D299" s="2"/>
+      <c r="E299" s="17"/>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A300" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C300" s="2">
+        <v>63</v>
+      </c>
+      <c r="D300" s="2"/>
+      <c r="E300" s="17"/>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A301" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C301" s="2">
+        <v>64</v>
+      </c>
+      <c r="D301" s="2"/>
+      <c r="E301" s="17"/>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A302" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C302" s="2">
+        <v>65</v>
+      </c>
+      <c r="D302" s="2"/>
+      <c r="E302" s="17"/>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A303" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C303" s="2">
+        <v>66</v>
+      </c>
+      <c r="D303" s="2"/>
+      <c r="E303" s="17"/>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A304" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C304" s="2">
+        <v>67</v>
+      </c>
+      <c r="D304" s="2"/>
+      <c r="E304" s="17"/>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A305" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C305" s="2">
+        <v>68</v>
+      </c>
+      <c r="D305" s="2"/>
+      <c r="E305" s="17"/>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A306" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C306" s="2">
+        <v>69</v>
+      </c>
+      <c r="D306" s="2"/>
+      <c r="E306" s="17"/>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A307" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C307" s="2">
+        <v>70</v>
+      </c>
+      <c r="D307" s="2"/>
+      <c r="E307" s="17"/>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A308" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C308" s="2">
+        <v>71</v>
+      </c>
+      <c r="D308" s="2"/>
+      <c r="E308" s="17"/>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A309" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C309" s="2">
+        <v>72</v>
+      </c>
+      <c r="D309" s="2"/>
+      <c r="E309" s="17"/>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A310" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="B310" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="C310" s="9">
+        <v>73</v>
+      </c>
+      <c r="D310" s="9"/>
+      <c r="E310" s="17"/>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A311" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B311" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C311" s="5">
+        <v>1</v>
+      </c>
+      <c r="D311" s="5"/>
+      <c r="E311" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A312" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C312" s="2">
+        <v>2</v>
+      </c>
+      <c r="D312" s="2"/>
+      <c r="E312" s="17"/>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A313" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="B313" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C313" s="3">
+        <v>3</v>
+      </c>
+      <c r="D313" s="2">
+        <v>3</v>
+      </c>
+      <c r="E313" s="17"/>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A314" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="B314" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C314" s="3">
+        <v>4</v>
+      </c>
+      <c r="D314" s="2">
+        <v>3</v>
+      </c>
+      <c r="E314" s="17"/>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A315" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="B315" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C315" s="3">
+        <v>5</v>
+      </c>
+      <c r="D315" s="2">
+        <v>3</v>
+      </c>
+      <c r="E315" s="17"/>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A316" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="B316" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="C316" s="9">
+        <v>6</v>
+      </c>
+      <c r="D316" s="9">
+        <v>6</v>
+      </c>
+      <c r="E316" s="17"/>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A317" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B317" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="C317" s="6">
+        <v>1</v>
+      </c>
+      <c r="D317" s="5">
+        <v>1</v>
+      </c>
+      <c r="E317" s="17">
+        <v>6</v>
+      </c>
+      <c r="F317" s="7">
+        <v>3</v>
+      </c>
+      <c r="G317" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A318" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="B318" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C318" s="3">
+        <v>2</v>
+      </c>
+      <c r="D318" s="18">
+        <v>2</v>
+      </c>
+      <c r="E318" s="17"/>
+      <c r="F318" s="7">
+        <v>55</v>
+      </c>
+      <c r="G318" s="20">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A319" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="B319" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C319" s="3">
+        <v>3</v>
+      </c>
+      <c r="D319" s="18">
+        <v>2</v>
+      </c>
+      <c r="E319" s="17"/>
+      <c r="F319" s="7">
+        <v>50</v>
+      </c>
+      <c r="G319" s="20"/>
+    </row>
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A320" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="B320" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C320" s="3">
+        <v>4</v>
+      </c>
+      <c r="D320" s="18">
+        <v>4</v>
+      </c>
+      <c r="E320" s="17"/>
+      <c r="F320" s="7">
         <v>180</v>
       </c>
-      <c r="C204">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>135</v>
-      </c>
-      <c r="B205" t="s">
-        <v>181</v>
-      </c>
-      <c r="C205">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
-        <v>135</v>
-      </c>
-      <c r="B206" t="s">
-        <v>182</v>
-      </c>
-      <c r="C206">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
-        <v>135</v>
-      </c>
-      <c r="B207" t="s">
-        <v>183</v>
-      </c>
-      <c r="C207">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
-        <v>135</v>
-      </c>
-      <c r="B208" t="s">
-        <v>184</v>
-      </c>
-      <c r="C208">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
-        <v>135</v>
-      </c>
-      <c r="B209" t="s">
+      <c r="G320" s="20">
         <v>185</v>
       </c>
-      <c r="C209">
+    </row>
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A321" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="B321" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C321" s="3">
+        <v>5</v>
+      </c>
+      <c r="D321" s="18">
+        <v>4</v>
+      </c>
+      <c r="E321" s="17"/>
+      <c r="F321" s="7">
+        <v>3</v>
+      </c>
+      <c r="G321" s="20"/>
+    </row>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A322" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C322" s="2">
+        <v>6</v>
+      </c>
+      <c r="D322" s="18">
+        <v>6</v>
+      </c>
+      <c r="E322" s="17"/>
+      <c r="F322" s="7">
+        <v>30</v>
+      </c>
+      <c r="G322" s="18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A323" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="B323" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C323" s="3">
+        <v>7</v>
+      </c>
+      <c r="D323" s="18">
+        <v>1</v>
+      </c>
+      <c r="E323" s="17"/>
+      <c r="F323" s="7">
+        <v>75</v>
+      </c>
+      <c r="G323" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A324" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C324" s="2">
+        <v>8</v>
+      </c>
+      <c r="D324" s="18">
+        <v>8</v>
+      </c>
+      <c r="E324" s="17"/>
+      <c r="F324" s="7">
         <v>50</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
-        <v>135</v>
-      </c>
-      <c r="B210" t="s">
-        <v>186</v>
-      </c>
-      <c r="C210">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>135</v>
-      </c>
-      <c r="B211" t="s">
-        <v>187</v>
-      </c>
-      <c r="C211">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
-        <v>135</v>
-      </c>
-      <c r="B212" t="s">
-        <v>188</v>
-      </c>
-      <c r="C212">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>135</v>
-      </c>
-      <c r="B213" t="s">
-        <v>189</v>
-      </c>
-      <c r="C213">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>135</v>
-      </c>
-      <c r="B214" t="s">
-        <v>190</v>
-      </c>
-      <c r="C214">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
-        <v>135</v>
-      </c>
-      <c r="B215" t="s">
-        <v>191</v>
-      </c>
-      <c r="C215">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>135</v>
-      </c>
-      <c r="B216" t="s">
-        <v>192</v>
-      </c>
-      <c r="C216">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>135</v>
-      </c>
-      <c r="B217" t="s">
-        <v>193</v>
-      </c>
-      <c r="C217">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>135</v>
-      </c>
-      <c r="B218" t="s">
-        <v>194</v>
-      </c>
-      <c r="C218">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
-        <v>135</v>
-      </c>
-      <c r="B219" t="s">
-        <v>195</v>
-      </c>
-      <c r="C219">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>135</v>
-      </c>
-      <c r="B220" t="s">
-        <v>196</v>
-      </c>
-      <c r="C220">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>135</v>
-      </c>
-      <c r="B221" t="s">
-        <v>197</v>
-      </c>
-      <c r="C221">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>135</v>
-      </c>
-      <c r="B222" t="s">
-        <v>198</v>
-      </c>
-      <c r="C222">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>135</v>
-      </c>
-      <c r="B223" t="s">
-        <v>199</v>
-      </c>
-      <c r="C223">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>135</v>
-      </c>
-      <c r="B224" t="s">
-        <v>200</v>
-      </c>
-      <c r="C224">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
-        <v>135</v>
-      </c>
-      <c r="B225" t="s">
-        <v>201</v>
-      </c>
-      <c r="C225">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
-        <v>135</v>
-      </c>
-      <c r="B226" t="s">
-        <v>202</v>
-      </c>
-      <c r="C226">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
-        <v>135</v>
-      </c>
-      <c r="B227" t="s">
-        <v>203</v>
-      </c>
-      <c r="C227">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
-        <v>135</v>
-      </c>
-      <c r="B228" t="s">
-        <v>204</v>
-      </c>
-      <c r="C228">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
-        <v>135</v>
-      </c>
-      <c r="B229" t="s">
-        <v>205</v>
-      </c>
-      <c r="C229">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
-        <v>135</v>
-      </c>
-      <c r="B230" t="s">
-        <v>206</v>
-      </c>
-      <c r="C230">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
-        <v>135</v>
-      </c>
-      <c r="B231" t="s">
-        <v>207</v>
-      </c>
-      <c r="C231">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
-        <v>135</v>
-      </c>
-      <c r="B232" t="s">
-        <v>208</v>
-      </c>
-      <c r="C232">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
-        <v>135</v>
-      </c>
-      <c r="B233" t="s">
-        <v>209</v>
-      </c>
-      <c r="C233">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
-        <v>135</v>
-      </c>
-      <c r="B234" t="s">
-        <v>210</v>
-      </c>
-      <c r="C234">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
-        <v>135</v>
-      </c>
-      <c r="B235" t="s">
-        <v>211</v>
-      </c>
-      <c r="C235">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
-        <v>135</v>
-      </c>
-      <c r="B236" t="s">
-        <v>212</v>
-      </c>
-      <c r="C236">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
-        <v>135</v>
-      </c>
-      <c r="B237" t="s">
-        <v>213</v>
-      </c>
-      <c r="C237">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A238" t="s">
-        <v>214</v>
-      </c>
-      <c r="B238" t="s">
-        <v>215</v>
-      </c>
-      <c r="C238">
+      <c r="G324" s="18">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A325" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B325" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C325" s="9">
+        <v>9</v>
+      </c>
+      <c r="D325" s="9">
+        <v>9</v>
+      </c>
+      <c r="E325" s="17"/>
+      <c r="F325" s="7">
+        <v>3</v>
+      </c>
+      <c r="G325" s="18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A326" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B326" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="C326" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A239" t="s">
-        <v>214</v>
-      </c>
-      <c r="B239" t="s">
-        <v>216</v>
-      </c>
-      <c r="C239">
+      <c r="D326" s="18">
+        <v>1</v>
+      </c>
+      <c r="E326" s="17">
+        <v>6</v>
+      </c>
+      <c r="G326" s="2">
+        <f>SUM(G317:G325)</f>
+        <v>483</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A327" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="B327" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C327" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A240" t="s">
-        <v>214</v>
-      </c>
-      <c r="B240" t="s">
-        <v>217</v>
-      </c>
-      <c r="C240">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
-        <v>214</v>
-      </c>
-      <c r="B241" t="s">
-        <v>218</v>
-      </c>
-      <c r="C241">
+      <c r="D327" s="18">
+        <v>2</v>
+      </c>
+      <c r="E327" s="17"/>
+    </row>
+    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A328" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="B328" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C328" s="2">
+        <v>3</v>
+      </c>
+      <c r="D328" s="18">
+        <v>3</v>
+      </c>
+      <c r="E328" s="17"/>
+    </row>
+    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A329" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C329" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
-        <v>214</v>
-      </c>
-      <c r="B242" t="s">
-        <v>219</v>
-      </c>
-      <c r="C242">
+      <c r="D329" s="18">
+        <v>4</v>
+      </c>
+      <c r="E329" s="17"/>
+    </row>
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A330" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C330" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
-        <v>214</v>
-      </c>
-      <c r="B243" t="s">
-        <v>105</v>
-      </c>
-      <c r="C243">
+      <c r="D330" s="18">
+        <v>5</v>
+      </c>
+      <c r="E330" s="17"/>
+    </row>
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A331" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="B331" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C331" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
-        <v>214</v>
-      </c>
-      <c r="B244" t="s">
-        <v>220</v>
-      </c>
-      <c r="C244">
+      <c r="D331" s="18">
+        <v>6</v>
+      </c>
+      <c r="E331" s="17"/>
+    </row>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A332" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="B332" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="C332" s="10">
         <v>7</v>
       </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A245" t="s">
-        <v>214</v>
-      </c>
-      <c r="B245" t="s">
-        <v>221</v>
-      </c>
-      <c r="C245">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
-        <v>214</v>
-      </c>
-      <c r="B246" t="s">
-        <v>222</v>
-      </c>
-      <c r="C246">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A247" t="s">
-        <v>214</v>
-      </c>
-      <c r="B247" t="s">
-        <v>223</v>
-      </c>
-      <c r="C247">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
-        <v>214</v>
-      </c>
-      <c r="B248" t="s">
-        <v>224</v>
-      </c>
-      <c r="C248">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A249" t="s">
-        <v>214</v>
-      </c>
-      <c r="B249" t="s">
-        <v>225</v>
-      </c>
-      <c r="C249">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A250" t="s">
-        <v>214</v>
-      </c>
-      <c r="B250" t="s">
-        <v>226</v>
-      </c>
-      <c r="C250">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
-        <v>214</v>
-      </c>
-      <c r="B251" t="s">
-        <v>227</v>
-      </c>
-      <c r="C251">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A252" t="s">
-        <v>214</v>
-      </c>
-      <c r="B252" t="s">
-        <v>228</v>
-      </c>
-      <c r="C252">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
-        <v>214</v>
-      </c>
-      <c r="B253" t="s">
-        <v>229</v>
-      </c>
-      <c r="C253">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
-        <v>214</v>
-      </c>
-      <c r="B254" t="s">
-        <v>230</v>
-      </c>
-      <c r="C254">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
-        <v>214</v>
-      </c>
-      <c r="B255" t="s">
-        <v>231</v>
-      </c>
-      <c r="C255">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
-        <v>214</v>
-      </c>
-      <c r="B256" t="s">
-        <v>232</v>
-      </c>
-      <c r="C256">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
-        <v>214</v>
-      </c>
-      <c r="B257" t="s">
-        <v>233</v>
-      </c>
-      <c r="C257">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A258" t="s">
-        <v>214</v>
-      </c>
-      <c r="B258" t="s">
-        <v>234</v>
-      </c>
-      <c r="C258">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A259" t="s">
-        <v>214</v>
-      </c>
-      <c r="B259" t="s">
-        <v>235</v>
-      </c>
-      <c r="C259">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A260" t="s">
-        <v>214</v>
-      </c>
-      <c r="B260" t="s">
-        <v>236</v>
-      </c>
-      <c r="C260">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
-        <v>214</v>
-      </c>
-      <c r="B261" t="s">
-        <v>237</v>
-      </c>
-      <c r="C261">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A262" t="s">
-        <v>214</v>
-      </c>
-      <c r="B262" t="s">
-        <v>238</v>
-      </c>
-      <c r="C262">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A263" t="s">
-        <v>214</v>
-      </c>
-      <c r="B263" t="s">
-        <v>239</v>
-      </c>
-      <c r="C263">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A264" t="s">
-        <v>214</v>
-      </c>
-      <c r="B264" t="s">
-        <v>113</v>
-      </c>
-      <c r="C264">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
-        <v>214</v>
-      </c>
-      <c r="B265" t="s">
-        <v>240</v>
-      </c>
-      <c r="C265">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
-        <v>214</v>
-      </c>
-      <c r="B266" t="s">
-        <v>241</v>
-      </c>
-      <c r="C266">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A267" t="s">
-        <v>214</v>
-      </c>
-      <c r="B267" t="s">
-        <v>242</v>
-      </c>
-      <c r="C267">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A268" t="s">
-        <v>214</v>
-      </c>
-      <c r="B268" t="s">
-        <v>114</v>
-      </c>
-      <c r="C268">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A269" t="s">
-        <v>214</v>
-      </c>
-      <c r="B269" t="s">
-        <v>243</v>
-      </c>
-      <c r="C269">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A270" t="s">
-        <v>214</v>
-      </c>
-      <c r="B270" t="s">
-        <v>244</v>
-      </c>
-      <c r="C270">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A271" t="s">
-        <v>214</v>
-      </c>
-      <c r="B271" t="s">
-        <v>245</v>
-      </c>
-      <c r="C271">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A272" t="s">
-        <v>214</v>
-      </c>
-      <c r="B272" t="s">
-        <v>115</v>
-      </c>
-      <c r="C272">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
-        <v>214</v>
-      </c>
-      <c r="B273" t="s">
-        <v>246</v>
-      </c>
-      <c r="C273">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A274" t="s">
-        <v>214</v>
-      </c>
-      <c r="B274" t="s">
-        <v>247</v>
-      </c>
-      <c r="C274">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A275" t="s">
-        <v>214</v>
-      </c>
-      <c r="B275" t="s">
-        <v>118</v>
-      </c>
-      <c r="C275">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
-        <v>214</v>
-      </c>
-      <c r="B276" t="s">
-        <v>121</v>
-      </c>
-      <c r="C276">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A277" t="s">
-        <v>214</v>
-      </c>
-      <c r="B277" t="s">
-        <v>248</v>
-      </c>
-      <c r="C277">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A278" t="s">
-        <v>214</v>
-      </c>
-      <c r="B278" t="s">
-        <v>249</v>
-      </c>
-      <c r="C278">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A279" t="s">
-        <v>214</v>
-      </c>
-      <c r="B279" t="s">
-        <v>250</v>
-      </c>
-      <c r="C279">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A280" t="s">
-        <v>214</v>
-      </c>
-      <c r="B280" t="s">
-        <v>251</v>
-      </c>
-      <c r="C280">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A281" t="s">
-        <v>214</v>
-      </c>
-      <c r="B281" t="s">
-        <v>252</v>
-      </c>
-      <c r="C281">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A282" t="s">
-        <v>214</v>
-      </c>
-      <c r="B282" t="s">
-        <v>253</v>
-      </c>
-      <c r="C282">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A283" t="s">
-        <v>214</v>
-      </c>
-      <c r="B283" t="s">
-        <v>254</v>
-      </c>
-      <c r="C283">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A284" t="s">
-        <v>214</v>
-      </c>
-      <c r="B284" t="s">
-        <v>255</v>
-      </c>
-      <c r="C284">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A285" t="s">
-        <v>214</v>
-      </c>
-      <c r="B285" t="s">
-        <v>256</v>
-      </c>
-      <c r="C285">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A286" t="s">
-        <v>214</v>
-      </c>
-      <c r="B286" t="s">
-        <v>126</v>
-      </c>
-      <c r="C286">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A287" t="s">
-        <v>214</v>
-      </c>
-      <c r="B287" t="s">
-        <v>257</v>
-      </c>
-      <c r="C287">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A288" t="s">
-        <v>214</v>
-      </c>
-      <c r="B288" t="s">
-        <v>127</v>
-      </c>
-      <c r="C288">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A289" t="s">
-        <v>214</v>
-      </c>
-      <c r="B289" t="s">
-        <v>258</v>
-      </c>
-      <c r="C289">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A290" t="s">
-        <v>214</v>
-      </c>
-      <c r="B290" t="s">
-        <v>259</v>
-      </c>
-      <c r="C290">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A291" t="s">
-        <v>214</v>
-      </c>
-      <c r="B291" t="s">
-        <v>260</v>
-      </c>
-      <c r="C291">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A292" t="s">
-        <v>214</v>
-      </c>
-      <c r="B292" t="s">
-        <v>261</v>
-      </c>
-      <c r="C292">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A293" t="s">
-        <v>214</v>
-      </c>
-      <c r="B293" t="s">
-        <v>262</v>
-      </c>
-      <c r="C293">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A294" t="s">
-        <v>214</v>
-      </c>
-      <c r="B294" t="s">
-        <v>263</v>
-      </c>
-      <c r="C294">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A295" t="s">
-        <v>214</v>
-      </c>
-      <c r="B295" t="s">
-        <v>264</v>
-      </c>
-      <c r="C295">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A296" t="s">
-        <v>214</v>
-      </c>
-      <c r="B296" t="s">
-        <v>265</v>
-      </c>
-      <c r="C296">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
-        <v>214</v>
-      </c>
-      <c r="B297" t="s">
-        <v>266</v>
-      </c>
-      <c r="C297">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A298" t="s">
-        <v>214</v>
-      </c>
-      <c r="B298" t="s">
-        <v>267</v>
-      </c>
-      <c r="C298">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A299" t="s">
-        <v>214</v>
-      </c>
-      <c r="B299" t="s">
-        <v>268</v>
-      </c>
-      <c r="C299">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A300" t="s">
-        <v>214</v>
-      </c>
-      <c r="B300" t="s">
-        <v>269</v>
-      </c>
-      <c r="C300">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A301" t="s">
-        <v>214</v>
-      </c>
-      <c r="B301" t="s">
-        <v>270</v>
-      </c>
-      <c r="C301">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A302" t="s">
-        <v>214</v>
-      </c>
-      <c r="B302" t="s">
-        <v>271</v>
-      </c>
-      <c r="C302">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
-        <v>214</v>
-      </c>
-      <c r="B303" t="s">
-        <v>272</v>
-      </c>
-      <c r="C303">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A304" t="s">
-        <v>214</v>
-      </c>
-      <c r="B304" t="s">
-        <v>273</v>
-      </c>
-      <c r="C304">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A305" t="s">
-        <v>214</v>
-      </c>
-      <c r="B305" t="s">
-        <v>274</v>
-      </c>
-      <c r="C305">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
-        <v>214</v>
-      </c>
-      <c r="B306" t="s">
-        <v>275</v>
-      </c>
-      <c r="C306">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
-        <v>214</v>
-      </c>
-      <c r="B307" t="s">
-        <v>276</v>
-      </c>
-      <c r="C307">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
-        <v>214</v>
-      </c>
-      <c r="B308" t="s">
-        <v>277</v>
-      </c>
-      <c r="C308">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A309" t="s">
-        <v>214</v>
-      </c>
-      <c r="B309" t="s">
-        <v>278</v>
-      </c>
-      <c r="C309">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A310" t="s">
-        <v>214</v>
-      </c>
-      <c r="B310" t="s">
-        <v>279</v>
-      </c>
-      <c r="C310">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A311" t="s">
-        <v>280</v>
-      </c>
-      <c r="B311" t="s">
-        <v>281</v>
-      </c>
-      <c r="C311">
+      <c r="D332" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A312" t="s">
-        <v>280</v>
-      </c>
-      <c r="B312" t="s">
-        <v>282</v>
-      </c>
-      <c r="C312">
+      <c r="E332" s="17"/>
+    </row>
+    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A333" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B333" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C333" s="6">
+        <v>1</v>
+      </c>
+      <c r="D333" s="5">
+        <v>1</v>
+      </c>
+      <c r="E333" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A334" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B334" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C334" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A313" t="s">
-        <v>280</v>
-      </c>
-      <c r="B313" t="s">
-        <v>283</v>
-      </c>
-      <c r="C313">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A314" t="s">
-        <v>280</v>
-      </c>
-      <c r="B314" t="s">
-        <v>284</v>
-      </c>
-      <c r="C314">
+      <c r="D334" s="2">
+        <v>1</v>
+      </c>
+      <c r="E334" s="17"/>
+    </row>
+    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A335" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C335" s="2">
+        <v>3</v>
+      </c>
+      <c r="D335" s="2">
+        <v>3</v>
+      </c>
+      <c r="E335" s="17"/>
+    </row>
+    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A336" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="B336" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="C336" s="9">
         <v>4</v>
       </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A315" t="s">
-        <v>280</v>
-      </c>
-      <c r="B315" t="s">
-        <v>285</v>
-      </c>
-      <c r="C315">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A316" t="s">
-        <v>280</v>
-      </c>
-      <c r="B316" t="s">
-        <v>286</v>
-      </c>
-      <c r="C316">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A317" t="s">
-        <v>287</v>
-      </c>
-      <c r="B317" t="s">
-        <v>288</v>
-      </c>
-      <c r="C317">
+      <c r="D336" s="9">
+        <v>4</v>
+      </c>
+      <c r="E336" s="17"/>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A337" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B337" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C337" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A318" t="s">
-        <v>287</v>
-      </c>
-      <c r="B318" t="s">
-        <v>289</v>
-      </c>
-      <c r="C318">
+      <c r="D337" s="5"/>
+      <c r="E337" s="15">
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A319" t="s">
-        <v>287</v>
-      </c>
-      <c r="B319" t="s">
-        <v>290</v>
-      </c>
-      <c r="C319">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A320" t="s">
-        <v>287</v>
-      </c>
-      <c r="B320" t="s">
-        <v>291</v>
-      </c>
-      <c r="C320">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A321" t="s">
-        <v>287</v>
-      </c>
-      <c r="B321" t="s">
-        <v>292</v>
-      </c>
-      <c r="C321">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A322" t="s">
-        <v>287</v>
-      </c>
-      <c r="B322" t="s">
-        <v>293</v>
-      </c>
-      <c r="C322">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A323" t="s">
-        <v>287</v>
-      </c>
-      <c r="B323" t="s">
-        <v>294</v>
-      </c>
-      <c r="C323">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A324" t="s">
-        <v>287</v>
-      </c>
-      <c r="B324" t="s">
-        <v>295</v>
-      </c>
-      <c r="C324">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A325" t="s">
-        <v>287</v>
-      </c>
-      <c r="B325" t="s">
-        <v>296</v>
-      </c>
-      <c r="C325">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A326" t="s">
-        <v>297</v>
-      </c>
-      <c r="B326" t="s">
-        <v>298</v>
-      </c>
-      <c r="C326">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A327" t="s">
-        <v>297</v>
-      </c>
-      <c r="B327" t="s">
-        <v>299</v>
-      </c>
-      <c r="C327">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A338" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="B338" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="C338" s="9">
         <v>2</v>
       </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A328" t="s">
-        <v>297</v>
-      </c>
-      <c r="B328" t="s">
-        <v>300</v>
-      </c>
-      <c r="C328">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A329" t="s">
-        <v>297</v>
-      </c>
-      <c r="B329" t="s">
-        <v>301</v>
-      </c>
-      <c r="C329">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A330" t="s">
-        <v>297</v>
-      </c>
-      <c r="B330" t="s">
-        <v>302</v>
-      </c>
-      <c r="C330">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A331" t="s">
-        <v>297</v>
-      </c>
-      <c r="B331" t="s">
-        <v>303</v>
-      </c>
-      <c r="C331">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A332" t="s">
-        <v>297</v>
-      </c>
-      <c r="B332" t="s">
-        <v>304</v>
-      </c>
-      <c r="C332">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A333" t="s">
-        <v>305</v>
-      </c>
-      <c r="B333" t="s">
-        <v>306</v>
-      </c>
-      <c r="C333">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A334" t="s">
-        <v>305</v>
-      </c>
-      <c r="B334" t="s">
-        <v>307</v>
-      </c>
-      <c r="C334">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A335" t="s">
-        <v>305</v>
-      </c>
-      <c r="B335" t="s">
-        <v>308</v>
-      </c>
-      <c r="C335">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A336" t="s">
-        <v>305</v>
-      </c>
-      <c r="B336" t="s">
-        <v>309</v>
-      </c>
-      <c r="C336">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A337" t="s">
-        <v>310</v>
-      </c>
-      <c r="B337" t="s">
-        <v>311</v>
-      </c>
-      <c r="C337">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A338" t="s">
-        <v>310</v>
-      </c>
-      <c r="B338" t="s">
-        <v>309</v>
-      </c>
-      <c r="C338">
-        <v>2</v>
-      </c>
+      <c r="D338" s="9"/>
+      <c r="E338" s="15"/>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E339" s="2"/>
+      <c r="F339" s="2"/>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E340" s="2"/>
+      <c r="F340" s="2"/>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E341" s="2"/>
+      <c r="F341" s="2"/>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E342" s="2"/>
+      <c r="F342" s="2"/>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E343" s="2"/>
+      <c r="F343" s="2"/>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E344" s="2"/>
+      <c r="F344" s="2"/>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E345" s="2"/>
+      <c r="F345" s="2"/>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E346" s="2"/>
+      <c r="F346" s="2"/>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E347" s="2"/>
+      <c r="F347" s="2"/>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E348" s="2"/>
+      <c r="F348" s="2"/>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E349" s="2"/>
+      <c r="F349" s="2"/>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E350" s="2"/>
+      <c r="F350" s="2"/>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E351" s="2"/>
+      <c r="F351" s="2"/>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E352" s="2"/>
+      <c r="F352" s="2"/>
+    </row>
+    <row r="353" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E353" s="2"/>
+      <c r="F353" s="2"/>
+    </row>
+    <row r="354" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E354" s="8"/>
     </row>
   </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G318:G319"/>
+    <mergeCell ref="G320:G321"/>
+    <mergeCell ref="F129:F159"/>
+    <mergeCell ref="F122:F128"/>
+    <mergeCell ref="F119:F121"/>
+    <mergeCell ref="E238:E310"/>
+    <mergeCell ref="E160:E237"/>
+    <mergeCell ref="E122:E128"/>
+    <mergeCell ref="E119:E121"/>
+    <mergeCell ref="E129:E159"/>
+    <mergeCell ref="E326:E332"/>
+    <mergeCell ref="E317:E325"/>
+    <mergeCell ref="E333:E336"/>
+    <mergeCell ref="E337:E338"/>
+    <mergeCell ref="E311:E316"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data_exploration/Encoding/categorical_value_mapping.xlsx
+++ b/data_exploration/Encoding/categorical_value_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\Documents\GitHub Repository\Patient_Feedback\data_exploration\Encoding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25551D3-C813-4ECA-8A9A-5BD977350CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204A4225-78C6-4803-AA30-D087CCAF30D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="321">
   <si>
     <t>Column</t>
   </si>
@@ -998,6 +998,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -1139,13 +1142,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1153,31 +1155,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1482,16 +1482,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H354"/>
+  <dimension ref="A1:I354"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="78.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="7"/>
-    <col min="7" max="7" width="13.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="2"/>
+    <col min="5" max="5" width="11" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="6"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1504,14 +1504,12 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>312</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -1523,10 +1521,10 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="H2" s="21"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -1538,10 +1536,10 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="13" t="s">
         <v>316</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="13" t="s">
         <v>317</v>
       </c>
     </row>
@@ -1555,10 +1553,10 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="H4" s="22"/>
+      <c r="H4" s="11"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -1570,10 +1568,10 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="13">
         <v>7</v>
       </c>
-      <c r="H5" s="23">
+      <c r="H5" s="13">
         <v>6</v>
       </c>
     </row>
@@ -1587,10 +1585,10 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="13">
         <v>17</v>
       </c>
-      <c r="H6" s="23">
+      <c r="H6" s="13">
         <v>16</v>
       </c>
     </row>
@@ -1604,10 +1602,10 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="13">
         <v>20</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="13">
         <v>19</v>
       </c>
     </row>
@@ -1621,10 +1619,10 @@
       <c r="C8">
         <v>7</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="13">
         <v>25</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="13">
         <v>1</v>
       </c>
     </row>
@@ -1638,10 +1636,10 @@
       <c r="C9">
         <v>8</v>
       </c>
-      <c r="G9" s="22" t="s">
+      <c r="G9" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="H9" s="22"/>
+      <c r="H9" s="11"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -1653,10 +1651,10 @@
       <c r="C10">
         <v>9</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="13">
         <v>4</v>
       </c>
-      <c r="H10" s="23">
+      <c r="H10" s="13">
         <v>3</v>
       </c>
     </row>
@@ -1670,10 +1668,10 @@
       <c r="C11">
         <v>10</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="13">
         <v>5</v>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="13">
         <v>3</v>
       </c>
     </row>
@@ -1687,10 +1685,10 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="H12" s="22"/>
+      <c r="H12" s="11"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -1702,10 +1700,10 @@
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="G13" s="23">
-        <v>3</v>
-      </c>
-      <c r="H13" s="23">
+      <c r="G13" s="13">
+        <v>3</v>
+      </c>
+      <c r="H13" s="13">
         <v>2</v>
       </c>
     </row>
@@ -1719,10 +1717,10 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="13">
         <v>5</v>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="13">
         <v>4</v>
       </c>
     </row>
@@ -1736,10 +1734,10 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="13">
         <v>7</v>
       </c>
-      <c r="H15" s="23">
+      <c r="H15" s="13">
         <v>1</v>
       </c>
     </row>
@@ -1753,10 +1751,10 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="H16" s="13"/>
+      <c r="H16" s="11"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -1768,10 +1766,10 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="13">
         <v>2</v>
       </c>
-      <c r="H17" s="23">
+      <c r="H17" s="13">
         <v>1</v>
       </c>
     </row>
@@ -1785,10 +1783,10 @@
       <c r="C18">
         <v>17</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="H18" s="13"/>
+      <c r="H18" s="11"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -1800,10 +1798,10 @@
       <c r="C19">
         <v>18</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="13">
         <v>7</v>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="13">
         <v>1</v>
       </c>
     </row>
@@ -2895,3198 +2893,3062 @@
       <c r="C118">
         <v>1</v>
       </c>
-      <c r="E118" s="4"/>
+      <c r="E118" s="3"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="4" t="s">
+      <c r="A119" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B119" s="5" t="s">
+      <c r="B119" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C119" s="5">
+      <c r="C119" s="4">
         <v>1</v>
       </c>
-      <c r="D119" s="5"/>
-      <c r="E119" s="15">
-        <v>3</v>
-      </c>
-      <c r="F119" s="12"/>
+      <c r="D119" s="4"/>
+      <c r="E119" s="20">
+        <v>3</v>
+      </c>
+      <c r="F119" s="18"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" s="7" t="s">
+      <c r="A120" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="B120" t="s">
         <v>93</v>
       </c>
-      <c r="C120" s="2">
+      <c r="C120">
         <v>2</v>
       </c>
-      <c r="D120" s="2"/>
-      <c r="E120" s="15"/>
-      <c r="F120" s="12"/>
+      <c r="E120" s="20"/>
+      <c r="F120" s="18"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="8" t="s">
+      <c r="A121" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B121" s="9" t="s">
+      <c r="B121" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C121" s="9">
-        <v>3</v>
-      </c>
-      <c r="D121" s="9"/>
-      <c r="E121" s="15"/>
-      <c r="F121" s="12"/>
+      <c r="C121" s="8">
+        <v>3</v>
+      </c>
+      <c r="D121" s="8"/>
+      <c r="E121" s="20"/>
+      <c r="F121" s="18"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="4" t="s">
+      <c r="A122" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B122" s="5" t="s">
+      <c r="B122" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C122" s="5">
+      <c r="C122" s="4">
         <v>1</v>
       </c>
-      <c r="D122" s="5"/>
-      <c r="E122" s="17">
+      <c r="D122" s="4"/>
+      <c r="E122" s="19">
         <v>7</v>
       </c>
-      <c r="F122" s="12"/>
+      <c r="F122" s="18"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="7" t="s">
+      <c r="A123" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B123" t="s">
         <v>97</v>
       </c>
-      <c r="C123" s="2">
+      <c r="C123">
         <v>2</v>
       </c>
-      <c r="D123" s="2"/>
-      <c r="E123" s="17"/>
-      <c r="F123" s="12"/>
+      <c r="E123" s="19"/>
+      <c r="F123" s="18"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="7" t="s">
+      <c r="A124" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B124" t="s">
         <v>98</v>
       </c>
-      <c r="C124" s="2">
-        <v>3</v>
-      </c>
-      <c r="D124" s="2"/>
-      <c r="E124" s="17"/>
-      <c r="F124" s="12"/>
+      <c r="C124">
+        <v>3</v>
+      </c>
+      <c r="E124" s="19"/>
+      <c r="F124" s="18"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="7" t="s">
+      <c r="A125" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="B125" t="s">
         <v>99</v>
       </c>
-      <c r="C125" s="2">
+      <c r="C125">
         <v>4</v>
       </c>
-      <c r="D125" s="2"/>
-      <c r="E125" s="17"/>
-      <c r="F125" s="12"/>
+      <c r="E125" s="19"/>
+      <c r="F125" s="18"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="7" t="s">
+      <c r="A126" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="B126" t="s">
         <v>100</v>
       </c>
-      <c r="C126" s="2">
+      <c r="C126">
         <v>5</v>
       </c>
-      <c r="D126" s="2"/>
-      <c r="E126" s="17"/>
-      <c r="F126" s="12"/>
+      <c r="E126" s="19"/>
+      <c r="F126" s="18"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" s="7" t="s">
+      <c r="A127" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="B127" t="s">
         <v>101</v>
       </c>
-      <c r="C127" s="2">
+      <c r="C127">
         <v>6</v>
       </c>
-      <c r="D127" s="2"/>
-      <c r="E127" s="17"/>
-      <c r="F127" s="12"/>
+      <c r="E127" s="19"/>
+      <c r="F127" s="18"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" s="8" t="s">
+      <c r="A128" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B128" s="9" t="s">
+      <c r="B128" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="C128" s="9">
+      <c r="C128" s="8">
         <v>7</v>
       </c>
-      <c r="D128" s="9"/>
-      <c r="E128" s="17"/>
-      <c r="F128" s="12"/>
+      <c r="D128" s="8"/>
+      <c r="E128" s="19"/>
+      <c r="F128" s="18"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" s="4" t="s">
+      <c r="A129" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B129" s="6" t="s">
+      <c r="B129" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C129" s="5">
+      <c r="C129" s="4">
         <v>1</v>
       </c>
-      <c r="D129" s="6">
+      <c r="D129" s="5">
         <v>1</v>
       </c>
-      <c r="E129" s="17">
+      <c r="E129" s="19">
         <v>27</v>
       </c>
-      <c r="F129" s="12"/>
+      <c r="F129" s="18"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" s="7" t="s">
+      <c r="A130" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="B130" t="s">
         <v>105</v>
       </c>
-      <c r="C130" s="2">
+      <c r="C130">
         <v>2</v>
       </c>
-      <c r="D130" s="2">
+      <c r="D130">
         <v>2</v>
       </c>
-      <c r="E130" s="17"/>
-      <c r="F130" s="12"/>
+      <c r="E130" s="19"/>
+      <c r="F130" s="18"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="7" t="s">
+      <c r="A131" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="B131" t="s">
         <v>106</v>
       </c>
-      <c r="C131" s="2">
-        <v>3</v>
-      </c>
-      <c r="D131" s="2">
-        <v>3</v>
-      </c>
-      <c r="E131" s="17"/>
-      <c r="F131" s="12"/>
+      <c r="C131">
+        <v>3</v>
+      </c>
+      <c r="D131">
+        <v>3</v>
+      </c>
+      <c r="E131" s="19"/>
+      <c r="F131" s="18"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A132" s="7" t="s">
+      <c r="A132" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="B132" t="s">
         <v>107</v>
       </c>
-      <c r="C132" s="2">
+      <c r="C132">
         <v>4</v>
       </c>
-      <c r="D132" s="18">
+      <c r="D132">
         <v>4</v>
       </c>
-      <c r="E132" s="17"/>
-      <c r="F132" s="12"/>
+      <c r="E132" s="19"/>
+      <c r="F132" s="18"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A133" s="7" t="s">
+      <c r="A133" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="B133" t="s">
         <v>108</v>
       </c>
-      <c r="C133" s="2">
+      <c r="C133">
         <v>5</v>
       </c>
-      <c r="D133" s="18">
+      <c r="D133">
         <v>5</v>
       </c>
-      <c r="E133" s="17"/>
-      <c r="F133" s="12"/>
+      <c r="E133" s="19"/>
+      <c r="F133" s="18"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A134" s="7" t="s">
+      <c r="A134" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="B134" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C134" s="2">
+      <c r="C134">
         <v>6</v>
       </c>
-      <c r="D134" s="3">
+      <c r="D134" s="2">
         <v>6</v>
       </c>
-      <c r="E134" s="17"/>
-      <c r="F134" s="12"/>
+      <c r="E134" s="19"/>
+      <c r="F134" s="18"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135" s="7" t="s">
+      <c r="A135" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B135" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C135" s="2">
+      <c r="C135">
         <v>7</v>
       </c>
-      <c r="D135" s="3">
+      <c r="D135" s="2">
         <v>6</v>
       </c>
-      <c r="E135" s="17"/>
-      <c r="F135" s="12"/>
-      <c r="G135" s="2">
+      <c r="E135" s="19"/>
+      <c r="F135" s="18"/>
+      <c r="G135">
         <v>7</v>
       </c>
-      <c r="H135" s="2">
+      <c r="H135">
         <v>6</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A136" s="7" t="s">
+      <c r="A136" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B136" s="11" t="s">
+      <c r="B136" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="C136" s="2">
+      <c r="C136">
         <v>8</v>
       </c>
-      <c r="D136" s="18">
+      <c r="D136">
         <v>8</v>
       </c>
-      <c r="E136" s="17"/>
-      <c r="F136" s="12"/>
+      <c r="E136" s="19"/>
+      <c r="F136" s="18"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A137" s="7" t="s">
+      <c r="A137" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B137" s="11" t="s">
+      <c r="B137" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="C137" s="2">
+      <c r="C137">
         <v>9</v>
       </c>
-      <c r="D137" s="18">
+      <c r="D137">
         <v>9</v>
       </c>
-      <c r="E137" s="17"/>
-      <c r="F137" s="12"/>
+      <c r="E137" s="19"/>
+      <c r="F137" s="18"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A138" s="7" t="s">
+      <c r="A138" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B138" s="11" t="s">
+      <c r="B138" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C138" s="2">
+      <c r="C138">
         <v>10</v>
       </c>
-      <c r="D138" s="18">
+      <c r="D138">
         <v>10</v>
       </c>
-      <c r="E138" s="17"/>
-      <c r="F138" s="12"/>
+      <c r="E138" s="19"/>
+      <c r="F138" s="18"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A139" s="7" t="s">
+      <c r="A139" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="B139" t="s">
         <v>114</v>
       </c>
-      <c r="C139" s="2">
+      <c r="C139">
         <v>11</v>
       </c>
-      <c r="D139" s="18">
+      <c r="D139">
         <v>11</v>
       </c>
-      <c r="E139" s="17"/>
-      <c r="F139" s="12"/>
+      <c r="E139" s="19"/>
+      <c r="F139" s="18"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="7" t="s">
+      <c r="A140" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="B140" t="s">
         <v>115</v>
       </c>
-      <c r="C140" s="2">
+      <c r="C140">
         <v>12</v>
       </c>
-      <c r="D140" s="18">
+      <c r="D140">
         <v>12</v>
       </c>
-      <c r="E140" s="17"/>
-      <c r="F140" s="12"/>
+      <c r="E140" s="19"/>
+      <c r="F140" s="18"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141" s="7" t="s">
+      <c r="A141" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="B141" t="s">
         <v>116</v>
       </c>
-      <c r="C141" s="2">
+      <c r="C141">
         <v>13</v>
       </c>
-      <c r="D141" s="18">
+      <c r="D141">
         <v>13</v>
       </c>
-      <c r="E141" s="17"/>
-      <c r="F141" s="12"/>
+      <c r="E141" s="19"/>
+      <c r="F141" s="18"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" s="7" t="s">
+      <c r="A142" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="B142" t="s">
         <v>117</v>
       </c>
-      <c r="C142" s="2">
+      <c r="C142">
         <v>14</v>
       </c>
-      <c r="D142" s="18">
+      <c r="D142">
         <v>14</v>
       </c>
-      <c r="E142" s="17"/>
-      <c r="F142" s="12"/>
+      <c r="E142" s="19"/>
+      <c r="F142" s="18"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A143" s="7" t="s">
+      <c r="A143" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B143" s="11" t="s">
+      <c r="B143" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C143" s="2">
+      <c r="C143">
         <v>15</v>
       </c>
-      <c r="D143" s="18">
+      <c r="D143">
         <v>15</v>
       </c>
-      <c r="E143" s="17"/>
-      <c r="F143" s="12"/>
+      <c r="E143" s="19"/>
+      <c r="F143" s="18"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A144" s="7" t="s">
+      <c r="A144" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B144" s="3" t="s">
+      <c r="B144" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C144" s="2">
+      <c r="C144">
         <v>16</v>
       </c>
-      <c r="D144" s="3">
+      <c r="D144" s="2">
         <v>16</v>
       </c>
-      <c r="E144" s="17"/>
-      <c r="F144" s="12"/>
+      <c r="E144" s="19"/>
+      <c r="F144" s="18"/>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A145" s="7" t="s">
+      <c r="A145" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="B145" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C145" s="2">
+      <c r="C145">
         <v>17</v>
       </c>
-      <c r="D145" s="3">
+      <c r="D145" s="2">
         <v>16</v>
       </c>
-      <c r="E145" s="17"/>
-      <c r="F145" s="12"/>
-      <c r="G145" s="2">
+      <c r="E145" s="19"/>
+      <c r="F145" s="18"/>
+      <c r="G145">
         <v>17</v>
       </c>
-      <c r="H145" s="2">
+      <c r="H145">
         <v>16</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A146" s="7" t="s">
+      <c r="A146" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B146" s="11" t="s">
+      <c r="B146" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="C146" s="2">
+      <c r="C146">
         <v>18</v>
       </c>
-      <c r="D146" s="18">
+      <c r="D146">
         <v>18</v>
       </c>
-      <c r="E146" s="17"/>
-      <c r="F146" s="12"/>
+      <c r="E146" s="19"/>
+      <c r="F146" s="18"/>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A147" s="7" t="s">
+      <c r="A147" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="B147" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C147" s="2">
+      <c r="C147">
         <v>19</v>
       </c>
-      <c r="D147" s="3">
+      <c r="D147" s="2">
         <v>19</v>
       </c>
-      <c r="E147" s="17"/>
-      <c r="F147" s="12"/>
+      <c r="E147" s="19"/>
+      <c r="F147" s="18"/>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A148" s="7" t="s">
+      <c r="A148" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B148" s="3" t="s">
+      <c r="B148" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C148" s="2">
+      <c r="C148">
         <v>20</v>
       </c>
-      <c r="D148" s="3">
+      <c r="D148" s="2">
         <v>19</v>
       </c>
-      <c r="E148" s="17"/>
-      <c r="F148" s="12"/>
-      <c r="G148" s="2">
+      <c r="E148" s="19"/>
+      <c r="F148" s="18"/>
+      <c r="G148">
         <v>20</v>
       </c>
-      <c r="H148" s="2">
+      <c r="H148">
         <v>19</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A149" s="7" t="s">
+      <c r="A149" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="B149" t="s">
         <v>124</v>
       </c>
-      <c r="C149" s="2">
+      <c r="C149">
         <v>21</v>
       </c>
-      <c r="D149" s="19">
+      <c r="D149" s="15">
         <v>21</v>
       </c>
-      <c r="E149" s="17"/>
-      <c r="F149" s="12"/>
+      <c r="E149" s="19"/>
+      <c r="F149" s="18"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A150" s="7" t="s">
+      <c r="A150" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="B150" t="s">
         <v>125</v>
       </c>
-      <c r="C150" s="2">
+      <c r="C150">
         <v>22</v>
       </c>
-      <c r="D150" s="19">
+      <c r="D150" s="15">
         <v>22</v>
       </c>
-      <c r="E150" s="17"/>
-      <c r="F150" s="12"/>
+      <c r="E150" s="19"/>
+      <c r="F150" s="18"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A151" s="7" t="s">
+      <c r="A151" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="B151" t="s">
         <v>126</v>
       </c>
-      <c r="C151" s="2">
+      <c r="C151">
         <v>23</v>
       </c>
-      <c r="D151" s="19">
+      <c r="D151" s="15">
         <v>23</v>
       </c>
-      <c r="E151" s="17"/>
-      <c r="F151" s="12"/>
+      <c r="E151" s="19"/>
+      <c r="F151" s="18"/>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A152" s="7" t="s">
+      <c r="A152" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B152" s="2" t="s">
+      <c r="B152" t="s">
         <v>127</v>
       </c>
-      <c r="C152" s="2">
+      <c r="C152">
         <v>24</v>
       </c>
-      <c r="D152" s="19">
+      <c r="D152" s="15">
         <v>24</v>
       </c>
-      <c r="E152" s="17"/>
-      <c r="F152" s="12"/>
+      <c r="E152" s="19"/>
+      <c r="F152" s="18"/>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A153" s="7" t="s">
+      <c r="A153" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B153" s="3" t="s">
+      <c r="B153" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C153" s="2">
+      <c r="C153">
         <v>25</v>
       </c>
-      <c r="D153" s="3">
+      <c r="D153" s="2">
         <v>1</v>
       </c>
-      <c r="E153" s="17"/>
-      <c r="F153" s="12"/>
-      <c r="G153" s="2">
+      <c r="E153" s="19"/>
+      <c r="F153" s="18"/>
+      <c r="G153">
         <v>25</v>
       </c>
-      <c r="H153" s="2">
+      <c r="H153">
         <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A154" s="7" t="s">
+      <c r="A154" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B154" s="11" t="s">
+      <c r="B154" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="C154" s="2">
+      <c r="C154">
         <v>26</v>
       </c>
-      <c r="D154" s="19">
+      <c r="D154" s="15">
         <v>26</v>
       </c>
-      <c r="E154" s="17"/>
-      <c r="F154" s="12"/>
+      <c r="E154" s="19"/>
+      <c r="F154" s="18"/>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A155" s="7" t="s">
+      <c r="A155" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B155" s="2" t="s">
+      <c r="B155" t="s">
         <v>130</v>
       </c>
-      <c r="C155" s="2">
+      <c r="C155">
         <v>27</v>
       </c>
-      <c r="D155" s="19">
+      <c r="D155" s="15">
         <v>27</v>
       </c>
-      <c r="E155" s="17"/>
-      <c r="F155" s="12"/>
+      <c r="E155" s="19"/>
+      <c r="F155" s="18"/>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A156" s="7" t="s">
+      <c r="A156" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B156" s="2" t="s">
+      <c r="B156" t="s">
         <v>131</v>
       </c>
-      <c r="C156" s="2">
+      <c r="C156">
         <v>28</v>
       </c>
-      <c r="D156" s="19">
+      <c r="D156" s="15">
         <v>28</v>
       </c>
-      <c r="E156" s="17"/>
-      <c r="F156" s="12"/>
+      <c r="E156" s="19"/>
+      <c r="F156" s="18"/>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A157" s="7" t="s">
+      <c r="A157" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B157" s="2" t="s">
+      <c r="B157" t="s">
         <v>132</v>
       </c>
-      <c r="C157" s="2">
+      <c r="C157">
         <v>29</v>
       </c>
-      <c r="D157" s="19">
+      <c r="D157" s="15">
         <v>29</v>
       </c>
-      <c r="E157" s="17"/>
-      <c r="F157" s="12"/>
+      <c r="E157" s="19"/>
+      <c r="F157" s="18"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A158" s="7" t="s">
+      <c r="A158" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B158" s="2" t="s">
+      <c r="B158" t="s">
         <v>133</v>
       </c>
-      <c r="C158" s="2">
+      <c r="C158">
         <v>30</v>
       </c>
-      <c r="D158" s="19">
+      <c r="D158" s="15">
         <v>30</v>
       </c>
-      <c r="E158" s="17"/>
-      <c r="F158" s="12"/>
+      <c r="E158" s="19"/>
+      <c r="F158" s="18"/>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A159" s="8" t="s">
+      <c r="A159" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B159" s="9" t="s">
+      <c r="B159" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="C159" s="9">
+      <c r="C159" s="8">
         <v>31</v>
       </c>
-      <c r="D159" s="9">
+      <c r="D159" s="8">
         <v>31</v>
       </c>
-      <c r="E159" s="17"/>
-      <c r="F159" s="12"/>
+      <c r="E159" s="19"/>
+      <c r="F159" s="18"/>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A160" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B160" s="5" t="s">
+      <c r="A160" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B160" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C160" s="5">
+      <c r="C160" s="4">
         <v>1</v>
       </c>
-      <c r="D160" s="5"/>
-      <c r="E160" s="17">
+      <c r="D160" s="4"/>
+      <c r="E160" s="19">
         <v>78</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B161" s="2" t="s">
+      <c r="A161" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B161" t="s">
         <v>137</v>
       </c>
-      <c r="C161" s="2">
+      <c r="C161">
         <v>2</v>
       </c>
-      <c r="D161" s="2"/>
-      <c r="E161" s="17"/>
+      <c r="E161" s="19"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B162" s="2" t="s">
+      <c r="A162" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B162" t="s">
         <v>138</v>
       </c>
-      <c r="C162" s="2">
-        <v>3</v>
-      </c>
-      <c r="D162" s="2"/>
-      <c r="E162" s="17"/>
+      <c r="C162">
+        <v>3</v>
+      </c>
+      <c r="E162" s="19"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B163" s="2" t="s">
+      <c r="A163" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B163" t="s">
         <v>139</v>
       </c>
-      <c r="C163" s="2">
+      <c r="C163">
         <v>4</v>
       </c>
-      <c r="D163" s="2"/>
-      <c r="E163" s="17"/>
+      <c r="E163" s="19"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B164" s="2" t="s">
+      <c r="A164" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B164" t="s">
         <v>140</v>
       </c>
-      <c r="C164" s="2">
+      <c r="C164">
         <v>5</v>
       </c>
-      <c r="D164" s="2"/>
-      <c r="E164" s="17"/>
+      <c r="E164" s="19"/>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B165" s="2" t="s">
+      <c r="A165" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B165" t="s">
         <v>141</v>
       </c>
-      <c r="C165" s="2">
+      <c r="C165">
         <v>6</v>
       </c>
-      <c r="D165" s="2"/>
-      <c r="E165" s="17"/>
+      <c r="E165" s="19"/>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A166" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B166" s="2" t="s">
+      <c r="A166" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B166" t="s">
         <v>142</v>
       </c>
-      <c r="C166" s="2">
+      <c r="C166">
         <v>7</v>
       </c>
-      <c r="D166" s="2"/>
-      <c r="E166" s="17"/>
+      <c r="E166" s="19"/>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B167" s="2" t="s">
+      <c r="A167" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B167" t="s">
         <v>143</v>
       </c>
-      <c r="C167" s="2">
+      <c r="C167">
         <v>8</v>
       </c>
-      <c r="D167" s="2"/>
-      <c r="E167" s="17"/>
+      <c r="E167" s="19"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A168" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B168" s="2" t="s">
+      <c r="A168" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B168" t="s">
         <v>144</v>
       </c>
-      <c r="C168" s="2">
+      <c r="C168">
         <v>9</v>
       </c>
-      <c r="D168" s="2"/>
-      <c r="E168" s="17"/>
+      <c r="E168" s="19"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B169" s="2" t="s">
+      <c r="A169" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B169" t="s">
         <v>145</v>
       </c>
-      <c r="C169" s="2">
+      <c r="C169">
         <v>10</v>
       </c>
-      <c r="D169" s="2"/>
-      <c r="E169" s="17"/>
+      <c r="E169" s="19"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A170" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B170" s="2" t="s">
+      <c r="A170" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B170" t="s">
         <v>146</v>
       </c>
-      <c r="C170" s="2">
+      <c r="C170">
         <v>11</v>
       </c>
-      <c r="D170" s="2"/>
-      <c r="E170" s="17"/>
+      <c r="E170" s="19"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B171" s="2" t="s">
+      <c r="A171" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B171" t="s">
         <v>147</v>
       </c>
-      <c r="C171" s="2">
+      <c r="C171">
         <v>12</v>
       </c>
-      <c r="D171" s="2"/>
-      <c r="E171" s="17"/>
+      <c r="E171" s="19"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A172" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B172" s="2" t="s">
+      <c r="A172" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B172" t="s">
         <v>148</v>
       </c>
-      <c r="C172" s="2">
+      <c r="C172">
         <v>13</v>
       </c>
-      <c r="D172" s="2"/>
-      <c r="E172" s="17"/>
+      <c r="E172" s="19"/>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B173" s="2" t="s">
+      <c r="A173" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B173" t="s">
         <v>149</v>
       </c>
-      <c r="C173" s="2">
+      <c r="C173">
         <v>14</v>
       </c>
-      <c r="D173" s="2"/>
-      <c r="E173" s="17"/>
+      <c r="E173" s="19"/>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A174" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B174" s="2" t="s">
+      <c r="A174" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B174" t="s">
         <v>150</v>
       </c>
-      <c r="C174" s="2">
+      <c r="C174">
         <v>15</v>
       </c>
-      <c r="D174" s="2"/>
-      <c r="E174" s="17"/>
+      <c r="E174" s="19"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A175" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B175" s="2" t="s">
+      <c r="A175" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B175" t="s">
         <v>151</v>
       </c>
-      <c r="C175" s="2">
+      <c r="C175">
         <v>16</v>
       </c>
-      <c r="D175" s="2"/>
-      <c r="E175" s="17"/>
+      <c r="E175" s="19"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A176" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B176" s="2" t="s">
+      <c r="A176" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B176" t="s">
         <v>152</v>
       </c>
-      <c r="C176" s="2">
+      <c r="C176">
         <v>17</v>
       </c>
-      <c r="D176" s="2"/>
-      <c r="E176" s="17"/>
+      <c r="E176" s="19"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A177" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B177" s="2" t="s">
+      <c r="A177" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B177" t="s">
         <v>153</v>
       </c>
-      <c r="C177" s="2">
+      <c r="C177">
         <v>18</v>
       </c>
-      <c r="D177" s="2"/>
-      <c r="E177" s="17"/>
+      <c r="E177" s="19"/>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A178" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B178" s="2" t="s">
+      <c r="A178" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B178" t="s">
         <v>154</v>
       </c>
-      <c r="C178" s="2">
+      <c r="C178">
         <v>19</v>
       </c>
-      <c r="D178" s="2"/>
-      <c r="E178" s="17"/>
+      <c r="E178" s="19"/>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A179" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B179" s="2" t="s">
+      <c r="A179" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B179" t="s">
         <v>155</v>
       </c>
-      <c r="C179" s="2">
+      <c r="C179">
         <v>20</v>
       </c>
-      <c r="D179" s="2"/>
-      <c r="E179" s="17"/>
+      <c r="E179" s="19"/>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A180" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B180" s="2" t="s">
+      <c r="A180" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B180" t="s">
         <v>156</v>
       </c>
-      <c r="C180" s="2">
+      <c r="C180">
         <v>21</v>
       </c>
-      <c r="D180" s="2"/>
-      <c r="E180" s="17"/>
+      <c r="E180" s="19"/>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A181" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B181" s="2" t="s">
+      <c r="A181" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B181" t="s">
         <v>157</v>
       </c>
-      <c r="C181" s="2">
+      <c r="C181">
         <v>22</v>
       </c>
-      <c r="D181" s="2"/>
-      <c r="E181" s="17"/>
+      <c r="E181" s="19"/>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A182" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B182" s="2" t="s">
+      <c r="A182" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B182" t="s">
         <v>158</v>
       </c>
-      <c r="C182" s="2">
+      <c r="C182">
         <v>23</v>
       </c>
-      <c r="D182" s="2"/>
-      <c r="E182" s="17"/>
+      <c r="E182" s="19"/>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A183" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B183" s="2" t="s">
+      <c r="A183" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B183" t="s">
         <v>159</v>
       </c>
-      <c r="C183" s="2">
+      <c r="C183">
         <v>24</v>
       </c>
-      <c r="D183" s="2"/>
-      <c r="E183" s="17"/>
+      <c r="E183" s="19"/>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A184" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B184" s="2" t="s">
+      <c r="A184" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B184" t="s">
         <v>160</v>
       </c>
-      <c r="C184" s="2">
+      <c r="C184">
         <v>25</v>
       </c>
-      <c r="D184" s="2"/>
-      <c r="E184" s="17"/>
+      <c r="E184" s="19"/>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A185" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B185" s="2" t="s">
+      <c r="A185" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B185" t="s">
         <v>161</v>
       </c>
-      <c r="C185" s="2">
+      <c r="C185">
         <v>26</v>
       </c>
-      <c r="D185" s="2"/>
-      <c r="E185" s="17"/>
+      <c r="E185" s="19"/>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A186" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B186" s="2" t="s">
+      <c r="A186" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B186" t="s">
         <v>162</v>
       </c>
-      <c r="C186" s="2">
+      <c r="C186">
         <v>27</v>
       </c>
-      <c r="D186" s="2"/>
-      <c r="E186" s="17"/>
+      <c r="E186" s="19"/>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A187" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B187" s="2" t="s">
+      <c r="A187" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B187" t="s">
         <v>163</v>
       </c>
-      <c r="C187" s="2">
+      <c r="C187">
         <v>28</v>
       </c>
-      <c r="D187" s="2"/>
-      <c r="E187" s="17"/>
+      <c r="E187" s="19"/>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A188" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B188" s="2" t="s">
+      <c r="A188" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B188" t="s">
         <v>164</v>
       </c>
-      <c r="C188" s="2">
+      <c r="C188">
         <v>29</v>
       </c>
-      <c r="D188" s="2"/>
-      <c r="E188" s="17"/>
+      <c r="E188" s="19"/>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A189" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B189" s="2" t="s">
+      <c r="A189" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B189" t="s">
         <v>165</v>
       </c>
-      <c r="C189" s="2">
+      <c r="C189">
         <v>30</v>
       </c>
-      <c r="D189" s="2"/>
-      <c r="E189" s="17"/>
+      <c r="E189" s="19"/>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A190" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B190" s="2" t="s">
+      <c r="A190" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B190" t="s">
         <v>166</v>
       </c>
-      <c r="C190" s="2">
+      <c r="C190">
         <v>31</v>
       </c>
-      <c r="D190" s="2"/>
-      <c r="E190" s="17"/>
+      <c r="E190" s="19"/>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A191" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B191" s="2" t="s">
+      <c r="A191" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B191" t="s">
         <v>167</v>
       </c>
-      <c r="C191" s="2">
+      <c r="C191">
         <v>32</v>
       </c>
-      <c r="D191" s="2"/>
-      <c r="E191" s="17"/>
+      <c r="E191" s="19"/>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A192" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B192" s="2" t="s">
+      <c r="A192" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B192" t="s">
         <v>168</v>
       </c>
-      <c r="C192" s="2">
+      <c r="C192">
         <v>33</v>
       </c>
-      <c r="D192" s="2"/>
-      <c r="E192" s="17"/>
+      <c r="E192" s="19"/>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A193" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B193" s="2" t="s">
+      <c r="A193" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B193" t="s">
         <v>169</v>
       </c>
-      <c r="C193" s="2">
+      <c r="C193">
         <v>34</v>
       </c>
-      <c r="D193" s="2"/>
-      <c r="E193" s="17"/>
+      <c r="E193" s="19"/>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A194" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B194" s="2" t="s">
+      <c r="A194" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B194" t="s">
         <v>170</v>
       </c>
-      <c r="C194" s="2">
+      <c r="C194">
         <v>35</v>
       </c>
-      <c r="D194" s="2"/>
-      <c r="E194" s="17"/>
+      <c r="E194" s="19"/>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A195" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B195" s="2" t="s">
+      <c r="A195" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B195" t="s">
         <v>171</v>
       </c>
-      <c r="C195" s="2">
+      <c r="C195">
         <v>36</v>
       </c>
-      <c r="D195" s="2"/>
-      <c r="E195" s="17"/>
+      <c r="E195" s="19"/>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A196" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B196" s="2" t="s">
+      <c r="A196" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B196" t="s">
         <v>172</v>
       </c>
-      <c r="C196" s="2">
+      <c r="C196">
         <v>37</v>
       </c>
-      <c r="D196" s="2"/>
-      <c r="E196" s="17"/>
+      <c r="E196" s="19"/>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A197" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B197" s="2" t="s">
+      <c r="A197" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B197" t="s">
         <v>173</v>
       </c>
-      <c r="C197" s="2">
+      <c r="C197">
         <v>38</v>
       </c>
-      <c r="D197" s="2"/>
-      <c r="E197" s="17"/>
+      <c r="E197" s="19"/>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A198" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B198" s="2" t="s">
+      <c r="A198" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B198" t="s">
         <v>174</v>
       </c>
-      <c r="C198" s="2">
+      <c r="C198">
         <v>39</v>
       </c>
-      <c r="D198" s="2"/>
-      <c r="E198" s="17"/>
+      <c r="E198" s="19"/>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A199" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B199" s="2" t="s">
+      <c r="A199" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B199" t="s">
         <v>175</v>
       </c>
-      <c r="C199" s="2">
+      <c r="C199">
         <v>40</v>
       </c>
-      <c r="D199" s="2"/>
-      <c r="E199" s="17"/>
+      <c r="E199" s="19"/>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A200" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B200" s="2" t="s">
+      <c r="A200" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B200" t="s">
         <v>176</v>
       </c>
-      <c r="C200" s="2">
+      <c r="C200">
         <v>41</v>
       </c>
-      <c r="D200" s="2"/>
-      <c r="E200" s="17"/>
+      <c r="E200" s="19"/>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A201" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B201" s="2" t="s">
+      <c r="A201" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B201" t="s">
         <v>177</v>
       </c>
-      <c r="C201" s="2">
+      <c r="C201">
         <v>42</v>
       </c>
-      <c r="D201" s="2"/>
-      <c r="E201" s="17"/>
+      <c r="E201" s="19"/>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A202" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B202" s="2" t="s">
+      <c r="A202" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B202" t="s">
         <v>178</v>
       </c>
-      <c r="C202" s="2">
+      <c r="C202">
         <v>43</v>
       </c>
-      <c r="D202" s="2"/>
-      <c r="E202" s="17"/>
+      <c r="E202" s="19"/>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A203" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B203" s="2" t="s">
+      <c r="A203" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B203" t="s">
         <v>179</v>
       </c>
-      <c r="C203" s="2">
-        <v>44</v>
-      </c>
-      <c r="D203" s="2"/>
-      <c r="E203" s="17"/>
+      <c r="C203">
+        <v>44</v>
+      </c>
+      <c r="E203" s="19"/>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A204" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B204" s="2" t="s">
+      <c r="A204" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B204" t="s">
         <v>180</v>
       </c>
-      <c r="C204" s="2">
+      <c r="C204">
         <v>45</v>
       </c>
-      <c r="D204" s="2"/>
-      <c r="E204" s="17"/>
+      <c r="E204" s="19"/>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A205" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B205" s="2" t="s">
+      <c r="A205" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B205" t="s">
         <v>181</v>
       </c>
-      <c r="C205" s="2">
+      <c r="C205">
         <v>46</v>
       </c>
-      <c r="D205" s="2"/>
-      <c r="E205" s="17"/>
+      <c r="E205" s="19"/>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A206" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B206" s="2" t="s">
+      <c r="A206" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B206" t="s">
         <v>182</v>
       </c>
-      <c r="C206" s="2">
+      <c r="C206">
         <v>47</v>
       </c>
-      <c r="D206" s="2"/>
-      <c r="E206" s="17"/>
+      <c r="E206" s="19"/>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A207" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B207" s="2" t="s">
+      <c r="A207" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B207" t="s">
         <v>183</v>
       </c>
-      <c r="C207" s="2">
+      <c r="C207">
         <v>48</v>
       </c>
-      <c r="D207" s="2"/>
-      <c r="E207" s="17"/>
+      <c r="E207" s="19"/>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A208" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B208" s="2" t="s">
+      <c r="A208" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B208" t="s">
         <v>184</v>
       </c>
-      <c r="C208" s="2">
+      <c r="C208">
         <v>49</v>
       </c>
-      <c r="D208" s="2"/>
-      <c r="E208" s="17"/>
+      <c r="E208" s="19"/>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A209" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B209" s="2" t="s">
+      <c r="A209" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B209" t="s">
         <v>185</v>
       </c>
-      <c r="C209" s="2">
+      <c r="C209">
         <v>50</v>
       </c>
-      <c r="D209" s="2"/>
-      <c r="E209" s="17"/>
+      <c r="E209" s="19"/>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A210" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B210" s="2" t="s">
+      <c r="A210" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B210" t="s">
         <v>186</v>
       </c>
-      <c r="C210" s="2">
+      <c r="C210">
         <v>51</v>
       </c>
-      <c r="D210" s="2"/>
-      <c r="E210" s="17"/>
+      <c r="E210" s="19"/>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A211" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B211" s="2" t="s">
+      <c r="A211" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B211" t="s">
         <v>187</v>
       </c>
-      <c r="C211" s="2">
+      <c r="C211">
         <v>52</v>
       </c>
-      <c r="D211" s="2"/>
-      <c r="E211" s="17"/>
+      <c r="E211" s="19"/>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A212" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B212" s="2" t="s">
+      <c r="A212" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B212" t="s">
         <v>188</v>
       </c>
-      <c r="C212" s="2">
+      <c r="C212">
         <v>53</v>
       </c>
-      <c r="D212" s="2"/>
-      <c r="E212" s="17"/>
+      <c r="E212" s="19"/>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A213" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B213" s="2" t="s">
+      <c r="A213" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B213" t="s">
         <v>189</v>
       </c>
-      <c r="C213" s="2">
+      <c r="C213">
         <v>54</v>
       </c>
-      <c r="D213" s="2"/>
-      <c r="E213" s="17"/>
+      <c r="E213" s="19"/>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A214" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B214" s="2" t="s">
+      <c r="A214" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B214" t="s">
         <v>190</v>
       </c>
-      <c r="C214" s="2">
+      <c r="C214">
         <v>55</v>
       </c>
-      <c r="D214" s="2"/>
-      <c r="E214" s="17"/>
+      <c r="E214" s="19"/>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A215" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B215" s="2" t="s">
+      <c r="A215" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B215" t="s">
         <v>191</v>
       </c>
-      <c r="C215" s="2">
+      <c r="C215">
         <v>56</v>
       </c>
-      <c r="D215" s="2"/>
-      <c r="E215" s="17"/>
+      <c r="E215" s="19"/>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A216" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B216" s="2" t="s">
+      <c r="A216" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B216" t="s">
         <v>192</v>
       </c>
-      <c r="C216" s="2">
+      <c r="C216">
         <v>57</v>
       </c>
-      <c r="D216" s="2"/>
-      <c r="E216" s="17"/>
+      <c r="E216" s="19"/>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A217" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B217" s="2" t="s">
+      <c r="A217" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B217" t="s">
         <v>193</v>
       </c>
-      <c r="C217" s="2">
+      <c r="C217">
         <v>58</v>
       </c>
-      <c r="D217" s="2"/>
-      <c r="E217" s="17"/>
+      <c r="E217" s="19"/>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A218" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B218" s="2" t="s">
+      <c r="A218" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B218" t="s">
         <v>194</v>
       </c>
-      <c r="C218" s="2">
+      <c r="C218">
         <v>59</v>
       </c>
-      <c r="D218" s="2"/>
-      <c r="E218" s="17"/>
+      <c r="E218" s="19"/>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A219" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B219" s="2" t="s">
+      <c r="A219" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B219" t="s">
         <v>195</v>
       </c>
-      <c r="C219" s="2">
+      <c r="C219">
         <v>60</v>
       </c>
-      <c r="D219" s="2"/>
-      <c r="E219" s="17"/>
+      <c r="E219" s="19"/>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A220" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B220" s="2" t="s">
+      <c r="A220" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B220" t="s">
         <v>196</v>
       </c>
-      <c r="C220" s="2">
+      <c r="C220">
         <v>61</v>
       </c>
-      <c r="D220" s="2"/>
-      <c r="E220" s="17"/>
+      <c r="E220" s="19"/>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A221" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B221" s="2" t="s">
+      <c r="A221" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B221" t="s">
         <v>197</v>
       </c>
-      <c r="C221" s="2">
+      <c r="C221">
         <v>62</v>
       </c>
-      <c r="D221" s="2"/>
-      <c r="E221" s="17"/>
+      <c r="E221" s="19"/>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A222" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B222" s="2" t="s">
+      <c r="A222" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B222" t="s">
         <v>198</v>
       </c>
-      <c r="C222" s="2">
+      <c r="C222">
         <v>63</v>
       </c>
-      <c r="D222" s="2"/>
-      <c r="E222" s="17"/>
+      <c r="E222" s="19"/>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A223" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B223" s="2" t="s">
+      <c r="A223" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B223" t="s">
         <v>199</v>
       </c>
-      <c r="C223" s="2">
+      <c r="C223">
         <v>64</v>
       </c>
-      <c r="D223" s="2"/>
-      <c r="E223" s="17"/>
+      <c r="E223" s="19"/>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A224" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B224" s="2" t="s">
+      <c r="A224" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B224" t="s">
         <v>200</v>
       </c>
-      <c r="C224" s="2">
+      <c r="C224">
         <v>65</v>
       </c>
-      <c r="D224" s="2"/>
-      <c r="E224" s="17"/>
+      <c r="E224" s="19"/>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A225" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B225" s="2" t="s">
+      <c r="A225" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B225" t="s">
         <v>201</v>
       </c>
-      <c r="C225" s="2">
+      <c r="C225">
         <v>66</v>
       </c>
-      <c r="D225" s="2"/>
-      <c r="E225" s="17"/>
+      <c r="E225" s="19"/>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A226" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B226" s="2" t="s">
+      <c r="A226" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B226" t="s">
         <v>202</v>
       </c>
-      <c r="C226" s="2">
+      <c r="C226">
         <v>67</v>
       </c>
-      <c r="D226" s="2"/>
-      <c r="E226" s="17"/>
+      <c r="E226" s="19"/>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A227" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B227" s="2" t="s">
+      <c r="A227" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B227" t="s">
         <v>203</v>
       </c>
-      <c r="C227" s="2">
+      <c r="C227">
         <v>68</v>
       </c>
-      <c r="D227" s="2"/>
-      <c r="E227" s="17"/>
+      <c r="E227" s="19"/>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A228" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B228" s="2" t="s">
+      <c r="A228" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B228" t="s">
         <v>204</v>
       </c>
-      <c r="C228" s="2">
+      <c r="C228">
         <v>69</v>
       </c>
-      <c r="D228" s="2"/>
-      <c r="E228" s="17"/>
+      <c r="E228" s="19"/>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A229" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B229" s="2" t="s">
+      <c r="A229" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B229" t="s">
         <v>205</v>
       </c>
-      <c r="C229" s="2">
+      <c r="C229">
         <v>70</v>
       </c>
-      <c r="D229" s="2"/>
-      <c r="E229" s="17"/>
+      <c r="E229" s="19"/>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A230" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B230" s="2" t="s">
+      <c r="A230" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B230" t="s">
         <v>206</v>
       </c>
-      <c r="C230" s="2">
+      <c r="C230">
         <v>71</v>
       </c>
-      <c r="D230" s="2"/>
-      <c r="E230" s="17"/>
+      <c r="E230" s="19"/>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A231" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B231" s="2" t="s">
+      <c r="A231" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B231" t="s">
         <v>207</v>
       </c>
-      <c r="C231" s="2">
+      <c r="C231">
         <v>72</v>
       </c>
-      <c r="D231" s="2"/>
-      <c r="E231" s="17"/>
+      <c r="E231" s="19"/>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A232" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B232" s="2" t="s">
+      <c r="A232" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B232" t="s">
         <v>208</v>
       </c>
-      <c r="C232" s="2">
+      <c r="C232">
         <v>73</v>
       </c>
-      <c r="D232" s="2"/>
-      <c r="E232" s="17"/>
+      <c r="E232" s="19"/>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A233" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B233" s="2" t="s">
+      <c r="A233" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B233" t="s">
         <v>209</v>
       </c>
-      <c r="C233" s="2">
+      <c r="C233">
         <v>74</v>
       </c>
-      <c r="D233" s="2"/>
-      <c r="E233" s="17"/>
+      <c r="E233" s="19"/>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A234" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B234" s="2" t="s">
+      <c r="A234" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B234" t="s">
         <v>210</v>
       </c>
-      <c r="C234" s="2">
+      <c r="C234">
         <v>75</v>
       </c>
-      <c r="D234" s="2"/>
-      <c r="E234" s="17"/>
+      <c r="E234" s="19"/>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A235" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B235" s="2" t="s">
+      <c r="A235" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B235" t="s">
         <v>211</v>
       </c>
-      <c r="C235" s="2">
+      <c r="C235">
         <v>76</v>
       </c>
-      <c r="D235" s="2"/>
-      <c r="E235" s="17"/>
+      <c r="E235" s="19"/>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A236" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B236" s="2" t="s">
+      <c r="A236" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B236" t="s">
         <v>212</v>
       </c>
-      <c r="C236" s="2">
+      <c r="C236">
         <v>77</v>
       </c>
-      <c r="D236" s="2"/>
-      <c r="E236" s="17"/>
+      <c r="E236" s="19"/>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A237" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B237" s="9" t="s">
+      <c r="A237" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B237" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="C237" s="9">
+      <c r="C237" s="8">
         <v>78</v>
       </c>
-      <c r="D237" s="9"/>
-      <c r="E237" s="17"/>
+      <c r="D237" s="8"/>
+      <c r="E237" s="19"/>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A238" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B238" s="5" t="s">
+      <c r="A238" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B238" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="C238" s="5">
+      <c r="C238" s="4">
         <v>1</v>
       </c>
-      <c r="D238" s="5"/>
-      <c r="E238" s="17">
+      <c r="D238" s="4"/>
+      <c r="E238" s="19">
         <v>78</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A239" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B239" s="2" t="s">
+      <c r="A239" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B239" t="s">
         <v>216</v>
       </c>
-      <c r="C239" s="2">
+      <c r="C239">
         <v>2</v>
       </c>
-      <c r="D239" s="2"/>
-      <c r="E239" s="17"/>
+      <c r="E239" s="19"/>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A240" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B240" s="2" t="s">
+      <c r="A240" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B240" t="s">
         <v>217</v>
       </c>
-      <c r="C240" s="2">
-        <v>3</v>
-      </c>
-      <c r="D240" s="2"/>
-      <c r="E240" s="17"/>
+      <c r="C240">
+        <v>3</v>
+      </c>
+      <c r="E240" s="19"/>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A241" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B241" s="2" t="s">
+      <c r="A241" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B241" t="s">
         <v>218</v>
       </c>
-      <c r="C241" s="2">
+      <c r="C241">
         <v>4</v>
       </c>
-      <c r="D241" s="2"/>
-      <c r="E241" s="17"/>
+      <c r="E241" s="19"/>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A242" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B242" s="2" t="s">
+      <c r="A242" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B242" t="s">
         <v>219</v>
       </c>
-      <c r="C242" s="2">
+      <c r="C242">
         <v>5</v>
       </c>
-      <c r="D242" s="2"/>
-      <c r="E242" s="17"/>
+      <c r="E242" s="19"/>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A243" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B243" s="2" t="s">
+      <c r="A243" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B243" t="s">
         <v>105</v>
       </c>
-      <c r="C243" s="2">
+      <c r="C243">
         <v>6</v>
       </c>
-      <c r="D243" s="2"/>
-      <c r="E243" s="17"/>
+      <c r="E243" s="19"/>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A244" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B244" s="2" t="s">
+      <c r="A244" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B244" t="s">
         <v>220</v>
       </c>
-      <c r="C244" s="2">
+      <c r="C244">
         <v>7</v>
       </c>
-      <c r="D244" s="2"/>
-      <c r="E244" s="17"/>
+      <c r="E244" s="19"/>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A245" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B245" s="2" t="s">
+      <c r="A245" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B245" t="s">
         <v>221</v>
       </c>
-      <c r="C245" s="2">
+      <c r="C245">
         <v>8</v>
       </c>
-      <c r="D245" s="2"/>
-      <c r="E245" s="17"/>
+      <c r="E245" s="19"/>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A246" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B246" s="2" t="s">
+      <c r="A246" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B246" t="s">
         <v>222</v>
       </c>
-      <c r="C246" s="2">
+      <c r="C246">
         <v>9</v>
       </c>
-      <c r="D246" s="2"/>
-      <c r="E246" s="17"/>
+      <c r="E246" s="19"/>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A247" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B247" s="2" t="s">
+      <c r="A247" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B247" t="s">
         <v>223</v>
       </c>
-      <c r="C247" s="2">
+      <c r="C247">
         <v>10</v>
       </c>
-      <c r="D247" s="2"/>
-      <c r="E247" s="17"/>
+      <c r="E247" s="19"/>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A248" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B248" s="2" t="s">
+      <c r="A248" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B248" t="s">
         <v>224</v>
       </c>
-      <c r="C248" s="2">
+      <c r="C248">
         <v>11</v>
       </c>
-      <c r="D248" s="2"/>
-      <c r="E248" s="17"/>
+      <c r="E248" s="19"/>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A249" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B249" s="2" t="s">
+      <c r="A249" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B249" t="s">
         <v>225</v>
       </c>
-      <c r="C249" s="2">
+      <c r="C249">
         <v>12</v>
       </c>
-      <c r="D249" s="2"/>
-      <c r="E249" s="17"/>
+      <c r="E249" s="19"/>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A250" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B250" s="2" t="s">
+      <c r="A250" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B250" t="s">
         <v>226</v>
       </c>
-      <c r="C250" s="2">
+      <c r="C250">
         <v>13</v>
       </c>
-      <c r="D250" s="2"/>
-      <c r="E250" s="17"/>
+      <c r="E250" s="19"/>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A251" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B251" s="2" t="s">
+      <c r="A251" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B251" t="s">
         <v>227</v>
       </c>
-      <c r="C251" s="2">
+      <c r="C251">
         <v>14</v>
       </c>
-      <c r="D251" s="2"/>
-      <c r="E251" s="17"/>
+      <c r="E251" s="19"/>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A252" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B252" s="2" t="s">
+      <c r="A252" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B252" t="s">
         <v>228</v>
       </c>
-      <c r="C252" s="2">
+      <c r="C252">
         <v>15</v>
       </c>
-      <c r="D252" s="2"/>
-      <c r="E252" s="17"/>
+      <c r="E252" s="19"/>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A253" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B253" s="2" t="s">
+      <c r="A253" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B253" t="s">
         <v>229</v>
       </c>
-      <c r="C253" s="2">
+      <c r="C253">
         <v>16</v>
       </c>
-      <c r="D253" s="2"/>
-      <c r="E253" s="17"/>
+      <c r="E253" s="19"/>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A254" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B254" s="2" t="s">
+      <c r="A254" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B254" t="s">
         <v>230</v>
       </c>
-      <c r="C254" s="2">
+      <c r="C254">
         <v>17</v>
       </c>
-      <c r="D254" s="2"/>
-      <c r="E254" s="17"/>
+      <c r="E254" s="19"/>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A255" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B255" s="2" t="s">
+      <c r="A255" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B255" t="s">
         <v>231</v>
       </c>
-      <c r="C255" s="2">
+      <c r="C255">
         <v>18</v>
       </c>
-      <c r="D255" s="2"/>
-      <c r="E255" s="17"/>
+      <c r="E255" s="19"/>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A256" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B256" s="2" t="s">
+      <c r="A256" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B256" t="s">
         <v>232</v>
       </c>
-      <c r="C256" s="2">
+      <c r="C256">
         <v>19</v>
       </c>
-      <c r="D256" s="2"/>
-      <c r="E256" s="17"/>
+      <c r="E256" s="19"/>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A257" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B257" s="2" t="s">
+      <c r="A257" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B257" t="s">
         <v>233</v>
       </c>
-      <c r="C257" s="2">
+      <c r="C257">
         <v>20</v>
       </c>
-      <c r="D257" s="2"/>
-      <c r="E257" s="17"/>
+      <c r="E257" s="19"/>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A258" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B258" s="2" t="s">
+      <c r="A258" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B258" t="s">
         <v>234</v>
       </c>
-      <c r="C258" s="2">
+      <c r="C258">
         <v>21</v>
       </c>
-      <c r="D258" s="2"/>
-      <c r="E258" s="17"/>
+      <c r="E258" s="19"/>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A259" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B259" s="2" t="s">
+      <c r="A259" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B259" t="s">
         <v>235</v>
       </c>
-      <c r="C259" s="2">
+      <c r="C259">
         <v>22</v>
       </c>
-      <c r="D259" s="2"/>
-      <c r="E259" s="17"/>
+      <c r="E259" s="19"/>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A260" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B260" s="2" t="s">
+      <c r="A260" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B260" t="s">
         <v>236</v>
       </c>
-      <c r="C260" s="2">
+      <c r="C260">
         <v>23</v>
       </c>
-      <c r="D260" s="2"/>
-      <c r="E260" s="17"/>
+      <c r="E260" s="19"/>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A261" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B261" s="2" t="s">
+      <c r="A261" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B261" t="s">
         <v>237</v>
       </c>
-      <c r="C261" s="2">
+      <c r="C261">
         <v>24</v>
       </c>
-      <c r="D261" s="2"/>
-      <c r="E261" s="17"/>
+      <c r="E261" s="19"/>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A262" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B262" s="2" t="s">
+      <c r="A262" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B262" t="s">
         <v>238</v>
       </c>
-      <c r="C262" s="2">
+      <c r="C262">
         <v>25</v>
       </c>
-      <c r="D262" s="2"/>
-      <c r="E262" s="17"/>
+      <c r="E262" s="19"/>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A263" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B263" s="2" t="s">
+      <c r="A263" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B263" t="s">
         <v>239</v>
       </c>
-      <c r="C263" s="2">
+      <c r="C263">
         <v>26</v>
       </c>
-      <c r="D263" s="2"/>
-      <c r="E263" s="17"/>
+      <c r="E263" s="19"/>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A264" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B264" s="2" t="s">
+      <c r="A264" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B264" t="s">
         <v>113</v>
       </c>
-      <c r="C264" s="2">
+      <c r="C264">
         <v>27</v>
       </c>
-      <c r="D264" s="2"/>
-      <c r="E264" s="17"/>
+      <c r="E264" s="19"/>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A265" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B265" s="2" t="s">
+      <c r="A265" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B265" t="s">
         <v>240</v>
       </c>
-      <c r="C265" s="2">
+      <c r="C265">
         <v>28</v>
       </c>
-      <c r="D265" s="2"/>
-      <c r="E265" s="17"/>
+      <c r="E265" s="19"/>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A266" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B266" s="2" t="s">
+      <c r="A266" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B266" t="s">
         <v>241</v>
       </c>
-      <c r="C266" s="2">
+      <c r="C266">
         <v>29</v>
       </c>
-      <c r="D266" s="2"/>
-      <c r="E266" s="17"/>
+      <c r="E266" s="19"/>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A267" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B267" s="2" t="s">
+      <c r="A267" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B267" t="s">
         <v>242</v>
       </c>
-      <c r="C267" s="2">
+      <c r="C267">
         <v>30</v>
       </c>
-      <c r="D267" s="2"/>
-      <c r="E267" s="17"/>
+      <c r="E267" s="19"/>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A268" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B268" s="2" t="s">
+      <c r="A268" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B268" t="s">
         <v>114</v>
       </c>
-      <c r="C268" s="2">
+      <c r="C268">
         <v>31</v>
       </c>
-      <c r="D268" s="2"/>
-      <c r="E268" s="17"/>
+      <c r="E268" s="19"/>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A269" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B269" s="2" t="s">
+      <c r="A269" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B269" t="s">
         <v>243</v>
       </c>
-      <c r="C269" s="2">
+      <c r="C269">
         <v>32</v>
       </c>
-      <c r="D269" s="2"/>
-      <c r="E269" s="17"/>
+      <c r="E269" s="19"/>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A270" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B270" s="2" t="s">
+      <c r="A270" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B270" t="s">
         <v>244</v>
       </c>
-      <c r="C270" s="2">
+      <c r="C270">
         <v>33</v>
       </c>
-      <c r="D270" s="2"/>
-      <c r="E270" s="17"/>
+      <c r="E270" s="19"/>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A271" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B271" s="2" t="s">
+      <c r="A271" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B271" t="s">
         <v>245</v>
       </c>
-      <c r="C271" s="2">
+      <c r="C271">
         <v>34</v>
       </c>
-      <c r="D271" s="2"/>
-      <c r="E271" s="17"/>
+      <c r="E271" s="19"/>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A272" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B272" s="2" t="s">
+      <c r="A272" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B272" t="s">
         <v>115</v>
       </c>
-      <c r="C272" s="2">
+      <c r="C272">
         <v>35</v>
       </c>
-      <c r="D272" s="2"/>
-      <c r="E272" s="17"/>
+      <c r="E272" s="19"/>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A273" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B273" s="2" t="s">
+      <c r="A273" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B273" t="s">
         <v>246</v>
       </c>
-      <c r="C273" s="2">
+      <c r="C273">
         <v>36</v>
       </c>
-      <c r="D273" s="2"/>
-      <c r="E273" s="17"/>
+      <c r="E273" s="19"/>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A274" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B274" s="2" t="s">
+      <c r="A274" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B274" t="s">
         <v>247</v>
       </c>
-      <c r="C274" s="2">
+      <c r="C274">
         <v>37</v>
       </c>
-      <c r="D274" s="2"/>
-      <c r="E274" s="17"/>
+      <c r="E274" s="19"/>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A275" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B275" s="2" t="s">
+      <c r="A275" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B275" t="s">
         <v>118</v>
       </c>
-      <c r="C275" s="2">
+      <c r="C275">
         <v>38</v>
       </c>
-      <c r="D275" s="2"/>
-      <c r="E275" s="17"/>
+      <c r="E275" s="19"/>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A276" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B276" s="2" t="s">
+      <c r="A276" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B276" t="s">
         <v>121</v>
       </c>
-      <c r="C276" s="2">
+      <c r="C276">
         <v>39</v>
       </c>
-      <c r="D276" s="2"/>
-      <c r="E276" s="17"/>
+      <c r="E276" s="19"/>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A277" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B277" s="2" t="s">
+      <c r="A277" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B277" t="s">
         <v>248</v>
       </c>
-      <c r="C277" s="2">
+      <c r="C277">
         <v>40</v>
       </c>
-      <c r="D277" s="2"/>
-      <c r="E277" s="17"/>
+      <c r="E277" s="19"/>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A278" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B278" s="2" t="s">
+      <c r="A278" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B278" t="s">
         <v>249</v>
       </c>
-      <c r="C278" s="2">
+      <c r="C278">
         <v>41</v>
       </c>
-      <c r="D278" s="2"/>
-      <c r="E278" s="17"/>
+      <c r="E278" s="19"/>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A279" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B279" s="2" t="s">
+      <c r="A279" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B279" t="s">
         <v>250</v>
       </c>
-      <c r="C279" s="2">
+      <c r="C279">
         <v>42</v>
       </c>
-      <c r="D279" s="2"/>
-      <c r="E279" s="17"/>
+      <c r="E279" s="19"/>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A280" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B280" s="2" t="s">
+      <c r="A280" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B280" t="s">
         <v>251</v>
       </c>
-      <c r="C280" s="2">
+      <c r="C280">
         <v>43</v>
       </c>
-      <c r="D280" s="2"/>
-      <c r="E280" s="17"/>
+      <c r="E280" s="19"/>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A281" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B281" s="2" t="s">
+      <c r="A281" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B281" t="s">
         <v>252</v>
       </c>
-      <c r="C281" s="2">
-        <v>44</v>
-      </c>
-      <c r="D281" s="2"/>
-      <c r="E281" s="17"/>
+      <c r="C281">
+        <v>44</v>
+      </c>
+      <c r="E281" s="19"/>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A282" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B282" s="2" t="s">
+      <c r="A282" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B282" t="s">
         <v>253</v>
       </c>
-      <c r="C282" s="2">
+      <c r="C282">
         <v>45</v>
       </c>
-      <c r="D282" s="2"/>
-      <c r="E282" s="17"/>
+      <c r="E282" s="19"/>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A283" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B283" s="2" t="s">
+      <c r="A283" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B283" t="s">
         <v>254</v>
       </c>
-      <c r="C283" s="2">
+      <c r="C283">
         <v>46</v>
       </c>
-      <c r="D283" s="2"/>
-      <c r="E283" s="17"/>
+      <c r="E283" s="19"/>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A284" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B284" s="2" t="s">
+      <c r="A284" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B284" t="s">
         <v>255</v>
       </c>
-      <c r="C284" s="2">
+      <c r="C284">
         <v>47</v>
       </c>
-      <c r="D284" s="2"/>
-      <c r="E284" s="17"/>
+      <c r="E284" s="19"/>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A285" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B285" s="2" t="s">
+      <c r="A285" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B285" t="s">
         <v>256</v>
       </c>
-      <c r="C285" s="2">
+      <c r="C285">
         <v>48</v>
       </c>
-      <c r="D285" s="2"/>
-      <c r="E285" s="17"/>
+      <c r="E285" s="19"/>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A286" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B286" s="2" t="s">
+      <c r="A286" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B286" t="s">
         <v>126</v>
       </c>
-      <c r="C286" s="2">
+      <c r="C286">
         <v>49</v>
       </c>
-      <c r="D286" s="2"/>
-      <c r="E286" s="17"/>
+      <c r="E286" s="19"/>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A287" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B287" s="2" t="s">
+      <c r="A287" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B287" t="s">
         <v>257</v>
       </c>
-      <c r="C287" s="2">
+      <c r="C287">
         <v>50</v>
       </c>
-      <c r="D287" s="2"/>
-      <c r="E287" s="17"/>
+      <c r="E287" s="19"/>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A288" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B288" s="2" t="s">
+      <c r="A288" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B288" t="s">
         <v>127</v>
       </c>
-      <c r="C288" s="2">
+      <c r="C288">
         <v>51</v>
       </c>
-      <c r="D288" s="2"/>
-      <c r="E288" s="17"/>
+      <c r="E288" s="19"/>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A289" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B289" s="2" t="s">
+      <c r="A289" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B289" t="s">
         <v>258</v>
       </c>
-      <c r="C289" s="2">
+      <c r="C289">
         <v>52</v>
       </c>
-      <c r="D289" s="2"/>
-      <c r="E289" s="17"/>
+      <c r="E289" s="19"/>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A290" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B290" s="2" t="s">
+      <c r="A290" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B290" t="s">
         <v>259</v>
       </c>
-      <c r="C290" s="2">
+      <c r="C290">
         <v>53</v>
       </c>
-      <c r="D290" s="2"/>
-      <c r="E290" s="17"/>
+      <c r="E290" s="19"/>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A291" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B291" s="2" t="s">
+      <c r="A291" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B291" t="s">
         <v>260</v>
       </c>
-      <c r="C291" s="2">
+      <c r="C291">
         <v>54</v>
       </c>
-      <c r="D291" s="2"/>
-      <c r="E291" s="17"/>
+      <c r="E291" s="19"/>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A292" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B292" s="2" t="s">
+      <c r="A292" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B292" t="s">
         <v>261</v>
       </c>
-      <c r="C292" s="2">
+      <c r="C292">
         <v>55</v>
       </c>
-      <c r="D292" s="2"/>
-      <c r="E292" s="17"/>
+      <c r="E292" s="19"/>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A293" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B293" s="2" t="s">
+      <c r="A293" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B293" t="s">
         <v>262</v>
       </c>
-      <c r="C293" s="2">
+      <c r="C293">
         <v>56</v>
       </c>
-      <c r="D293" s="2"/>
-      <c r="E293" s="17"/>
+      <c r="E293" s="19"/>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A294" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B294" s="2" t="s">
+      <c r="A294" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B294" t="s">
         <v>263</v>
       </c>
-      <c r="C294" s="2">
+      <c r="C294">
         <v>57</v>
       </c>
-      <c r="D294" s="2"/>
-      <c r="E294" s="17"/>
+      <c r="E294" s="19"/>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A295" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B295" s="2" t="s">
+      <c r="A295" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B295" t="s">
         <v>264</v>
       </c>
-      <c r="C295" s="2">
+      <c r="C295">
         <v>58</v>
       </c>
-      <c r="D295" s="2"/>
-      <c r="E295" s="17"/>
+      <c r="E295" s="19"/>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A296" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B296" s="2" t="s">
+      <c r="A296" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B296" t="s">
         <v>265</v>
       </c>
-      <c r="C296" s="2">
+      <c r="C296">
         <v>59</v>
       </c>
-      <c r="D296" s="2"/>
-      <c r="E296" s="17"/>
+      <c r="E296" s="19"/>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A297" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B297" s="2" t="s">
+      <c r="A297" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B297" t="s">
         <v>266</v>
       </c>
-      <c r="C297" s="2">
+      <c r="C297">
         <v>60</v>
       </c>
-      <c r="D297" s="2"/>
-      <c r="E297" s="17"/>
+      <c r="E297" s="19"/>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A298" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B298" s="2" t="s">
+      <c r="A298" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B298" t="s">
         <v>267</v>
       </c>
-      <c r="C298" s="2">
+      <c r="C298">
         <v>61</v>
       </c>
-      <c r="D298" s="2"/>
-      <c r="E298" s="17"/>
+      <c r="E298" s="19"/>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A299" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B299" s="2" t="s">
+      <c r="A299" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B299" t="s">
         <v>268</v>
       </c>
-      <c r="C299" s="2">
+      <c r="C299">
         <v>62</v>
       </c>
-      <c r="D299" s="2"/>
-      <c r="E299" s="17"/>
+      <c r="E299" s="19"/>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A300" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B300" s="2" t="s">
+      <c r="A300" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B300" t="s">
         <v>269</v>
       </c>
-      <c r="C300" s="2">
+      <c r="C300">
         <v>63</v>
       </c>
-      <c r="D300" s="2"/>
-      <c r="E300" s="17"/>
+      <c r="E300" s="19"/>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A301" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B301" s="2" t="s">
+      <c r="A301" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B301" t="s">
         <v>270</v>
       </c>
-      <c r="C301" s="2">
+      <c r="C301">
         <v>64</v>
       </c>
-      <c r="D301" s="2"/>
-      <c r="E301" s="17"/>
+      <c r="E301" s="19"/>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A302" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B302" s="2" t="s">
+      <c r="A302" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B302" t="s">
         <v>271</v>
       </c>
-      <c r="C302" s="2">
+      <c r="C302">
         <v>65</v>
       </c>
-      <c r="D302" s="2"/>
-      <c r="E302" s="17"/>
+      <c r="E302" s="19"/>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A303" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B303" s="2" t="s">
+      <c r="A303" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B303" t="s">
         <v>272</v>
       </c>
-      <c r="C303" s="2">
+      <c r="C303">
         <v>66</v>
       </c>
-      <c r="D303" s="2"/>
-      <c r="E303" s="17"/>
+      <c r="E303" s="19"/>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A304" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B304" s="2" t="s">
+      <c r="A304" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B304" t="s">
         <v>273</v>
       </c>
-      <c r="C304" s="2">
+      <c r="C304">
         <v>67</v>
       </c>
-      <c r="D304" s="2"/>
-      <c r="E304" s="17"/>
-    </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A305" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B305" s="2" t="s">
+      <c r="E304" s="19"/>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A305" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B305" t="s">
         <v>274</v>
       </c>
-      <c r="C305" s="2">
+      <c r="C305">
         <v>68</v>
       </c>
-      <c r="D305" s="2"/>
-      <c r="E305" s="17"/>
-    </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A306" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B306" s="2" t="s">
+      <c r="E305" s="19"/>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A306" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B306" t="s">
         <v>275</v>
       </c>
-      <c r="C306" s="2">
+      <c r="C306">
         <v>69</v>
       </c>
-      <c r="D306" s="2"/>
-      <c r="E306" s="17"/>
-    </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A307" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B307" s="2" t="s">
+      <c r="E306" s="19"/>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A307" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B307" t="s">
         <v>276</v>
       </c>
-      <c r="C307" s="2">
+      <c r="C307">
         <v>70</v>
       </c>
-      <c r="D307" s="2"/>
-      <c r="E307" s="17"/>
-    </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A308" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B308" s="2" t="s">
+      <c r="E307" s="19"/>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A308" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B308" t="s">
         <v>277</v>
       </c>
-      <c r="C308" s="2">
+      <c r="C308">
         <v>71</v>
       </c>
-      <c r="D308" s="2"/>
-      <c r="E308" s="17"/>
-    </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A309" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B309" s="2" t="s">
+      <c r="E308" s="19"/>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A309" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B309" t="s">
         <v>278</v>
       </c>
-      <c r="C309" s="2">
+      <c r="C309">
         <v>72</v>
       </c>
-      <c r="D309" s="2"/>
-      <c r="E309" s="17"/>
-    </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A310" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="B310" s="9" t="s">
+      <c r="E309" s="19"/>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A310" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B310" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="C310" s="9">
+      <c r="C310" s="8">
         <v>73</v>
       </c>
-      <c r="D310" s="9"/>
-      <c r="E310" s="17"/>
-    </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A311" s="4" t="s">
+      <c r="D310" s="8"/>
+      <c r="E310" s="19"/>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A311" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B311" s="5" t="s">
+      <c r="B311" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="C311" s="5">
+      <c r="C311" s="4">
         <v>1</v>
       </c>
-      <c r="D311" s="5"/>
-      <c r="E311" s="17">
+      <c r="D311" s="4"/>
+      <c r="E311" s="19">
         <v>4</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A312" s="7" t="s">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A312" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="B312" s="2" t="s">
+      <c r="B312" t="s">
         <v>282</v>
       </c>
-      <c r="C312" s="2">
+      <c r="C312">
         <v>2</v>
       </c>
-      <c r="D312" s="2"/>
-      <c r="E312" s="17"/>
-    </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A313" s="7" t="s">
+      <c r="E312" s="19"/>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A313" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="B313" s="3" t="s">
+      <c r="B313" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C313" s="3">
-        <v>3</v>
-      </c>
-      <c r="D313" s="2">
-        <v>3</v>
-      </c>
-      <c r="E313" s="17"/>
-    </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A314" s="7" t="s">
+      <c r="C313" s="2">
+        <v>3</v>
+      </c>
+      <c r="D313">
+        <v>3</v>
+      </c>
+      <c r="E313" s="19"/>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A314" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="B314" s="3" t="s">
+      <c r="B314" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="C314" s="3">
+      <c r="C314" s="2">
         <v>4</v>
       </c>
-      <c r="D314" s="2">
-        <v>3</v>
-      </c>
-      <c r="E314" s="17"/>
-    </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A315" s="7" t="s">
+      <c r="D314">
+        <v>3</v>
+      </c>
+      <c r="E314" s="19"/>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A315" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="B315" s="3" t="s">
+      <c r="B315" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C315" s="3">
+      <c r="C315" s="2">
         <v>5</v>
       </c>
-      <c r="D315" s="2">
-        <v>3</v>
-      </c>
-      <c r="E315" s="17"/>
-    </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A316" s="8" t="s">
+      <c r="D315">
+        <v>3</v>
+      </c>
+      <c r="E315" s="19"/>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A316" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="B316" s="9" t="s">
+      <c r="B316" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="C316" s="9">
+      <c r="C316" s="8">
         <v>6</v>
       </c>
-      <c r="D316" s="9">
+      <c r="D316" s="8">
         <v>6</v>
       </c>
-      <c r="E316" s="17"/>
-    </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A317" s="4" t="s">
+      <c r="E316" s="19"/>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A317" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="B317" s="6" t="s">
+      <c r="B317" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="C317" s="6">
+      <c r="C317" s="5">
         <v>1</v>
       </c>
-      <c r="D317" s="5">
+      <c r="D317" s="4">
         <v>1</v>
       </c>
-      <c r="E317" s="17">
+      <c r="E317" s="19">
         <v>6</v>
       </c>
-      <c r="F317" s="7">
-        <v>3</v>
-      </c>
-      <c r="G317" s="2">
+      <c r="F317" s="6">
+        <v>3</v>
+      </c>
+      <c r="G317">
         <v>80</v>
       </c>
-    </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A318" s="7" t="s">
+      <c r="I317" s="15" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A318" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="B318" s="3" t="s">
+      <c r="B318" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C318" s="3">
+      <c r="C318" s="2">
         <v>2</v>
       </c>
-      <c r="D318" s="18">
+      <c r="D318">
         <v>2</v>
       </c>
-      <c r="E318" s="17"/>
-      <c r="F318" s="7">
+      <c r="E318" s="19"/>
+      <c r="F318" s="6">
         <v>55</v>
       </c>
-      <c r="G318" s="20">
+      <c r="G318" s="17">
         <v>105</v>
       </c>
-    </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A319" s="7" t="s">
+      <c r="I318" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A319" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="B319" s="3" t="s">
+      <c r="B319" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="C319" s="3">
-        <v>3</v>
-      </c>
-      <c r="D319" s="18">
+      <c r="C319" s="2">
+        <v>3</v>
+      </c>
+      <c r="D319">
         <v>2</v>
       </c>
-      <c r="E319" s="17"/>
-      <c r="F319" s="7">
+      <c r="E319" s="19"/>
+      <c r="F319" s="6">
         <v>50</v>
       </c>
-      <c r="G319" s="20"/>
-    </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A320" s="7" t="s">
+      <c r="G319" s="17"/>
+      <c r="I319" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A320" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="B320" s="3" t="s">
+      <c r="B320" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C320" s="3">
+      <c r="C320" s="2">
         <v>4</v>
       </c>
-      <c r="D320" s="18">
+      <c r="D320">
         <v>4</v>
       </c>
-      <c r="E320" s="17"/>
-      <c r="F320" s="7">
+      <c r="E320" s="19"/>
+      <c r="F320" s="6">
         <v>180</v>
       </c>
-      <c r="G320" s="20">
+      <c r="G320" s="17">
         <v>185</v>
       </c>
-    </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A321" s="7" t="s">
+      <c r="I320" s="15" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A321" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="B321" s="3" t="s">
+      <c r="B321" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C321" s="3">
+      <c r="C321" s="2">
         <v>5</v>
       </c>
-      <c r="D321" s="18">
+      <c r="D321">
         <v>4</v>
       </c>
-      <c r="E321" s="17"/>
-      <c r="F321" s="7">
-        <v>3</v>
-      </c>
-      <c r="G321" s="20"/>
-    </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A322" s="7" t="s">
+      <c r="E321" s="19"/>
+      <c r="F321" s="6">
+        <v>3</v>
+      </c>
+      <c r="G321" s="17"/>
+      <c r="I321" s="15" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A322" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="B322" s="2" t="s">
+      <c r="B322" t="s">
         <v>293</v>
       </c>
-      <c r="C322" s="2">
+      <c r="C322">
         <v>6</v>
       </c>
-      <c r="D322" s="18">
+      <c r="D322">
         <v>6</v>
       </c>
-      <c r="E322" s="17"/>
-      <c r="F322" s="7">
+      <c r="E322" s="19"/>
+      <c r="F322" s="6">
         <v>30</v>
       </c>
-      <c r="G322" s="18">
+      <c r="G322">
         <v>30</v>
       </c>
-    </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A323" s="7" t="s">
+      <c r="I322" s="8" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A323" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="B323" s="3" t="s">
+      <c r="B323" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="C323" s="3">
+      <c r="C323" s="2">
         <v>7</v>
       </c>
-      <c r="D323" s="18">
+      <c r="D323">
         <v>1</v>
       </c>
-      <c r="E323" s="17"/>
-      <c r="F323" s="7">
+      <c r="E323" s="19"/>
+      <c r="F323" s="6">
         <v>75</v>
       </c>
-      <c r="G323" s="2" t="s">
+      <c r="G323" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A324" s="7" t="s">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A324" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="B324" s="2" t="s">
+      <c r="B324" t="s">
         <v>295</v>
       </c>
-      <c r="C324" s="2">
+      <c r="C324">
         <v>8</v>
       </c>
-      <c r="D324" s="18">
+      <c r="D324">
         <v>8</v>
       </c>
-      <c r="E324" s="17"/>
-      <c r="F324" s="7">
+      <c r="E324" s="19"/>
+      <c r="F324" s="6">
         <v>50</v>
       </c>
-      <c r="G324" s="18">
+      <c r="G324">
         <v>80</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A325" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="B325" s="9" t="s">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A325" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="B325" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="C325" s="9">
+      <c r="C325" s="8">
         <v>9</v>
       </c>
-      <c r="D325" s="9">
+      <c r="D325" s="8">
         <v>9</v>
       </c>
-      <c r="E325" s="17"/>
-      <c r="F325" s="7">
-        <v>3</v>
-      </c>
-      <c r="G325" s="18">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A326" s="4" t="s">
+      <c r="E325" s="19"/>
+      <c r="F325" s="6">
+        <v>3</v>
+      </c>
+      <c r="G325">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A326" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="B326" s="6" t="s">
+      <c r="B326" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="C326" s="6">
+      <c r="C326" s="5">
         <v>1</v>
       </c>
-      <c r="D326" s="18">
+      <c r="D326">
         <v>1</v>
       </c>
-      <c r="E326" s="17">
+      <c r="E326" s="19">
         <v>6</v>
       </c>
-      <c r="G326" s="2">
+      <c r="G326">
         <f>SUM(G317:G325)</f>
         <v>483</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A327" s="7" t="s">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A327" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="B327" s="2" t="s">
+      <c r="B327" t="s">
         <v>299</v>
       </c>
-      <c r="C327" s="2">
+      <c r="C327">
         <v>2</v>
       </c>
-      <c r="D327" s="18">
+      <c r="D327">
         <v>2</v>
       </c>
-      <c r="E327" s="17"/>
-    </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A328" s="7" t="s">
+      <c r="E327" s="19"/>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A328" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="B328" s="2" t="s">
+      <c r="B328" t="s">
         <v>300</v>
       </c>
-      <c r="C328" s="2">
-        <v>3</v>
-      </c>
-      <c r="D328" s="18">
-        <v>3</v>
-      </c>
-      <c r="E328" s="17"/>
-    </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A329" s="7" t="s">
+      <c r="C328">
+        <v>3</v>
+      </c>
+      <c r="D328">
+        <v>3</v>
+      </c>
+      <c r="E328" s="19"/>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A329" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="B329" s="2" t="s">
+      <c r="B329" t="s">
         <v>301</v>
       </c>
-      <c r="C329" s="2">
+      <c r="C329">
         <v>4</v>
       </c>
-      <c r="D329" s="18">
+      <c r="D329">
         <v>4</v>
       </c>
-      <c r="E329" s="17"/>
-    </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A330" s="7" t="s">
+      <c r="E329" s="19"/>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A330" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="B330" s="2" t="s">
+      <c r="B330" t="s">
         <v>302</v>
       </c>
-      <c r="C330" s="2">
+      <c r="C330">
         <v>5</v>
       </c>
-      <c r="D330" s="18">
+      <c r="D330">
         <v>5</v>
       </c>
-      <c r="E330" s="17"/>
-    </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A331" s="7" t="s">
+      <c r="E330" s="19"/>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A331" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="B331" s="2" t="s">
+      <c r="B331" t="s">
         <v>303</v>
       </c>
-      <c r="C331" s="2">
+      <c r="C331">
         <v>6</v>
       </c>
-      <c r="D331" s="18">
+      <c r="D331">
         <v>6</v>
       </c>
-      <c r="E331" s="17"/>
-    </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A332" s="8" t="s">
+      <c r="E331" s="19"/>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A332" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="B332" s="10" t="s">
+      <c r="B332" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="C332" s="10">
+      <c r="C332" s="9">
         <v>7</v>
       </c>
-      <c r="D332" s="9">
+      <c r="D332" s="8">
         <v>1</v>
       </c>
-      <c r="E332" s="17"/>
-    </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A333" s="4" t="s">
+      <c r="E332" s="19"/>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A333" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="B333" s="6" t="s">
+      <c r="B333" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="C333" s="6">
+      <c r="C333" s="5">
         <v>1</v>
       </c>
-      <c r="D333" s="5">
+      <c r="D333" s="4">
         <v>1</v>
       </c>
-      <c r="E333" s="17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A334" s="7" t="s">
+      <c r="E333" s="19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A334" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="B334" s="3" t="s">
+      <c r="B334" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C334" s="3">
+      <c r="C334" s="2">
         <v>2</v>
       </c>
-      <c r="D334" s="2">
+      <c r="D334">
         <v>1</v>
       </c>
-      <c r="E334" s="17"/>
-    </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A335" s="7" t="s">
+      <c r="E334" s="19"/>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A335" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="B335" s="2" t="s">
+      <c r="B335" t="s">
         <v>308</v>
       </c>
-      <c r="C335" s="2">
-        <v>3</v>
-      </c>
-      <c r="D335" s="2">
-        <v>3</v>
-      </c>
-      <c r="E335" s="17"/>
-    </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A336" s="8" t="s">
+      <c r="C335">
+        <v>3</v>
+      </c>
+      <c r="D335">
+        <v>3</v>
+      </c>
+      <c r="E335" s="19"/>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A336" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="B336" s="9" t="s">
+      <c r="B336" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="C336" s="9">
+      <c r="C336" s="8">
         <v>4</v>
       </c>
-      <c r="D336" s="9">
+      <c r="D336" s="8">
         <v>4</v>
       </c>
-      <c r="E336" s="17"/>
+      <c r="E336" s="19"/>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A337" s="4" t="s">
+      <c r="A337" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B337" s="5" t="s">
+      <c r="B337" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="C337" s="5">
+      <c r="C337" s="4">
         <v>1</v>
       </c>
-      <c r="D337" s="5"/>
-      <c r="E337" s="15">
+      <c r="D337" s="4"/>
+      <c r="E337" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A338" s="8" t="s">
+      <c r="A338" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="B338" s="9" t="s">
+      <c r="B338" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="C338" s="9">
+      <c r="C338" s="8">
         <v>2</v>
       </c>
-      <c r="D338" s="9"/>
-      <c r="E338" s="15"/>
+      <c r="D338" s="8"/>
+      <c r="E338" s="20"/>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E339" s="2"/>
-      <c r="F339" s="2"/>
+      <c r="E339"/>
+      <c r="F339"/>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E340" s="2"/>
-      <c r="F340" s="2"/>
+      <c r="E340"/>
+      <c r="F340"/>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E341" s="2"/>
-      <c r="F341" s="2"/>
+      <c r="E341"/>
+      <c r="F341"/>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E342" s="2"/>
-      <c r="F342" s="2"/>
+      <c r="E342"/>
+      <c r="F342"/>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E343" s="2"/>
-      <c r="F343" s="2"/>
+      <c r="E343"/>
+      <c r="F343"/>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E344" s="2"/>
-      <c r="F344" s="2"/>
+      <c r="E344"/>
+      <c r="F344"/>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E345" s="2"/>
-      <c r="F345" s="2"/>
+      <c r="E345"/>
+      <c r="F345"/>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E346" s="2"/>
-      <c r="F346" s="2"/>
+      <c r="E346"/>
+      <c r="F346"/>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E347" s="2"/>
-      <c r="F347" s="2"/>
+      <c r="E347"/>
+      <c r="F347"/>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E348" s="2"/>
-      <c r="F348" s="2"/>
+      <c r="E348"/>
+      <c r="F348"/>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E349" s="2"/>
-      <c r="F349" s="2"/>
+      <c r="E349"/>
+      <c r="F349"/>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E350" s="2"/>
-      <c r="F350" s="2"/>
+      <c r="E350"/>
+      <c r="F350"/>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E351" s="2"/>
-      <c r="F351" s="2"/>
+      <c r="E351"/>
+      <c r="F351"/>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E352" s="2"/>
-      <c r="F352" s="2"/>
+      <c r="E352"/>
+      <c r="F352"/>
     </row>
     <row r="353" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E353" s="2"/>
-      <c r="F353" s="2"/>
+      <c r="E353"/>
+      <c r="F353"/>
     </row>
     <row r="354" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E354" s="8"/>
+      <c r="E354" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="E326:E332"/>
+    <mergeCell ref="E317:E325"/>
+    <mergeCell ref="E333:E336"/>
+    <mergeCell ref="E337:E338"/>
+    <mergeCell ref="E311:E316"/>
+    <mergeCell ref="E238:E310"/>
+    <mergeCell ref="E160:E237"/>
+    <mergeCell ref="E122:E128"/>
+    <mergeCell ref="E119:E121"/>
+    <mergeCell ref="E129:E159"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="G318:G319"/>
     <mergeCell ref="G320:G321"/>
     <mergeCell ref="F129:F159"/>
     <mergeCell ref="F122:F128"/>
     <mergeCell ref="F119:F121"/>
-    <mergeCell ref="E238:E310"/>
-    <mergeCell ref="E160:E237"/>
-    <mergeCell ref="E122:E128"/>
-    <mergeCell ref="E119:E121"/>
-    <mergeCell ref="E129:E159"/>
-    <mergeCell ref="E326:E332"/>
-    <mergeCell ref="E317:E325"/>
-    <mergeCell ref="E333:E336"/>
-    <mergeCell ref="E337:E338"/>
-    <mergeCell ref="E311:E316"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_exploration/Encoding/categorical_value_mapping.xlsx
+++ b/data_exploration/Encoding/categorical_value_mapping.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\Documents\GitHub Repository\Patient_Feedback\data_exploration\Encoding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204A4225-78C6-4803-AA30-D087CCAF30D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B70A206-826C-4067-B0CE-1F0DEC703D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$C$1:$F$155</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="389">
   <si>
     <t>Column</t>
   </si>
@@ -357,12 +361,6 @@
   </si>
   <si>
     <t>Bureaucracy</t>
-  </si>
-  <si>
-    <t>Clinician -Errors</t>
-  </si>
-  <si>
-    <t>Delay -Access</t>
   </si>
   <si>
     <t>Delay -access</t>
@@ -1001,13 +999,223 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Clinician - Errors</t>
+  </si>
+  <si>
+    <t>Delay - Access</t>
+  </si>
+  <si>
+    <t>إعطاء مواعيد صور متأخرة</t>
+  </si>
+  <si>
+    <t>Delay Access (Imaging Appointment)</t>
+  </si>
+  <si>
+    <t>Equipment &amp; Supplies Problems (OR, Echo..)</t>
+  </si>
+  <si>
+    <t>إجراءات معقّدة/موافقات/تكاليف</t>
+  </si>
+  <si>
+    <t>Complex Procedures / Approvals / Costs</t>
+  </si>
+  <si>
+    <t>إنتظار الإجراءات الطبية(صور,فحوصات..)</t>
+  </si>
+  <si>
+    <t>Delay Procedure (Waiting for Imaging, LAB Tests..)</t>
+  </si>
+  <si>
+    <t>إهمال عام(الرعاية الشخصية,الرعاية الصحية,بيئة آمنة,الدعم النفسي..)</t>
+  </si>
+  <si>
+    <t>Neglect - General (Basic Care, Medical Care, Safe Environment..)</t>
+  </si>
+  <si>
+    <t>اعتراض حول آلية الزيارة</t>
+  </si>
+  <si>
+    <t>الإنتظار للمعاينة</t>
+  </si>
+  <si>
+    <t>Delay Access (Waiting for Consultation..)</t>
+  </si>
+  <si>
+    <t>Daily Doctor Visits (Attending / Consulting Physician)</t>
+  </si>
+  <si>
+    <t>Noise (Accompagnant, Patients..)</t>
+  </si>
+  <si>
+    <t>Noise (Workshop..)</t>
+  </si>
+  <si>
+    <t>Noise (Devices, Doors..)</t>
+  </si>
+  <si>
+    <t>Respect for Beliefs</t>
+  </si>
+  <si>
+    <t>انتظار الأدوار</t>
+  </si>
+  <si>
+    <t>بطء تنظيف طارىء</t>
+  </si>
+  <si>
+    <t>Surgical Procedures Delayed</t>
+  </si>
+  <si>
+    <t>Delay Medical Procedure</t>
+  </si>
+  <si>
+    <t>Delay Transfer (Room..)</t>
+  </si>
+  <si>
+    <t>Delayed Procedure (Imaging Reports..)</t>
+  </si>
+  <si>
+    <t>Delay Procedure (Medical Attendance..)</t>
+  </si>
+  <si>
+    <t>Delayed Nurse Call</t>
+  </si>
+  <si>
+    <t>Delay - General</t>
+  </si>
+  <si>
+    <t>تحويل المريض من الطوارئ إلى العيادات</t>
+  </si>
+  <si>
+    <t>Nutritional Problem (Cold Food, Insufficient..)</t>
+  </si>
+  <si>
+    <t>IV Problem (IV Insertion Error..)</t>
+  </si>
+  <si>
+    <t>Technical Skills of Staff (That Compromise Safety)</t>
+  </si>
+  <si>
+    <t>Error - Medication</t>
+  </si>
+  <si>
+    <t>Error Procedure (Lab, X-Ray..)</t>
+  </si>
+  <si>
+    <t>Coordination Failure (Team, Other Departments..)</t>
+  </si>
+  <si>
+    <t>خلل تنسيق طبي(الأطباء,التمريض..)</t>
+  </si>
+  <si>
+    <t>Teamwork Problem (Doctors, Nursing..)</t>
+  </si>
+  <si>
+    <t>Coordination Problem (Team, Other Departments..)</t>
+  </si>
+  <si>
+    <t>Failure to Provide (Information, Treatment..)</t>
+  </si>
+  <si>
+    <t>Nursing Care Problems (Diaper, Bath..)</t>
+  </si>
+  <si>
+    <t>Scheduling Error</t>
+  </si>
+  <si>
+    <t>Dismissing Patients</t>
+  </si>
+  <si>
+    <t>Noise (Employee..)</t>
+  </si>
+  <si>
+    <t>طلبات الدرجة الأولى</t>
+  </si>
+  <si>
+    <t>Documentation Problem (Devices, Discharge..)</t>
+  </si>
+  <si>
+    <t>Phone Calls Not Answered</t>
+  </si>
+  <si>
+    <t>Failure to Respond (Nurse Call Unfunctional)</t>
+  </si>
+  <si>
+    <t>عدم الموافقة(الخطة العلاجية,قرار المغادرة..)</t>
+  </si>
+  <si>
+    <t>Failure to Agree (Treatment Plan, Discharge Decision..)</t>
+  </si>
+  <si>
+    <t>Failure to Provide (Assistant Visit Issue..)</t>
+  </si>
+  <si>
+    <t>Patient Cases Not Organized</t>
+  </si>
+  <si>
+    <t>Bed Unavailability</t>
+  </si>
+  <si>
+    <t>Accommodation Problems (Devices, Beds..)</t>
+  </si>
+  <si>
+    <t>Accommodation Problems (Area Problem..)</t>
+  </si>
+  <si>
+    <t>Accommodation Problems (Tissue, Basket..)</t>
+  </si>
+  <si>
+    <t>Problems in the Facilities (Pillows, Covers..)</t>
+  </si>
+  <si>
+    <t>Hygiene Problem (Room..)</t>
+  </si>
+  <si>
+    <t>Security Problem (Lost..)</t>
+  </si>
+  <si>
+    <t>Complications (Surgical Complication)</t>
+  </si>
+  <si>
+    <t>Delay Access (Clinic Appointment)</t>
+  </si>
+  <si>
+    <t>IV Problem (Nursing Skills..)</t>
+  </si>
+  <si>
+    <t>Technician Skills Deficiency (Tests..)</t>
+  </si>
+  <si>
+    <t>Noise</t>
+  </si>
+  <si>
+    <t>Parent ID Category</t>
+  </si>
+  <si>
+    <t>Parent ID SubCategory</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>Accommodation</t>
+  </si>
+  <si>
+    <t>Delay - Procedure</t>
+  </si>
+  <si>
+    <t>Error - General</t>
+  </si>
+  <si>
+    <t>Accommodation Problems(Air Conditioning..)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1025,6 +1233,14 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1142,7 +1358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1165,6 +1381,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1174,10 +1396,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1505,10 +1730,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1521,10 +1746,10 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="G2" s="16" t="s">
-        <v>314</v>
-      </c>
-      <c r="H2" s="16"/>
+      <c r="G2" s="18" t="s">
+        <v>312</v>
+      </c>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -1537,10 +1762,10 @@
         <v>2</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1554,7 +1779,7 @@
         <v>3</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H4" s="11"/>
     </row>
@@ -1637,7 +1862,7 @@
         <v>8</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -1686,7 +1911,7 @@
         <v>11</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -1752,7 +1977,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -1784,7 +2009,7 @@
         <v>17</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H18" s="11"/>
     </row>
@@ -2906,10 +3131,10 @@
         <v>1</v>
       </c>
       <c r="D119" s="4"/>
-      <c r="E119" s="20">
+      <c r="E119" s="17">
         <v>3</v>
       </c>
-      <c r="F119" s="18"/>
+      <c r="F119" s="20"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
@@ -2921,8 +3146,8 @@
       <c r="C120">
         <v>2</v>
       </c>
-      <c r="E120" s="20"/>
-      <c r="F120" s="18"/>
+      <c r="E120" s="17"/>
+      <c r="F120" s="20"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
@@ -2935,8 +3160,8 @@
         <v>3</v>
       </c>
       <c r="D121" s="8"/>
-      <c r="E121" s="20"/>
-      <c r="F121" s="18"/>
+      <c r="E121" s="17"/>
+      <c r="F121" s="20"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
@@ -2949,10 +3174,10 @@
         <v>1</v>
       </c>
       <c r="D122" s="4"/>
-      <c r="E122" s="19">
+      <c r="E122" s="16">
         <v>7</v>
       </c>
-      <c r="F122" s="18"/>
+      <c r="F122" s="20"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="6" t="s">
@@ -2964,8 +3189,8 @@
       <c r="C123">
         <v>2</v>
       </c>
-      <c r="E123" s="19"/>
-      <c r="F123" s="18"/>
+      <c r="E123" s="16"/>
+      <c r="F123" s="20"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
@@ -2977,8 +3202,8 @@
       <c r="C124">
         <v>3</v>
       </c>
-      <c r="E124" s="19"/>
-      <c r="F124" s="18"/>
+      <c r="E124" s="16"/>
+      <c r="F124" s="20"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="6" t="s">
@@ -2990,8 +3215,8 @@
       <c r="C125">
         <v>4</v>
       </c>
-      <c r="E125" s="19"/>
-      <c r="F125" s="18"/>
+      <c r="E125" s="16"/>
+      <c r="F125" s="20"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
@@ -3003,8 +3228,8 @@
       <c r="C126">
         <v>5</v>
       </c>
-      <c r="E126" s="19"/>
-      <c r="F126" s="18"/>
+      <c r="E126" s="16"/>
+      <c r="F126" s="20"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
@@ -3016,8 +3241,8 @@
       <c r="C127">
         <v>6</v>
       </c>
-      <c r="E127" s="19"/>
-      <c r="F127" s="18"/>
+      <c r="E127" s="16"/>
+      <c r="F127" s="20"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
@@ -3030,8 +3255,8 @@
         <v>7</v>
       </c>
       <c r="D128" s="8"/>
-      <c r="E128" s="19"/>
-      <c r="F128" s="18"/>
+      <c r="E128" s="16"/>
+      <c r="F128" s="20"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
@@ -3046,10 +3271,10 @@
       <c r="D129" s="5">
         <v>1</v>
       </c>
-      <c r="E129" s="19">
+      <c r="E129" s="16">
         <v>27</v>
       </c>
-      <c r="F129" s="18"/>
+      <c r="F129" s="20"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
@@ -3064,8 +3289,8 @@
       <c r="D130">
         <v>2</v>
       </c>
-      <c r="E130" s="19"/>
-      <c r="F130" s="18"/>
+      <c r="E130" s="16"/>
+      <c r="F130" s="20"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
@@ -3080,8 +3305,8 @@
       <c r="D131">
         <v>3</v>
       </c>
-      <c r="E131" s="19"/>
-      <c r="F131" s="18"/>
+      <c r="E131" s="16"/>
+      <c r="F131" s="20"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
@@ -3096,15 +3321,15 @@
       <c r="D132">
         <v>4</v>
       </c>
-      <c r="E132" s="19"/>
-      <c r="F132" s="18"/>
+      <c r="E132" s="16"/>
+      <c r="F132" s="20"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B133" t="s">
-        <v>108</v>
+        <v>319</v>
       </c>
       <c r="C133">
         <v>5</v>
@@ -3112,15 +3337,15 @@
       <c r="D133">
         <v>5</v>
       </c>
-      <c r="E133" s="19"/>
-      <c r="F133" s="18"/>
+      <c r="E133" s="16"/>
+      <c r="F133" s="20"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>109</v>
+        <v>320</v>
       </c>
       <c r="C134">
         <v>6</v>
@@ -3128,15 +3353,15 @@
       <c r="D134" s="2">
         <v>6</v>
       </c>
-      <c r="E134" s="19"/>
-      <c r="F134" s="18"/>
+      <c r="E134" s="16"/>
+      <c r="F134" s="20"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C135">
         <v>7</v>
@@ -3144,8 +3369,8 @@
       <c r="D135" s="2">
         <v>6</v>
       </c>
-      <c r="E135" s="19"/>
-      <c r="F135" s="18"/>
+      <c r="E135" s="16"/>
+      <c r="F135" s="20"/>
       <c r="G135">
         <v>7</v>
       </c>
@@ -3158,7 +3383,7 @@
         <v>103</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C136">
         <v>8</v>
@@ -3166,15 +3391,15 @@
       <c r="D136">
         <v>8</v>
       </c>
-      <c r="E136" s="19"/>
-      <c r="F136" s="18"/>
+      <c r="E136" s="16"/>
+      <c r="F136" s="20"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C137">
         <v>9</v>
@@ -3182,15 +3407,15 @@
       <c r="D137">
         <v>9</v>
       </c>
-      <c r="E137" s="19"/>
-      <c r="F137" s="18"/>
+      <c r="E137" s="16"/>
+      <c r="F137" s="20"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C138">
         <v>10</v>
@@ -3198,15 +3423,15 @@
       <c r="D138">
         <v>10</v>
       </c>
-      <c r="E138" s="19"/>
-      <c r="F138" s="18"/>
+      <c r="E138" s="16"/>
+      <c r="F138" s="20"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B139" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C139">
         <v>11</v>
@@ -3214,15 +3439,15 @@
       <c r="D139">
         <v>11</v>
       </c>
-      <c r="E139" s="19"/>
-      <c r="F139" s="18"/>
+      <c r="E139" s="16"/>
+      <c r="F139" s="20"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B140" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C140">
         <v>12</v>
@@ -3230,15 +3455,15 @@
       <c r="D140">
         <v>12</v>
       </c>
-      <c r="E140" s="19"/>
-      <c r="F140" s="18"/>
+      <c r="E140" s="16"/>
+      <c r="F140" s="20"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B141" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C141">
         <v>13</v>
@@ -3246,15 +3471,15 @@
       <c r="D141">
         <v>13</v>
       </c>
-      <c r="E141" s="19"/>
-      <c r="F141" s="18"/>
+      <c r="E141" s="16"/>
+      <c r="F141" s="20"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B142" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C142">
         <v>14</v>
@@ -3262,15 +3487,15 @@
       <c r="D142">
         <v>14</v>
       </c>
-      <c r="E142" s="19"/>
-      <c r="F142" s="18"/>
+      <c r="E142" s="16"/>
+      <c r="F142" s="20"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C143">
         <v>15</v>
@@ -3278,15 +3503,15 @@
       <c r="D143">
         <v>15</v>
       </c>
-      <c r="E143" s="19"/>
-      <c r="F143" s="18"/>
+      <c r="E143" s="16"/>
+      <c r="F143" s="20"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C144">
         <v>16</v>
@@ -3294,15 +3519,15 @@
       <c r="D144" s="2">
         <v>16</v>
       </c>
-      <c r="E144" s="19"/>
-      <c r="F144" s="18"/>
+      <c r="E144" s="16"/>
+      <c r="F144" s="20"/>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C145">
         <v>17</v>
@@ -3310,8 +3535,8 @@
       <c r="D145" s="2">
         <v>16</v>
       </c>
-      <c r="E145" s="19"/>
-      <c r="F145" s="18"/>
+      <c r="E145" s="16"/>
+      <c r="F145" s="20"/>
       <c r="G145">
         <v>17</v>
       </c>
@@ -3324,7 +3549,7 @@
         <v>103</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C146">
         <v>18</v>
@@ -3332,15 +3557,15 @@
       <c r="D146">
         <v>18</v>
       </c>
-      <c r="E146" s="19"/>
-      <c r="F146" s="18"/>
+      <c r="E146" s="16"/>
+      <c r="F146" s="20"/>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C147">
         <v>19</v>
@@ -3348,15 +3573,15 @@
       <c r="D147" s="2">
         <v>19</v>
       </c>
-      <c r="E147" s="19"/>
-      <c r="F147" s="18"/>
+      <c r="E147" s="16"/>
+      <c r="F147" s="20"/>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C148">
         <v>20</v>
@@ -3364,8 +3589,8 @@
       <c r="D148" s="2">
         <v>19</v>
       </c>
-      <c r="E148" s="19"/>
-      <c r="F148" s="18"/>
+      <c r="E148" s="16"/>
+      <c r="F148" s="20"/>
       <c r="G148">
         <v>20</v>
       </c>
@@ -3378,7 +3603,7 @@
         <v>103</v>
       </c>
       <c r="B149" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C149">
         <v>21</v>
@@ -3386,15 +3611,15 @@
       <c r="D149" s="15">
         <v>21</v>
       </c>
-      <c r="E149" s="19"/>
-      <c r="F149" s="18"/>
+      <c r="E149" s="16"/>
+      <c r="F149" s="20"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B150" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C150">
         <v>22</v>
@@ -3402,15 +3627,15 @@
       <c r="D150" s="15">
         <v>22</v>
       </c>
-      <c r="E150" s="19"/>
-      <c r="F150" s="18"/>
+      <c r="E150" s="16"/>
+      <c r="F150" s="20"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B151" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C151">
         <v>23</v>
@@ -3418,15 +3643,15 @@
       <c r="D151" s="15">
         <v>23</v>
       </c>
-      <c r="E151" s="19"/>
-      <c r="F151" s="18"/>
+      <c r="E151" s="16"/>
+      <c r="F151" s="20"/>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B152" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C152">
         <v>24</v>
@@ -3434,15 +3659,15 @@
       <c r="D152" s="15">
         <v>24</v>
       </c>
-      <c r="E152" s="19"/>
-      <c r="F152" s="18"/>
+      <c r="E152" s="16"/>
+      <c r="F152" s="20"/>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C153">
         <v>25</v>
@@ -3450,8 +3675,8 @@
       <c r="D153" s="2">
         <v>1</v>
       </c>
-      <c r="E153" s="19"/>
-      <c r="F153" s="18"/>
+      <c r="E153" s="16"/>
+      <c r="F153" s="20"/>
       <c r="G153">
         <v>25</v>
       </c>
@@ -3464,7 +3689,7 @@
         <v>103</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C154">
         <v>26</v>
@@ -3472,15 +3697,15 @@
       <c r="D154" s="15">
         <v>26</v>
       </c>
-      <c r="E154" s="19"/>
-      <c r="F154" s="18"/>
+      <c r="E154" s="16"/>
+      <c r="F154" s="20"/>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B155" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C155">
         <v>27</v>
@@ -3488,15 +3713,15 @@
       <c r="D155" s="15">
         <v>27</v>
       </c>
-      <c r="E155" s="19"/>
-      <c r="F155" s="18"/>
+      <c r="E155" s="16"/>
+      <c r="F155" s="20"/>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B156" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C156">
         <v>28</v>
@@ -3504,15 +3729,15 @@
       <c r="D156" s="15">
         <v>28</v>
       </c>
-      <c r="E156" s="19"/>
-      <c r="F156" s="18"/>
+      <c r="E156" s="16"/>
+      <c r="F156" s="20"/>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B157" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C157">
         <v>29</v>
@@ -3520,15 +3745,15 @@
       <c r="D157" s="15">
         <v>29</v>
       </c>
-      <c r="E157" s="19"/>
-      <c r="F157" s="18"/>
+      <c r="E157" s="16"/>
+      <c r="F157" s="20"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B158" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C158">
         <v>30</v>
@@ -3536,15 +3761,15 @@
       <c r="D158" s="15">
         <v>30</v>
       </c>
-      <c r="E158" s="19"/>
-      <c r="F158" s="18"/>
+      <c r="E158" s="16"/>
+      <c r="F158" s="20"/>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
         <v>103</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C159" s="8">
         <v>31</v>
@@ -3552,1015 +3777,1015 @@
       <c r="D159" s="8">
         <v>31</v>
       </c>
-      <c r="E159" s="19"/>
-      <c r="F159" s="18"/>
+      <c r="E159" s="16"/>
+      <c r="F159" s="20"/>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C160" s="4">
         <v>1</v>
       </c>
       <c r="D160" s="4"/>
-      <c r="E160" s="19">
+      <c r="E160" s="16">
         <v>78</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B161" t="s">
         <v>135</v>
-      </c>
-      <c r="B161" t="s">
-        <v>137</v>
       </c>
       <c r="C161">
         <v>2</v>
       </c>
-      <c r="E161" s="19"/>
+      <c r="E161" s="16"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B162" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C162">
         <v>3</v>
       </c>
-      <c r="E162" s="19"/>
+      <c r="E162" s="16"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B163" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C163">
         <v>4</v>
       </c>
-      <c r="E163" s="19"/>
+      <c r="E163" s="16"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B164" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C164">
         <v>5</v>
       </c>
-      <c r="E164" s="19"/>
+      <c r="E164" s="16"/>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B165" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C165">
         <v>6</v>
       </c>
-      <c r="E165" s="19"/>
+      <c r="E165" s="16"/>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B166" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C166">
         <v>7</v>
       </c>
-      <c r="E166" s="19"/>
+      <c r="E166" s="16"/>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B167" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C167">
         <v>8</v>
       </c>
-      <c r="E167" s="19"/>
+      <c r="E167" s="16"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B168" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C168">
         <v>9</v>
       </c>
-      <c r="E168" s="19"/>
+      <c r="E168" s="16"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B169" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C169">
         <v>10</v>
       </c>
-      <c r="E169" s="19"/>
+      <c r="E169" s="16"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B170" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C170">
         <v>11</v>
       </c>
-      <c r="E170" s="19"/>
+      <c r="E170" s="16"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B171" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C171">
         <v>12</v>
       </c>
-      <c r="E171" s="19"/>
+      <c r="E171" s="16"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B172" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C172">
         <v>13</v>
       </c>
-      <c r="E172" s="19"/>
+      <c r="E172" s="16"/>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B173" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C173">
         <v>14</v>
       </c>
-      <c r="E173" s="19"/>
+      <c r="E173" s="16"/>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B174" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C174">
         <v>15</v>
       </c>
-      <c r="E174" s="19"/>
+      <c r="E174" s="16"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B175" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C175">
         <v>16</v>
       </c>
-      <c r="E175" s="19"/>
+      <c r="E175" s="16"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B176" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C176">
         <v>17</v>
       </c>
-      <c r="E176" s="19"/>
+      <c r="E176" s="16"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B177" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C177">
         <v>18</v>
       </c>
-      <c r="E177" s="19"/>
+      <c r="E177" s="16"/>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B178" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C178">
         <v>19</v>
       </c>
-      <c r="E178" s="19"/>
+      <c r="E178" s="16"/>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B179" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C179">
         <v>20</v>
       </c>
-      <c r="E179" s="19"/>
+      <c r="E179" s="16"/>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B180" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C180">
         <v>21</v>
       </c>
-      <c r="E180" s="19"/>
+      <c r="E180" s="16"/>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B181" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C181">
         <v>22</v>
       </c>
-      <c r="E181" s="19"/>
+      <c r="E181" s="16"/>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B182" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C182">
         <v>23</v>
       </c>
-      <c r="E182" s="19"/>
+      <c r="E182" s="16"/>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B183" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C183">
         <v>24</v>
       </c>
-      <c r="E183" s="19"/>
+      <c r="E183" s="16"/>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B184" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C184">
         <v>25</v>
       </c>
-      <c r="E184" s="19"/>
+      <c r="E184" s="16"/>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B185" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C185">
         <v>26</v>
       </c>
-      <c r="E185" s="19"/>
+      <c r="E185" s="16"/>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B186" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C186">
         <v>27</v>
       </c>
-      <c r="E186" s="19"/>
+      <c r="E186" s="16"/>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B187" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C187">
         <v>28</v>
       </c>
-      <c r="E187" s="19"/>
+      <c r="E187" s="16"/>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B188" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C188">
         <v>29</v>
       </c>
-      <c r="E188" s="19"/>
+      <c r="E188" s="16"/>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B189" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C189">
         <v>30</v>
       </c>
-      <c r="E189" s="19"/>
+      <c r="E189" s="16"/>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B190" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C190">
         <v>31</v>
       </c>
-      <c r="E190" s="19"/>
+      <c r="E190" s="16"/>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B191" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C191">
         <v>32</v>
       </c>
-      <c r="E191" s="19"/>
+      <c r="E191" s="16"/>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B192" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C192">
         <v>33</v>
       </c>
-      <c r="E192" s="19"/>
+      <c r="E192" s="16"/>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B193" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C193">
         <v>34</v>
       </c>
-      <c r="E193" s="19"/>
+      <c r="E193" s="16"/>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B194" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C194">
         <v>35</v>
       </c>
-      <c r="E194" s="19"/>
+      <c r="E194" s="16"/>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B195" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C195">
         <v>36</v>
       </c>
-      <c r="E195" s="19"/>
+      <c r="E195" s="16"/>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B196" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C196">
         <v>37</v>
       </c>
-      <c r="E196" s="19"/>
+      <c r="E196" s="16"/>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B197" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C197">
         <v>38</v>
       </c>
-      <c r="E197" s="19"/>
+      <c r="E197" s="16"/>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B198" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C198">
         <v>39</v>
       </c>
-      <c r="E198" s="19"/>
+      <c r="E198" s="16"/>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B199" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C199">
         <v>40</v>
       </c>
-      <c r="E199" s="19"/>
+      <c r="E199" s="16"/>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B200" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C200">
         <v>41</v>
       </c>
-      <c r="E200" s="19"/>
+      <c r="E200" s="16"/>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B201" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C201">
         <v>42</v>
       </c>
-      <c r="E201" s="19"/>
+      <c r="E201" s="16"/>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B202" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C202">
         <v>43</v>
       </c>
-      <c r="E202" s="19"/>
+      <c r="E202" s="16"/>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B203" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C203">
         <v>44</v>
       </c>
-      <c r="E203" s="19"/>
+      <c r="E203" s="16"/>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B204" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C204">
         <v>45</v>
       </c>
-      <c r="E204" s="19"/>
+      <c r="E204" s="16"/>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B205" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C205">
         <v>46</v>
       </c>
-      <c r="E205" s="19"/>
+      <c r="E205" s="16"/>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B206" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C206">
         <v>47</v>
       </c>
-      <c r="E206" s="19"/>
+      <c r="E206" s="16"/>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B207" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C207">
         <v>48</v>
       </c>
-      <c r="E207" s="19"/>
+      <c r="E207" s="16"/>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B208" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C208">
         <v>49</v>
       </c>
-      <c r="E208" s="19"/>
+      <c r="E208" s="16"/>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B209" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C209">
         <v>50</v>
       </c>
-      <c r="E209" s="19"/>
+      <c r="E209" s="16"/>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B210" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C210">
         <v>51</v>
       </c>
-      <c r="E210" s="19"/>
+      <c r="E210" s="16"/>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B211" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C211">
         <v>52</v>
       </c>
-      <c r="E211" s="19"/>
+      <c r="E211" s="16"/>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B212" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C212">
         <v>53</v>
       </c>
-      <c r="E212" s="19"/>
+      <c r="E212" s="16"/>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B213" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C213">
         <v>54</v>
       </c>
-      <c r="E213" s="19"/>
+      <c r="E213" s="16"/>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B214" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C214">
         <v>55</v>
       </c>
-      <c r="E214" s="19"/>
+      <c r="E214" s="16"/>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B215" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C215">
         <v>56</v>
       </c>
-      <c r="E215" s="19"/>
+      <c r="E215" s="16"/>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B216" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C216">
         <v>57</v>
       </c>
-      <c r="E216" s="19"/>
+      <c r="E216" s="16"/>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B217" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C217">
         <v>58</v>
       </c>
-      <c r="E217" s="19"/>
+      <c r="E217" s="16"/>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B218" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C218">
         <v>59</v>
       </c>
-      <c r="E218" s="19"/>
+      <c r="E218" s="16"/>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B219" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C219">
         <v>60</v>
       </c>
-      <c r="E219" s="19"/>
+      <c r="E219" s="16"/>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B220" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C220">
         <v>61</v>
       </c>
-      <c r="E220" s="19"/>
+      <c r="E220" s="16"/>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B221" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C221">
         <v>62</v>
       </c>
-      <c r="E221" s="19"/>
+      <c r="E221" s="16"/>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B222" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C222">
         <v>63</v>
       </c>
-      <c r="E222" s="19"/>
+      <c r="E222" s="16"/>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B223" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C223">
         <v>64</v>
       </c>
-      <c r="E223" s="19"/>
+      <c r="E223" s="16"/>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B224" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C224">
         <v>65</v>
       </c>
-      <c r="E224" s="19"/>
+      <c r="E224" s="16"/>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B225" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C225">
         <v>66</v>
       </c>
-      <c r="E225" s="19"/>
+      <c r="E225" s="16"/>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B226" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C226">
         <v>67</v>
       </c>
-      <c r="E226" s="19"/>
+      <c r="E226" s="16"/>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B227" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C227">
         <v>68</v>
       </c>
-      <c r="E227" s="19"/>
+      <c r="E227" s="16"/>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B228" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C228">
         <v>69</v>
       </c>
-      <c r="E228" s="19"/>
+      <c r="E228" s="16"/>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B229" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C229">
         <v>70</v>
       </c>
-      <c r="E229" s="19"/>
+      <c r="E229" s="16"/>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B230" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C230">
         <v>71</v>
       </c>
-      <c r="E230" s="19"/>
+      <c r="E230" s="16"/>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B231" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C231">
         <v>72</v>
       </c>
-      <c r="E231" s="19"/>
+      <c r="E231" s="16"/>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B232" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C232">
         <v>73</v>
       </c>
-      <c r="E232" s="19"/>
+      <c r="E232" s="16"/>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B233" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C233">
         <v>74</v>
       </c>
-      <c r="E233" s="19"/>
+      <c r="E233" s="16"/>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B234" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C234">
         <v>75</v>
       </c>
-      <c r="E234" s="19"/>
+      <c r="E234" s="16"/>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B235" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C235">
         <v>76</v>
       </c>
-      <c r="E235" s="19"/>
+      <c r="E235" s="16"/>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B236" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C236">
         <v>77</v>
       </c>
-      <c r="E236" s="19"/>
+      <c r="E236" s="16"/>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B237" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C237" s="8">
         <v>78</v>
       </c>
       <c r="D237" s="8"/>
-      <c r="E237" s="19"/>
+      <c r="E237" s="16"/>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C238" s="4">
         <v>1</v>
       </c>
       <c r="D238" s="4"/>
-      <c r="E238" s="19">
+      <c r="E238" s="16">
         <v>78</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="B239" t="s">
         <v>214</v>
-      </c>
-      <c r="B239" t="s">
-        <v>216</v>
       </c>
       <c r="C239">
         <v>2</v>
       </c>
-      <c r="E239" s="19"/>
+      <c r="E239" s="16"/>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B240" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C240">
         <v>3</v>
       </c>
-      <c r="E240" s="19"/>
+      <c r="E240" s="16"/>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B241" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C241">
         <v>4</v>
       </c>
-      <c r="E241" s="19"/>
+      <c r="E241" s="16"/>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B242" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C242">
         <v>5</v>
       </c>
-      <c r="E242" s="19"/>
+      <c r="E242" s="16"/>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B243" t="s">
         <v>105</v>
@@ -4568,846 +4793,846 @@
       <c r="C243">
         <v>6</v>
       </c>
-      <c r="E243" s="19"/>
+      <c r="E243" s="16"/>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B244" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C244">
         <v>7</v>
       </c>
-      <c r="E244" s="19"/>
+      <c r="E244" s="16"/>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B245" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C245">
         <v>8</v>
       </c>
-      <c r="E245" s="19"/>
+      <c r="E245" s="16"/>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B246" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C246">
         <v>9</v>
       </c>
-      <c r="E246" s="19"/>
+      <c r="E246" s="16"/>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B247" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C247">
         <v>10</v>
       </c>
-      <c r="E247" s="19"/>
+      <c r="E247" s="16"/>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B248" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C248">
         <v>11</v>
       </c>
-      <c r="E248" s="19"/>
+      <c r="E248" s="16"/>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B249" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C249">
         <v>12</v>
       </c>
-      <c r="E249" s="19"/>
+      <c r="E249" s="16"/>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B250" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C250">
         <v>13</v>
       </c>
-      <c r="E250" s="19"/>
+      <c r="E250" s="16"/>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B251" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C251">
         <v>14</v>
       </c>
-      <c r="E251" s="19"/>
+      <c r="E251" s="16"/>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B252" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C252">
         <v>15</v>
       </c>
-      <c r="E252" s="19"/>
+      <c r="E252" s="16"/>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B253" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C253">
         <v>16</v>
       </c>
-      <c r="E253" s="19"/>
+      <c r="E253" s="16"/>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B254" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C254">
         <v>17</v>
       </c>
-      <c r="E254" s="19"/>
+      <c r="E254" s="16"/>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B255" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C255">
         <v>18</v>
       </c>
-      <c r="E255" s="19"/>
+      <c r="E255" s="16"/>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B256" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C256">
         <v>19</v>
       </c>
-      <c r="E256" s="19"/>
+      <c r="E256" s="16"/>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B257" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C257">
         <v>20</v>
       </c>
-      <c r="E257" s="19"/>
+      <c r="E257" s="16"/>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B258" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C258">
         <v>21</v>
       </c>
-      <c r="E258" s="19"/>
+      <c r="E258" s="16"/>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B259" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C259">
         <v>22</v>
       </c>
-      <c r="E259" s="19"/>
+      <c r="E259" s="16"/>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B260" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C260">
         <v>23</v>
       </c>
-      <c r="E260" s="19"/>
+      <c r="E260" s="16"/>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B261" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C261">
         <v>24</v>
       </c>
-      <c r="E261" s="19"/>
+      <c r="E261" s="16"/>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B262" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C262">
         <v>25</v>
       </c>
-      <c r="E262" s="19"/>
+      <c r="E262" s="16"/>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B263" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C263">
         <v>26</v>
       </c>
-      <c r="E263" s="19"/>
+      <c r="E263" s="16"/>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B264" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C264">
         <v>27</v>
       </c>
-      <c r="E264" s="19"/>
+      <c r="E264" s="16"/>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B265" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C265">
         <v>28</v>
       </c>
-      <c r="E265" s="19"/>
+      <c r="E265" s="16"/>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B266" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C266">
         <v>29</v>
       </c>
-      <c r="E266" s="19"/>
+      <c r="E266" s="16"/>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B267" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C267">
         <v>30</v>
       </c>
-      <c r="E267" s="19"/>
+      <c r="E267" s="16"/>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B268" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C268">
         <v>31</v>
       </c>
-      <c r="E268" s="19"/>
+      <c r="E268" s="16"/>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B269" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C269">
         <v>32</v>
       </c>
-      <c r="E269" s="19"/>
+      <c r="E269" s="16"/>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B270" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C270">
         <v>33</v>
       </c>
-      <c r="E270" s="19"/>
+      <c r="E270" s="16"/>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B271" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C271">
         <v>34</v>
       </c>
-      <c r="E271" s="19"/>
+      <c r="E271" s="16"/>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B272" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C272">
         <v>35</v>
       </c>
-      <c r="E272" s="19"/>
+      <c r="E272" s="16"/>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B273" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C273">
         <v>36</v>
       </c>
-      <c r="E273" s="19"/>
+      <c r="E273" s="16"/>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B274" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C274">
         <v>37</v>
       </c>
-      <c r="E274" s="19"/>
+      <c r="E274" s="16"/>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B275" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C275">
         <v>38</v>
       </c>
-      <c r="E275" s="19"/>
+      <c r="E275" s="16"/>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B276" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C276">
         <v>39</v>
       </c>
-      <c r="E276" s="19"/>
+      <c r="E276" s="16"/>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B277" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C277">
         <v>40</v>
       </c>
-      <c r="E277" s="19"/>
+      <c r="E277" s="16"/>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B278" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C278">
         <v>41</v>
       </c>
-      <c r="E278" s="19"/>
+      <c r="E278" s="16"/>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B279" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C279">
         <v>42</v>
       </c>
-      <c r="E279" s="19"/>
+      <c r="E279" s="16"/>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B280" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C280">
         <v>43</v>
       </c>
-      <c r="E280" s="19"/>
+      <c r="E280" s="16"/>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B281" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C281">
         <v>44</v>
       </c>
-      <c r="E281" s="19"/>
+      <c r="E281" s="16"/>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B282" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C282">
         <v>45</v>
       </c>
-      <c r="E282" s="19"/>
+      <c r="E282" s="16"/>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B283" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C283">
         <v>46</v>
       </c>
-      <c r="E283" s="19"/>
+      <c r="E283" s="16"/>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B284" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C284">
         <v>47</v>
       </c>
-      <c r="E284" s="19"/>
+      <c r="E284" s="16"/>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B285" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C285">
         <v>48</v>
       </c>
-      <c r="E285" s="19"/>
+      <c r="E285" s="16"/>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B286" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C286">
         <v>49</v>
       </c>
-      <c r="E286" s="19"/>
+      <c r="E286" s="16"/>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B287" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C287">
         <v>50</v>
       </c>
-      <c r="E287" s="19"/>
+      <c r="E287" s="16"/>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B288" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C288">
         <v>51</v>
       </c>
-      <c r="E288" s="19"/>
+      <c r="E288" s="16"/>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B289" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C289">
         <v>52</v>
       </c>
-      <c r="E289" s="19"/>
+      <c r="E289" s="16"/>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B290" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C290">
         <v>53</v>
       </c>
-      <c r="E290" s="19"/>
+      <c r="E290" s="16"/>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B291" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C291">
         <v>54</v>
       </c>
-      <c r="E291" s="19"/>
+      <c r="E291" s="16"/>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B292" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C292">
         <v>55</v>
       </c>
-      <c r="E292" s="19"/>
+      <c r="E292" s="16"/>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B293" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C293">
         <v>56</v>
       </c>
-      <c r="E293" s="19"/>
+      <c r="E293" s="16"/>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B294" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C294">
         <v>57</v>
       </c>
-      <c r="E294" s="19"/>
+      <c r="E294" s="16"/>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B295" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C295">
         <v>58</v>
       </c>
-      <c r="E295" s="19"/>
+      <c r="E295" s="16"/>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B296" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C296">
         <v>59</v>
       </c>
-      <c r="E296" s="19"/>
+      <c r="E296" s="16"/>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B297" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C297">
         <v>60</v>
       </c>
-      <c r="E297" s="19"/>
+      <c r="E297" s="16"/>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B298" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C298">
         <v>61</v>
       </c>
-      <c r="E298" s="19"/>
+      <c r="E298" s="16"/>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B299" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C299">
         <v>62</v>
       </c>
-      <c r="E299" s="19"/>
+      <c r="E299" s="16"/>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B300" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C300">
         <v>63</v>
       </c>
-      <c r="E300" s="19"/>
+      <c r="E300" s="16"/>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B301" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C301">
         <v>64</v>
       </c>
-      <c r="E301" s="19"/>
+      <c r="E301" s="16"/>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B302" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C302">
         <v>65</v>
       </c>
-      <c r="E302" s="19"/>
+      <c r="E302" s="16"/>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B303" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C303">
         <v>66</v>
       </c>
-      <c r="E303" s="19"/>
+      <c r="E303" s="16"/>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B304" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C304">
         <v>67</v>
       </c>
-      <c r="E304" s="19"/>
+      <c r="E304" s="16"/>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B305" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C305">
         <v>68</v>
       </c>
-      <c r="E305" s="19"/>
+      <c r="E305" s="16"/>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B306" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C306">
         <v>69</v>
       </c>
-      <c r="E306" s="19"/>
+      <c r="E306" s="16"/>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B307" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C307">
         <v>70</v>
       </c>
-      <c r="E307" s="19"/>
+      <c r="E307" s="16"/>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B308" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C308">
         <v>71</v>
       </c>
-      <c r="E308" s="19"/>
+      <c r="E308" s="16"/>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B309" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C309">
         <v>72</v>
       </c>
-      <c r="E309" s="19"/>
+      <c r="E309" s="16"/>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B310" s="8" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C310" s="8">
         <v>73</v>
       </c>
       <c r="D310" s="8"/>
-      <c r="E310" s="19"/>
+      <c r="E310" s="16"/>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C311" s="4">
         <v>1</v>
       </c>
       <c r="D311" s="4"/>
-      <c r="E311" s="19">
+      <c r="E311" s="16">
         <v>4</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B312" t="s">
         <v>280</v>
-      </c>
-      <c r="B312" t="s">
-        <v>282</v>
       </c>
       <c r="C312">
         <v>2</v>
       </c>
-      <c r="E312" s="19"/>
+      <c r="E312" s="16"/>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C313" s="2">
         <v>3</v>
@@ -5415,14 +5640,14 @@
       <c r="D313">
         <v>3</v>
       </c>
-      <c r="E313" s="19"/>
+      <c r="E313" s="16"/>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C314" s="2">
         <v>4</v>
@@ -5430,14 +5655,14 @@
       <c r="D314">
         <v>3</v>
       </c>
-      <c r="E314" s="19"/>
+      <c r="E314" s="16"/>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C315" s="2">
         <v>5</v>
@@ -5445,14 +5670,14 @@
       <c r="D315">
         <v>3</v>
       </c>
-      <c r="E315" s="19"/>
+      <c r="E315" s="16"/>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" s="7" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B316" s="8" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C316" s="8">
         <v>6</v>
@@ -5460,14 +5685,14 @@
       <c r="D316" s="8">
         <v>6</v>
       </c>
-      <c r="E316" s="19"/>
+      <c r="E316" s="16"/>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C317" s="5">
         <v>1</v>
@@ -5475,7 +5700,7 @@
       <c r="D317" s="4">
         <v>1</v>
       </c>
-      <c r="E317" s="19">
+      <c r="E317" s="16">
         <v>6</v>
       </c>
       <c r="F317" s="6">
@@ -5485,15 +5710,15 @@
         <v>80</v>
       </c>
       <c r="I317" s="15" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="B318" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="B318" s="2" t="s">
-        <v>289</v>
       </c>
       <c r="C318" s="2">
         <v>2</v>
@@ -5501,23 +5726,23 @@
       <c r="D318">
         <v>2</v>
       </c>
-      <c r="E318" s="19"/>
+      <c r="E318" s="16"/>
       <c r="F318" s="6">
         <v>55</v>
       </c>
-      <c r="G318" s="17">
+      <c r="G318" s="19">
         <v>105</v>
       </c>
       <c r="I318" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C319" s="2">
         <v>3</v>
@@ -5525,21 +5750,21 @@
       <c r="D319">
         <v>2</v>
       </c>
-      <c r="E319" s="19"/>
+      <c r="E319" s="16"/>
       <c r="F319" s="6">
         <v>50</v>
       </c>
-      <c r="G319" s="17"/>
+      <c r="G319" s="19"/>
       <c r="I319" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C320" s="2">
         <v>4</v>
@@ -5547,23 +5772,23 @@
       <c r="D320">
         <v>4</v>
       </c>
-      <c r="E320" s="19"/>
+      <c r="E320" s="16"/>
       <c r="F320" s="6">
         <v>180</v>
       </c>
-      <c r="G320" s="17">
+      <c r="G320" s="19">
         <v>185</v>
       </c>
       <c r="I320" s="15" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C321" s="2">
         <v>5</v>
@@ -5571,21 +5796,21 @@
       <c r="D321">
         <v>4</v>
       </c>
-      <c r="E321" s="19"/>
+      <c r="E321" s="16"/>
       <c r="F321" s="6">
         <v>3</v>
       </c>
-      <c r="G321" s="17"/>
+      <c r="G321" s="19"/>
       <c r="I321" s="15" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B322" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C322">
         <v>6</v>
@@ -5593,7 +5818,7 @@
       <c r="D322">
         <v>6</v>
       </c>
-      <c r="E322" s="19"/>
+      <c r="E322" s="16"/>
       <c r="F322" s="6">
         <v>30</v>
       </c>
@@ -5601,15 +5826,15 @@
         <v>30</v>
       </c>
       <c r="I322" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C323" s="2">
         <v>7</v>
@@ -5617,20 +5842,20 @@
       <c r="D323">
         <v>1</v>
       </c>
-      <c r="E323" s="19"/>
+      <c r="E323" s="16"/>
       <c r="F323" s="6">
         <v>75</v>
       </c>
       <c r="G323" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B324" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C324">
         <v>8</v>
@@ -5638,7 +5863,7 @@
       <c r="D324">
         <v>8</v>
       </c>
-      <c r="E324" s="19"/>
+      <c r="E324" s="16"/>
       <c r="F324" s="6">
         <v>50</v>
       </c>
@@ -5648,10 +5873,10 @@
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" s="7" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B325" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C325" s="8">
         <v>9</v>
@@ -5659,7 +5884,7 @@
       <c r="D325" s="8">
         <v>9</v>
       </c>
-      <c r="E325" s="19"/>
+      <c r="E325" s="16"/>
       <c r="F325" s="6">
         <v>3</v>
       </c>
@@ -5669,10 +5894,10 @@
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C326" s="5">
         <v>1</v>
@@ -5680,7 +5905,7 @@
       <c r="D326">
         <v>1</v>
       </c>
-      <c r="E326" s="19">
+      <c r="E326" s="16">
         <v>6</v>
       </c>
       <c r="G326">
@@ -5690,10 +5915,10 @@
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="B327" t="s">
         <v>297</v>
-      </c>
-      <c r="B327" t="s">
-        <v>299</v>
       </c>
       <c r="C327">
         <v>2</v>
@@ -5701,14 +5926,14 @@
       <c r="D327">
         <v>2</v>
       </c>
-      <c r="E327" s="19"/>
+      <c r="E327" s="16"/>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B328" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C328">
         <v>3</v>
@@ -5716,14 +5941,14 @@
       <c r="D328">
         <v>3</v>
       </c>
-      <c r="E328" s="19"/>
+      <c r="E328" s="16"/>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B329" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C329">
         <v>4</v>
@@ -5731,14 +5956,14 @@
       <c r="D329">
         <v>4</v>
       </c>
-      <c r="E329" s="19"/>
+      <c r="E329" s="16"/>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B330" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C330">
         <v>5</v>
@@ -5746,14 +5971,14 @@
       <c r="D330">
         <v>5</v>
       </c>
-      <c r="E330" s="19"/>
+      <c r="E330" s="16"/>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B331" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C331">
         <v>6</v>
@@ -5761,14 +5986,14 @@
       <c r="D331">
         <v>6</v>
       </c>
-      <c r="E331" s="19"/>
+      <c r="E331" s="16"/>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" s="7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B332" s="9" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C332" s="9">
         <v>7</v>
@@ -5776,14 +6001,14 @@
       <c r="D332" s="8">
         <v>1</v>
       </c>
-      <c r="E332" s="19"/>
+      <c r="E332" s="16"/>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C333" s="5">
         <v>1</v>
@@ -5791,16 +6016,16 @@
       <c r="D333" s="4">
         <v>1</v>
       </c>
-      <c r="E333" s="19">
+      <c r="E333" s="16">
         <v>3</v>
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="B334" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="B334" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="C334" s="2">
         <v>2</v>
@@ -5808,14 +6033,14 @@
       <c r="D334">
         <v>1</v>
       </c>
-      <c r="E334" s="19"/>
+      <c r="E334" s="16"/>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B335" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C335">
         <v>3</v>
@@ -5823,14 +6048,14 @@
       <c r="D335">
         <v>3</v>
       </c>
-      <c r="E335" s="19"/>
+      <c r="E335" s="16"/>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" s="7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B336" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C336" s="8">
         <v>4</v>
@@ -5838,35 +6063,35 @@
       <c r="D336" s="8">
         <v>4</v>
       </c>
-      <c r="E336" s="19"/>
+      <c r="E336" s="16"/>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C337" s="4">
         <v>1</v>
       </c>
       <c r="D337" s="4"/>
-      <c r="E337" s="20">
+      <c r="E337" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="7" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B338" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C338" s="8">
         <v>2</v>
       </c>
       <c r="D338" s="8"/>
-      <c r="E338" s="20"/>
+      <c r="E338" s="17"/>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E339"/>
@@ -5933,23 +6158,1772 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="E326:E332"/>
-    <mergeCell ref="E317:E325"/>
-    <mergeCell ref="E333:E336"/>
-    <mergeCell ref="E337:E338"/>
-    <mergeCell ref="E311:E316"/>
-    <mergeCell ref="E238:E310"/>
-    <mergeCell ref="E160:E237"/>
-    <mergeCell ref="E122:E128"/>
-    <mergeCell ref="E119:E121"/>
-    <mergeCell ref="E129:E159"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="G318:G319"/>
     <mergeCell ref="G320:G321"/>
     <mergeCell ref="F129:F159"/>
     <mergeCell ref="F122:F128"/>
     <mergeCell ref="F119:F121"/>
+    <mergeCell ref="E238:E310"/>
+    <mergeCell ref="E160:E237"/>
+    <mergeCell ref="E122:E128"/>
+    <mergeCell ref="E119:E121"/>
+    <mergeCell ref="E129:E159"/>
+    <mergeCell ref="E326:E332"/>
+    <mergeCell ref="E317:E325"/>
+    <mergeCell ref="E333:E336"/>
+    <mergeCell ref="E337:E338"/>
+    <mergeCell ref="E311:E316"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{156AD1A7-E670-4FD2-878D-D670E3FF8905}">
+  <dimension ref="A1:F155"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="59.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>384</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>382</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>383</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="F1" s="23"/>
+    </row>
+    <row r="2" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2" s="23"/>
+    </row>
+    <row r="3" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3" s="23"/>
+    </row>
+    <row r="4" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" s="23"/>
+    </row>
+    <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="F5" s="23"/>
+    </row>
+    <row r="6" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="F6" s="23"/>
+    </row>
+    <row r="7" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="F7" s="23"/>
+    </row>
+    <row r="8" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="F8" s="23"/>
+    </row>
+    <row r="9" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9" s="23"/>
+    </row>
+    <row r="10" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="F10" s="23"/>
+    </row>
+    <row r="11" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="F11" s="23"/>
+    </row>
+    <row r="12" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="F12" s="23"/>
+    </row>
+    <row r="13" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="F13" s="23"/>
+    </row>
+    <row r="14" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="F14" s="23"/>
+    </row>
+    <row r="15" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="F15" s="23"/>
+    </row>
+    <row r="16" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="F16" s="23"/>
+    </row>
+    <row r="17" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="F17" s="23"/>
+    </row>
+    <row r="18" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="F18" s="23"/>
+    </row>
+    <row r="19" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="F19" s="23"/>
+    </row>
+    <row r="20" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="F20" s="23"/>
+    </row>
+    <row r="21" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="F21" s="23"/>
+    </row>
+    <row r="22" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="F22" s="23"/>
+    </row>
+    <row r="23" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="F23" s="23"/>
+    </row>
+    <row r="24" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="F24" s="23"/>
+    </row>
+    <row r="25" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" s="23"/>
+    </row>
+    <row r="26" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="F26" s="23"/>
+    </row>
+    <row r="27" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="F27" s="23"/>
+    </row>
+    <row r="28" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="F28" s="23"/>
+    </row>
+    <row r="29" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="F29" s="23"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="F30" s="23"/>
+    </row>
+    <row r="31" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="F31" s="23"/>
+    </row>
+    <row r="32" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="F32" s="23"/>
+    </row>
+    <row r="33" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="F33" s="23"/>
+    </row>
+    <row r="34" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="F34" s="23"/>
+    </row>
+    <row r="35" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="F35" s="23"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="F36" s="23"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="F37" s="23"/>
+    </row>
+    <row r="38" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="F38" s="23"/>
+    </row>
+    <row r="39" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>370</v>
+      </c>
+      <c r="F39" s="23"/>
+    </row>
+    <row r="40" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="F40" s="23"/>
+    </row>
+    <row r="41" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="E41" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="F41" s="23"/>
+    </row>
+    <row r="42" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="E42" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="F42" s="23"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="E43" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="F43" s="23"/>
+    </row>
+    <row r="44" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B44" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="D44" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="E44" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="F44" s="23"/>
+    </row>
+    <row r="45" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B45" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="D45" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="E45" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="F45" s="23"/>
+    </row>
+    <row r="46" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B46" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C46" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="D46" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="F46" s="23"/>
+    </row>
+    <row r="47" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E47" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="F47" s="23"/>
+    </row>
+    <row r="48" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B48" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>386</v>
+      </c>
+      <c r="D48" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="E48" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="F48" s="23"/>
+    </row>
+    <row r="49" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B49" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" s="23" t="s">
+        <v>386</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="E49" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="F49" s="23"/>
+    </row>
+    <row r="50" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>386</v>
+      </c>
+      <c r="D50" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="E50" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="F50" s="23"/>
+    </row>
+    <row r="51" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B51" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>386</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E51" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="F51" s="23"/>
+    </row>
+    <row r="52" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B52" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C52" s="23" t="s">
+        <v>386</v>
+      </c>
+      <c r="D52" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="E52" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="F52" s="23"/>
+    </row>
+    <row r="53" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B53" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C53" s="23" t="s">
+        <v>386</v>
+      </c>
+      <c r="D53" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="E53" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="F53" s="23"/>
+    </row>
+    <row r="54" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B54" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C54" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="E54" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="F54" s="23"/>
+    </row>
+    <row r="55" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B55" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C55" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="E55" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="F55" s="23"/>
+    </row>
+    <row r="56" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B56" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C56" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="E56" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="F56" s="23"/>
+    </row>
+    <row r="57" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B57" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C57" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="D57" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="E57" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="F57" s="23"/>
+    </row>
+    <row r="58" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B58" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C58" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="D58" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="F58" s="23"/>
+    </row>
+    <row r="59" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B59" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C59" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="D59" s="21" t="s">
+        <v>366</v>
+      </c>
+      <c r="E59" s="21" t="s">
+        <v>367</v>
+      </c>
+      <c r="F59" s="23"/>
+    </row>
+    <row r="60" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B60" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C60" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="F60" s="23"/>
+    </row>
+    <row r="61" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B61" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C61" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="F61" s="23"/>
+    </row>
+    <row r="62" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B62" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C62" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="D62" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="E62" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="F62" s="23"/>
+    </row>
+    <row r="63" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B63" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C63" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E63" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="F63" s="23"/>
+    </row>
+    <row r="64" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B64" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C64" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="D64" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="E64" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="F64" s="23"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B65" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C65" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="E65" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="F65" s="23"/>
+    </row>
+    <row r="66" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B66" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C66" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="D66" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="E66" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="F66" s="23"/>
+    </row>
+    <row r="67" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B67" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C67" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="D67" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E67" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="F67" s="23"/>
+    </row>
+    <row r="68" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B68" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C68" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="E68" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="F68" s="23"/>
+    </row>
+    <row r="69" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B69" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C69" s="23" t="s">
+        <v>387</v>
+      </c>
+      <c r="D69" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="E69" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="F69" s="23"/>
+    </row>
+    <row r="70" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B70" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C70" s="23" t="s">
+        <v>387</v>
+      </c>
+      <c r="D70" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="E70" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="F70" s="23"/>
+    </row>
+    <row r="71" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B71" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C71" s="23" t="s">
+        <v>387</v>
+      </c>
+      <c r="D71" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="E71" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="F71" s="23"/>
+    </row>
+    <row r="72" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B72" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C72" s="23" t="s">
+        <v>387</v>
+      </c>
+      <c r="D72" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="E72" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="F72" s="23"/>
+    </row>
+    <row r="73" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B73" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C73" s="23" t="s">
+        <v>387</v>
+      </c>
+      <c r="D73" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E73" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="F73" s="23"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B74" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C74" s="23" t="s">
+        <v>387</v>
+      </c>
+      <c r="D74" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="E74" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="F74" s="23"/>
+    </row>
+    <row r="75" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B75" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C75" s="23" t="s">
+        <v>387</v>
+      </c>
+      <c r="D75" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="E75" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="F75" s="23"/>
+    </row>
+    <row r="76" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B76" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C76" s="23" t="s">
+        <v>351</v>
+      </c>
+      <c r="D76" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="E76" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="F76" s="23"/>
+    </row>
+    <row r="77" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B77" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C77" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="D77" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="E77" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="F77" s="23"/>
+    </row>
+    <row r="78" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B78" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C78" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="D78" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="E78" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="F78" s="23"/>
+    </row>
+    <row r="79" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="23"/>
+      <c r="F79" s="23"/>
+    </row>
+    <row r="80" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="23"/>
+      <c r="C80" s="23"/>
+      <c r="F80" s="23"/>
+    </row>
+    <row r="81" spans="2:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="23"/>
+      <c r="C81" s="23"/>
+      <c r="F81" s="23"/>
+    </row>
+    <row r="82" spans="2:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="23"/>
+      <c r="C82" s="23"/>
+      <c r="F82" s="23"/>
+    </row>
+    <row r="83" spans="2:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="23"/>
+      <c r="C83" s="23"/>
+      <c r="F83" s="23"/>
+    </row>
+    <row r="84" spans="2:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="23"/>
+      <c r="C84" s="23"/>
+      <c r="F84" s="23"/>
+    </row>
+    <row r="85" spans="2:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="23"/>
+      <c r="C85" s="23"/>
+      <c r="F85" s="23"/>
+    </row>
+    <row r="86" spans="2:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="23"/>
+      <c r="C86" s="23"/>
+      <c r="D86" s="21"/>
+      <c r="E86" s="21"/>
+      <c r="F86" s="23"/>
+    </row>
+    <row r="87" spans="2:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="23"/>
+      <c r="C87" s="23"/>
+      <c r="F87" s="23"/>
+    </row>
+    <row r="88" spans="2:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="23"/>
+      <c r="C88" s="23"/>
+      <c r="F88" s="23"/>
+    </row>
+    <row r="89" spans="2:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B89" s="23"/>
+      <c r="C89" s="23"/>
+      <c r="F89" s="23"/>
+    </row>
+    <row r="90" spans="2:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B90" s="23"/>
+      <c r="C90" s="23"/>
+      <c r="F90" s="23"/>
+    </row>
+    <row r="91" spans="2:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="23"/>
+      <c r="C91" s="23"/>
+      <c r="F91" s="23"/>
+    </row>
+    <row r="92" spans="2:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B92" s="23"/>
+      <c r="C92" s="23"/>
+      <c r="F92" s="23"/>
+    </row>
+    <row r="93" spans="2:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C93" s="21"/>
+      <c r="F93" s="23"/>
+    </row>
+    <row r="94" spans="2:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C94" s="21"/>
+      <c r="F94" s="23"/>
+    </row>
+    <row r="95" spans="2:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C95" s="21"/>
+      <c r="F95" s="23"/>
+    </row>
+    <row r="96" spans="2:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C96" s="21"/>
+      <c r="F96" s="23"/>
+    </row>
+    <row r="97" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C97" s="21"/>
+      <c r="F97" s="23"/>
+    </row>
+    <row r="98" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C98" s="21"/>
+      <c r="F98" s="23"/>
+    </row>
+    <row r="99" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C99" s="21"/>
+      <c r="F99" s="23"/>
+    </row>
+    <row r="100" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C100" s="21"/>
+      <c r="F100" s="23"/>
+    </row>
+    <row r="101" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C101" s="21"/>
+      <c r="F101" s="23"/>
+    </row>
+    <row r="102" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C102" s="21"/>
+      <c r="F102" s="23"/>
+    </row>
+    <row r="103" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C103" s="21"/>
+      <c r="F103" s="23"/>
+    </row>
+    <row r="104" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C104" s="21"/>
+      <c r="F104" s="23"/>
+    </row>
+    <row r="105" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C105" s="21"/>
+    </row>
+    <row r="106" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C106" s="21"/>
+      <c r="F106" s="23"/>
+    </row>
+    <row r="107" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C107" s="21"/>
+      <c r="F107" s="23"/>
+    </row>
+    <row r="108" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C108" s="21"/>
+      <c r="F108" s="23"/>
+    </row>
+    <row r="109" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C109" s="21"/>
+      <c r="F109" s="23"/>
+    </row>
+    <row r="110" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C110" s="21"/>
+      <c r="F110" s="23"/>
+    </row>
+    <row r="111" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C111" s="21"/>
+      <c r="F111" s="23"/>
+    </row>
+    <row r="112" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C112" s="21"/>
+      <c r="F112" s="23"/>
+    </row>
+    <row r="113" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C113" s="21"/>
+      <c r="F113" s="23"/>
+    </row>
+    <row r="114" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C114" s="21"/>
+      <c r="F114" s="23"/>
+    </row>
+    <row r="115" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C115" s="21"/>
+      <c r="F115" s="23"/>
+    </row>
+    <row r="116" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C116" s="21"/>
+      <c r="F116" s="23"/>
+    </row>
+    <row r="117" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C117" s="21"/>
+      <c r="F117" s="23"/>
+    </row>
+    <row r="118" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C118" s="21"/>
+      <c r="F118" s="23"/>
+    </row>
+    <row r="119" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C119" s="21"/>
+      <c r="F119" s="23"/>
+    </row>
+    <row r="120" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C120" s="21"/>
+      <c r="F120" s="23"/>
+    </row>
+    <row r="121" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C121" s="21"/>
+      <c r="F121" s="23"/>
+    </row>
+    <row r="122" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C122" s="21"/>
+      <c r="F122" s="23"/>
+    </row>
+    <row r="123" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C123" s="21"/>
+      <c r="F123" s="23"/>
+    </row>
+    <row r="124" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C124" s="21"/>
+      <c r="F124" s="23"/>
+    </row>
+    <row r="125" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C125" s="21"/>
+      <c r="F125" s="23"/>
+    </row>
+    <row r="126" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C126" s="21"/>
+      <c r="F126" s="23"/>
+    </row>
+    <row r="127" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C127" s="21"/>
+      <c r="F127" s="23"/>
+    </row>
+    <row r="128" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C128" s="21"/>
+      <c r="F128" s="23"/>
+    </row>
+    <row r="129" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C129" s="21"/>
+      <c r="F129" s="23"/>
+    </row>
+    <row r="130" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C130" s="21"/>
+      <c r="F130" s="23"/>
+    </row>
+    <row r="131" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C131" s="21"/>
+      <c r="F131" s="23"/>
+    </row>
+    <row r="132" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C132" s="21"/>
+      <c r="F132" s="23"/>
+    </row>
+    <row r="133" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C133" s="21"/>
+      <c r="F133" s="23"/>
+    </row>
+    <row r="134" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C134" s="21"/>
+      <c r="F134" s="23"/>
+    </row>
+    <row r="135" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C135" s="21"/>
+      <c r="F135" s="23"/>
+    </row>
+    <row r="136" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C136" s="21"/>
+      <c r="F136" s="23"/>
+    </row>
+    <row r="137" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C137" s="21"/>
+      <c r="F137" s="23"/>
+    </row>
+    <row r="138" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C138" s="21"/>
+      <c r="F138" s="23"/>
+    </row>
+    <row r="139" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C139" s="21"/>
+      <c r="F139" s="23"/>
+    </row>
+    <row r="140" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C140" s="21"/>
+      <c r="F140" s="23"/>
+    </row>
+    <row r="141" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C141" s="21"/>
+      <c r="F141" s="23"/>
+    </row>
+    <row r="142" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C142" s="21"/>
+      <c r="F142" s="23"/>
+    </row>
+    <row r="143" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C143" s="21"/>
+      <c r="F143" s="23"/>
+    </row>
+    <row r="144" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C144" s="21"/>
+    </row>
+    <row r="145" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C145" s="21"/>
+      <c r="F145" s="23"/>
+    </row>
+    <row r="146" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C146" s="21"/>
+      <c r="F146" s="23"/>
+    </row>
+    <row r="147" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C147" s="21"/>
+      <c r="F147" s="23"/>
+    </row>
+    <row r="148" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C148" s="21"/>
+      <c r="F148" s="23"/>
+    </row>
+    <row r="149" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C149" s="21"/>
+      <c r="F149" s="23"/>
+    </row>
+    <row r="150" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C150" s="21"/>
+      <c r="F150" s="23"/>
+    </row>
+    <row r="151" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C151" s="21"/>
+      <c r="F151" s="23"/>
+    </row>
+    <row r="152" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C152" s="21"/>
+      <c r="F152" s="23"/>
+    </row>
+    <row r="153" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C153" s="21"/>
+      <c r="F153" s="23"/>
+    </row>
+    <row r="154" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C154" s="21"/>
+      <c r="F154" s="23"/>
+    </row>
+    <row r="155" spans="3:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C155" s="21"/>
+      <c r="F155" s="23"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="C1:F155" xr:uid="{156AD1A7-E670-4FD2-878D-D670E3FF8905}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:F155">
+      <sortCondition ref="E1:E155"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="70" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
 </file>